--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B186"/>
+  <dimension ref="A1:B187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2087,574 +2087,586 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>QRB56514</t>
+          <t>QHB18956</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ZmLU-WzDm</t>
+          <t>B4nt-rvpd</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>QUE22078</t>
+          <t>QRB56514</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>tCyA-Oi7m</t>
+          <t>ZmLU-WzDm</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>QYS77373</t>
+          <t>QUE22078</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>bdKc-q4v6</t>
+          <t>tCyA-Oi7m</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>RBA20127</t>
+          <t>QYS77373</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>oE79-b1Se</t>
+          <t>bdKc-q4v6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RLQ73857</t>
+          <t>RBA20127</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>QZVO-4p3B</t>
+          <t>oE79-b1Se</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RNL06004</t>
+          <t>RLQ73857</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>WaLc-sBJY</t>
+          <t>QZVO-4p3B</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RSN71799</t>
+          <t>RNL06004</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>APKz-8tHA</t>
+          <t>WaLc-sBJY</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>SAF98648</t>
+          <t>RSN71799</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>JUDx-dQqy</t>
+          <t>APKz-8tHA</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SDE98641</t>
+          <t>SAF98648</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>E4LL-qV7u</t>
+          <t>JUDx-dQqy</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SEV98034</t>
+          <t>SDE98641</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>3FMv-ztV8</t>
+          <t>E4LL-qV7u</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SGE51092</t>
+          <t>SEV98034</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>9G7O-tS42</t>
+          <t>3FMv-ztV8</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SLP43775</t>
+          <t>SGE51092</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>JIk1-QTjm</t>
+          <t>9G7O-tS42</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SMF79012</t>
+          <t>SLP43775</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>NcnL-Ufev</t>
+          <t>JIk1-QTjm</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SNZ44527</t>
+          <t>SMF79012</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Idtr-Ef1p</t>
+          <t>NcnL-Ufev</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SPZ85652</t>
+          <t>SNZ44527</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>BqNU-jKbs</t>
+          <t>Idtr-Ef1p</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SQX65443</t>
+          <t>SPZ85652</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>2Y2u-Iexu</t>
+          <t>BqNU-jKbs</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SSU10232</t>
+          <t>SQX65443</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2s1b-MrBM</t>
+          <t>2Y2u-Iexu</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SYH46751</t>
+          <t>SSU10232</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>g47k-j3HG</t>
+          <t>2s1b-MrBM</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TKW11810</t>
+          <t>SYH46751</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>XbfA-yocA</t>
+          <t>g47k-j3HG</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TMJ36970</t>
+          <t>TKW11810</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>NiMt-vJm1</t>
+          <t>XbfA-yocA</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>TRC98148</t>
+          <t>TMJ36970</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ImK9-sJVr</t>
+          <t>NiMt-vJm1</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TTS04230</t>
+          <t>TRC98148</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>oJvJ-C0eE</t>
+          <t>ImK9-sJVr</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>TXC42578</t>
+          <t>TTS04230</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>ttrI-HkEA</t>
+          <t>oJvJ-C0eE</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>UUR79971</t>
+          <t>TXC42578</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>2Vvw-yPgX</t>
+          <t>ttrI-HkEA</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>VDD06679</t>
+          <t>UUR79971</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>9NFD-F33z</t>
+          <t>2Vvw-yPgX</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>VEQ81429</t>
+          <t>VDD06679</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>xnGV-gtxP</t>
+          <t>9NFD-F33z</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>VPE32737</t>
+          <t>VEQ81429</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>83SX-bO49</t>
+          <t>xnGV-gtxP</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>WJH36041</t>
+          <t>VPE32737</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>yPk4-9kvI</t>
+          <t>83SX-bO49</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>WNA57398</t>
+          <t>WJH36041</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>CU9v-k8Hc</t>
+          <t>yPk4-9kvI</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>WUA13603</t>
+          <t>WNA57398</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>hdCj-fLq2</t>
+          <t>CU9v-k8Hc</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>WUH93925</t>
+          <t>WUA13603</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>8m3J-Gzlk</t>
+          <t>hdCj-fLq2</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>WWS24235</t>
+          <t>WUH93925</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>dTMF-Ocal</t>
+          <t>8m3J-Gzlk</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>XKS75480</t>
+          <t>WWS24235</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>c0hS-CdvD</t>
+          <t>dTMF-Ocal</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>XOA75961</t>
+          <t>XKS75480</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>VRah-kBaa</t>
+          <t>c0hS-CdvD</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>XYT33259</t>
+          <t>XOA75961</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ahUH-85T2</t>
+          <t>VRah-kBaa</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>XYZ70850</t>
+          <t>XYT33259</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>jdV6-HalU</t>
+          <t>ahUH-85T2</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>YBX87679</t>
+          <t>XYZ70850</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>442D-goVh</t>
+          <t>jdV6-HalU</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>YCN31679</t>
+          <t>YBX87679</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>SBfE-010a</t>
+          <t>442D-goVh</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>YFU10307</t>
+          <t>YCN31679</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>pv8C-S2qP</t>
+          <t>SBfE-010a</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>YGP30798</t>
+          <t>YFU10307</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>dZEv-nHKw</t>
+          <t>pv8C-S2qP</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>YHZ51082</t>
+          <t>YGP30798</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>7j63-7HKa</t>
+          <t>dZEv-nHKw</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>YOT12953</t>
+          <t>YHZ51082</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SxGc-ZaIN</t>
+          <t>7j63-7HKa</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ZAM21080</t>
+          <t>YOT12953</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>COFy-pMla</t>
+          <t>SxGc-ZaIN</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ZHU54125</t>
+          <t>ZAM21080</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>5RJe-0r17</t>
+          <t>COFy-pMla</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ZLP77106</t>
+          <t>ZHU54125</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>djSn-TgS9</t>
+          <t>5RJe-0r17</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ZNA23106</t>
+          <t>ZLP77106</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SHid-kPC3</t>
+          <t>djSn-TgS9</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ZSU27095</t>
+          <t>ZNA23106</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>3TQp-7e2s</t>
+          <t>SHid-kPC3</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
+          <t>ZSU27095</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>3TQp-7e2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
           <t>ZVK04224</t>
         </is>
       </c>
-      <c r="B186" t="inlineStr">
+      <c r="B187" t="inlineStr">
         <is>
           <t>9gaA-gLOl</t>
         </is>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B187"/>
+  <dimension ref="A1:B191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,2110 +563,2158 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BFI60670</t>
+          <t>BBA65823</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>iOpa-quCx</t>
+          <t>8InB-77sx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BGG58729</t>
+          <t>BFI60670</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3RgL-WsLQ</t>
+          <t>iOpa-quCx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BJH88419</t>
+          <t>BGG58729</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>JwOH-onjo</t>
+          <t>3RgL-WsLQ</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BOZ64205</t>
+          <t>BJH88419</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cqic-pxFH</t>
+          <t>JwOH-onjo</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BUR49898</t>
+          <t>BOZ64205</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>uP55-nNU2</t>
+          <t>Cqic-pxFH</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>CBP36635</t>
+          <t>BUR49898</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3o0E-H0eS</t>
+          <t>uP55-nNU2</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CEG78579</t>
+          <t>CBP36635</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>oGuY-hS6y</t>
+          <t>3o0E-H0eS</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CEV66266</t>
+          <t>CEG78579</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>595F-5DPV</t>
+          <t>oGuY-hS6y</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CEX73283</t>
+          <t>CEV66266</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BvrE-h4h6</t>
+          <t>595F-5DPV</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CGY86131</t>
+          <t>CEX73283</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5EJ5-nSOu</t>
+          <t>BvrE-h4h6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CHZ14322</t>
+          <t>CGY86131</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>rJ50-xReo</t>
+          <t>5EJ5-nSOu</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CNJ73848</t>
+          <t>CHZ14322</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>uyHI-dehW</t>
+          <t>rJ50-xReo</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CNQ05106</t>
+          <t>CNJ73848</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>JKLS-ZXPj</t>
+          <t>uyHI-dehW</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CQL05471</t>
+          <t>CNQ05106</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>k8LF-oP5k</t>
+          <t>JKLS-ZXPj</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CWI21231</t>
+          <t>CQL05471</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VERb-T6sQ</t>
+          <t>k8LF-oP5k</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CXY21844</t>
+          <t>CWI21231</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nAFY-KtfZ</t>
+          <t>VERb-T6sQ</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CYB55817</t>
+          <t>CXY21844</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>kyA4-BHSa</t>
+          <t>nAFY-KtfZ</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CYN09662</t>
+          <t>CYB55817</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>unqS-753q</t>
+          <t>kyA4-BHSa</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>DCC25940</t>
+          <t>CYN09662</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>9X56-vHTG</t>
+          <t>unqS-753q</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DGL58063</t>
+          <t>DCC25940</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>lQpJ-cvmL</t>
+          <t>9X56-vHTG</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DHH79187</t>
+          <t>DGL58063</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>kp6O-nXp3</t>
+          <t>lQpJ-cvmL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DJK20638</t>
+          <t>DHH79187</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ZJAv-brF5</t>
+          <t>kp6O-nXp3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DLP45053</t>
+          <t>DJK20638</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>L7sf-MoLb</t>
+          <t>ZJAv-brF5</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DQD33133</t>
+          <t>DLP45053</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>WX5H-LiPX</t>
+          <t>L7sf-MoLb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DVJ66295</t>
+          <t>DQD33133</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8Bl3-qRML</t>
+          <t>WX5H-LiPX</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DZI77349</t>
+          <t>DTZ69845</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>exKl-ZgTI</t>
+          <t>FiA8-mFOt</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>EBT22822</t>
+          <t>DVJ66295</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2lhq-XPz5</t>
+          <t>8Bl3-qRML</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>EWP70521</t>
+          <t>DZI77349</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>sAoe-qfVx</t>
+          <t>exKl-ZgTI</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EYO38305</t>
+          <t>EBT22822</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>qbbV-unNd</t>
+          <t>2lhq-XPz5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FLQ72134</t>
+          <t>EWP70521</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Oj7z-iK7O</t>
+          <t>sAoe-qfVx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FNU34959</t>
+          <t>EYO38305</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>6Rb4-9itD</t>
+          <t>qbbV-unNd</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FOJ78948</t>
+          <t>FLQ72134</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>z4ZP-wYr2</t>
+          <t>Oj7z-iK7O</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FQP62630</t>
+          <t>FNU34959</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>YPWV-F4Jw</t>
+          <t>6Rb4-9itD</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FRS19080</t>
+          <t>FOJ78948</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>8lEh-Ggjd</t>
+          <t>z4ZP-wYr2</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FUSURIN1</t>
+          <t>FQP62630</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>sQd2-HCth</t>
+          <t>YPWV-F4Jw</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FWZ82980</t>
+          <t>FRS19080</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Km0s-i1f3</t>
+          <t>8lEh-Ggjd</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FXB60927</t>
+          <t>FUSURIN1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>d20X-vLsV</t>
+          <t>sQd2-HCth</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GCV61524</t>
+          <t>FWZ82980</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Xhaf-F9mT</t>
+          <t>Km0s-i1f3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GEL08954</t>
+          <t>FXB60927</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>zqti-TUKL</t>
+          <t>d20X-vLsV</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GEP48591</t>
+          <t>GCV61524</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ipb2-EtbP</t>
+          <t>Xhaf-F9mT</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GFN61654</t>
+          <t>GEL08954</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>nOpR-i46M</t>
+          <t>zqti-TUKL</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GIE22684</t>
+          <t>GEP48591</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>7YFY-lEPW</t>
+          <t>ipb2-EtbP</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GKE90115</t>
+          <t>GFN61654</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ZK3R-ekIU</t>
+          <t>nOpR-i46M</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GLG55164</t>
+          <t>GIE22684</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>rMri-gCbQ</t>
+          <t>7YFY-lEPW</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GQG06884</t>
+          <t>GKE90115</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>yZSK-Cyby</t>
+          <t>ZK3R-ekIU</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GSJ38697</t>
+          <t>GLG55164</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>dcc9-1DuY</t>
+          <t>rMri-gCbQ</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GSY94523</t>
+          <t>GQG06884</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CykC-fp9I</t>
+          <t>yZSK-Cyby</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GVM53776</t>
+          <t>GSJ38697</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IUZs-UrSU</t>
+          <t>dcc9-1DuY</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>HBP33017</t>
+          <t>GSY94523</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>D3ly-X1Qr</t>
+          <t>CykC-fp9I</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>HNS34640</t>
+          <t>GVM53776</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>dPb1-DHLF</t>
+          <t>IUZs-UrSU</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HPT02640</t>
+          <t>HBP33017</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>c2kk-PGg8</t>
+          <t>D3ly-X1Qr</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HQH08532</t>
+          <t>HNS34640</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0fh0-QX5H</t>
+          <t>dPb1-DHLF</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HRY29891</t>
+          <t>HPT02640</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>UjZ9-SZGT</t>
+          <t>c2kk-PGg8</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HWP25524</t>
+          <t>HQH08532</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BWy7-13Ec</t>
+          <t>0fh0-QX5H</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IAE88291</t>
+          <t>HRY29891</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>4Ceg-RIv5</t>
+          <t>UjZ9-SZGT</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>IGN23276</t>
+          <t>HWP25524</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ZKGo-6azn</t>
+          <t>BWy7-13Ec</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IGX57659</t>
+          <t>IAE88291</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>F8R5-Mhli</t>
+          <t>4Ceg-RIv5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ILO34901</t>
+          <t>IGN23276</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>VPO5-2Unw</t>
+          <t>ZKGo-6azn</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IMW07942</t>
+          <t>IGX57659</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ors6-bajw</t>
+          <t>F8R5-Mhli</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>IQI33918</t>
+          <t>ILO34901</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>quU8-kFRw</t>
+          <t>VPO5-2Unw</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IUU53315</t>
+          <t>IMW07942</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>bHGN-Gt9k</t>
+          <t>ors6-bajw</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IWX83001</t>
+          <t>IQI33918</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0hfb-VytH</t>
+          <t>quU8-kFRw</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>JJI69427</t>
+          <t>IUU53315</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Mcpe-MdKl</t>
+          <t>bHGN-Gt9k</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>JMV12916</t>
+          <t>IWX83001</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>wFYF-qjdW</t>
+          <t>0hfb-VytH</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>JNQ15800</t>
+          <t>JJI69427</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>UOVA-N6XO</t>
+          <t>Mcpe-MdKl</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>JSH83558</t>
+          <t>JMV12916</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>NUAZ-lHPu</t>
+          <t>wFYF-qjdW</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>JSO81414</t>
+          <t>JNQ15800</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2SfQ-XyEl</t>
+          <t>UOVA-N6XO</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>JTN17189</t>
+          <t>JSH83558</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>wg9A-To8N</t>
+          <t>NUAZ-lHPu</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>JTQ20003</t>
+          <t>JSO81414</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>xXs3-0q1q</t>
+          <t>2SfQ-XyEl</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>KCH53154</t>
+          <t>JTN17189</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RwJm-IF1y</t>
+          <t>wg9A-To8N</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>KCH80368</t>
+          <t>JTQ20003</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>j6lG-9k2c</t>
+          <t>xXs3-0q1q</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>KCS62207</t>
+          <t>KCH53154</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Ge7V-N1Fb</t>
+          <t>RwJm-IF1y</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>KNB79119</t>
+          <t>KCH80368</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>BRVy-AfTK</t>
+          <t>j6lG-9k2c</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>KPJ23941</t>
+          <t>KCS62207</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>qcjI-pNgm</t>
+          <t>Ge7V-N1Fb</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>KQT40874</t>
+          <t>KNB79119</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>sgUM-aaYM</t>
+          <t>BRVy-AfTK</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>KRH18822</t>
+          <t>KPJ23941</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>vMtE-4cYL</t>
+          <t>qcjI-pNgm</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>KTK81122</t>
+          <t>KQT40874</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>X8Dz-iKF1</t>
+          <t>sgUM-aaYM</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>KVA96952</t>
+          <t>KRH18822</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VuFC-8E26</t>
+          <t>vMtE-4cYL</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>KVU62139</t>
+          <t>KTK81122</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>LUI5-Geov</t>
+          <t>X8Dz-iKF1</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>KXZ79956</t>
+          <t>KVA96952</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>xmdQ-yw08</t>
+          <t>VuFC-8E26</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>KZL99357</t>
+          <t>KVU62139</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>14ZB-xFwZ</t>
+          <t>LUI5-Geov</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>KZU53477</t>
+          <t>KWN66857</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1qwx-jHLR</t>
+          <t>Fv4Y-68ZM</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>LFA56301</t>
+          <t>KXZ79956</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>trbu-XQWz</t>
+          <t>xmdQ-yw08</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>LGP73888</t>
+          <t>KZL99357</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DcIT-TKtd</t>
+          <t>14ZB-xFwZ</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>LHQ57930</t>
+          <t>KZU53477</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>cRpb-1kZX</t>
+          <t>1qwx-jHLR</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LJE73544</t>
+          <t>LFA56301</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>c8yU-Zgju</t>
+          <t>trbu-XQWz</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LKG10504</t>
+          <t>LGP73888</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>t6Zj-7N4q</t>
+          <t>DcIT-TKtd</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LLI56060</t>
+          <t>LHQ57930</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ePiy-wSTy</t>
+          <t>cRpb-1kZX</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LPM87075</t>
+          <t>LJE73544</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>AgXC-arDZ</t>
+          <t>c8yU-Zgju</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>MAI64055</t>
+          <t>LKG10504</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Mzqj-Ky8q</t>
+          <t>t6Zj-7N4q</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>MDE12029</t>
+          <t>LLI56060</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>hhXj-vBGM</t>
+          <t>ePiy-wSTy</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>MEG11153</t>
+          <t>LPM87075</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>QThA-UkVH</t>
+          <t>AgXC-arDZ</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MIJ60289</t>
+          <t>MAI64055</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>YgVT-De6l</t>
+          <t>Mzqj-Ky8q</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MNW15780</t>
+          <t>MDE12029</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>6iUB-Vag7</t>
+          <t>hhXj-vBGM</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MRQ02763</t>
+          <t>MEG11153</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>jkZw-MaOb</t>
+          <t>QThA-UkVH</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MUE50996</t>
+          <t>MIJ60289</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>UIda-nQtd</t>
+          <t>YgVT-De6l</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MUX13896</t>
+          <t>MNW15780</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>r20R-BlFc</t>
+          <t>6iUB-Vag7</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MXC93247</t>
+          <t>MRQ02763</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>fcAI-rABo</t>
+          <t>jkZw-MaOb</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MXM72788</t>
+          <t>MUE50996</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>iRyF-IaTc</t>
+          <t>UIda-nQtd</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MYX47244</t>
+          <t>MUX13896</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>zpLV-zFXv</t>
+          <t>r20R-BlFc</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>NAQ63112</t>
+          <t>MXC93247</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>vedO-3joS</t>
+          <t>fcAI-rABo</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>NCL61296</t>
+          <t>MXM72788</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MTj9-lIY8</t>
+          <t>iRyF-IaTc</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>NDJ67099</t>
+          <t>MYX47244</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>hrBW-w842</t>
+          <t>zpLV-zFXv</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NLP67632</t>
+          <t>NAQ63112</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>b9F6-vbZ5</t>
+          <t>vedO-3joS</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>NPD00961</t>
+          <t>NCL61296</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>aI8u-zYiw</t>
+          <t>MTj9-lIY8</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>NUI19784</t>
+          <t>NDJ67099</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>mF1f-kCQW</t>
+          <t>hrBW-w842</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>NWX06153</t>
+          <t>NLP67632</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>N3G4-xe8w</t>
+          <t>b9F6-vbZ5</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>NYF03161</t>
+          <t>NPD00961</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>zMxQ-K0fi</t>
+          <t>aI8u-zYiw</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>NZW46214</t>
+          <t>NUI19784</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>09st-zHFg</t>
+          <t>mF1f-kCQW</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>NZZ50766</t>
+          <t>NWX06153</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>XINJ-KGsC</t>
+          <t>N3G4-xe8w</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>OBI75581</t>
+          <t>NYF03161</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Mygc-BSFY</t>
+          <t>zMxQ-K0fi</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>OKY47911</t>
+          <t>NZW46214</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>uSoZ-cHIn</t>
+          <t>09st-zHFg</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ORR85927</t>
+          <t>NZZ50766</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>JgtA-rF6p</t>
+          <t>XINJ-KGsC</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>ORT63362</t>
+          <t>OBI75581</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>XZT6-FxOF</t>
+          <t>Mygc-BSFY</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>OSB52441</t>
+          <t>OKY47911</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>I1Cv-DmRA</t>
+          <t>uSoZ-cHIn</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>OWR55957</t>
+          <t>ORR85927</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>5xs5-2GVm</t>
+          <t>JgtA-rF6p</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>OXE34055</t>
+          <t>ORT63362</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>QMAt-FrNE</t>
+          <t>XZT6-FxOF</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>OYK39161</t>
+          <t>OSB52441</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>nDoT-dKaH</t>
+          <t>I1Cv-DmRA</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>OYZ43696</t>
+          <t>OWR55957</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NE1A-0H4Y</t>
+          <t>5xs5-2GVm</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>PDL18808</t>
+          <t>OXE34055</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>AyIU-xTfq</t>
+          <t>QMAt-FrNE</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>PDY46515</t>
+          <t>OYK39161</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Gg8E-S2pr</t>
+          <t>nDoT-dKaH</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PEP57928</t>
+          <t>OYZ43696</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>o921-Slsb</t>
+          <t>NE1A-0H4Y</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PJT16152</t>
+          <t>PDL18808</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ExFD-xCid</t>
+          <t>AyIU-xTfq</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PLL97657</t>
+          <t>PDY46515</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>NWjX-D2LF</t>
+          <t>Gg8E-S2pr</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PVU41752</t>
+          <t>PEP57928</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ugqe-Crjb</t>
+          <t>o921-Slsb</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>QFN79396</t>
+          <t>PJT16152</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jXUf-ZSmc</t>
+          <t>ExFD-xCid</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>QFU06512</t>
+          <t>PLL97657</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>MNwE-V6p6</t>
+          <t>NWjX-D2LF</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>QHB18956</t>
+          <t>PVU41752</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>B4nt-rvpd</t>
+          <t>ugqe-Crjb</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>QRB56514</t>
+          <t>QFN79396</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ZmLU-WzDm</t>
+          <t>jXUf-ZSmc</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>QUE22078</t>
+          <t>QFU06512</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>tCyA-Oi7m</t>
+          <t>MNwE-V6p6</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>QYS77373</t>
+          <t>QHB18956</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>bdKc-q4v6</t>
+          <t>B4nt-rvpd</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>RBA20127</t>
+          <t>QRB56514</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>oE79-b1Se</t>
+          <t>ZmLU-WzDm</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>RLQ73857</t>
+          <t>QUE22078</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>QZVO-4p3B</t>
+          <t>tCyA-Oi7m</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>RNL06004</t>
+          <t>QYS77373</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>WaLc-sBJY</t>
+          <t>bdKc-q4v6</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>RSN71799</t>
+          <t>RBA20127</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>APKz-8tHA</t>
+          <t>oE79-b1Se</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>SAF98648</t>
+          <t>RLQ73857</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>JUDx-dQqy</t>
+          <t>QZVO-4p3B</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>SDE98641</t>
+          <t>RNL06004</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>E4LL-qV7u</t>
+          <t>WaLc-sBJY</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>SEV98034</t>
+          <t>RSN71799</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>3FMv-ztV8</t>
+          <t>APKz-8tHA</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SGE51092</t>
+          <t>SAF98648</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>9G7O-tS42</t>
+          <t>JUDx-dQqy</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SLP43775</t>
+          <t>SDE98641</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>JIk1-QTjm</t>
+          <t>E4LL-qV7u</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SMF79012</t>
+          <t>SEV98034</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>NcnL-Ufev</t>
+          <t>3FMv-ztV8</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SNZ44527</t>
+          <t>SGE51092</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Idtr-Ef1p</t>
+          <t>9G7O-tS42</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SPZ85652</t>
+          <t>SLP43775</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>BqNU-jKbs</t>
+          <t>JIk1-QTjm</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SQX65443</t>
+          <t>SMF79012</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>2Y2u-Iexu</t>
+          <t>NcnL-Ufev</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SSU10232</t>
+          <t>SNZ44527</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>2s1b-MrBM</t>
+          <t>Idtr-Ef1p</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SYH46751</t>
+          <t>SPZ85652</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>g47k-j3HG</t>
+          <t>BqNU-jKbs</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>TKW11810</t>
+          <t>SQX65443</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>XbfA-yocA</t>
+          <t>2Y2u-Iexu</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>TMJ36970</t>
+          <t>SSU10232</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>NiMt-vJm1</t>
+          <t>2s1b-MrBM</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TRC98148</t>
+          <t>SYH46751</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>ImK9-sJVr</t>
+          <t>g47k-j3HG</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>TTS04230</t>
+          <t>TKW11810</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>oJvJ-C0eE</t>
+          <t>XbfA-yocA</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>TXC42578</t>
+          <t>TMJ36970</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>ttrI-HkEA</t>
+          <t>NiMt-vJm1</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>UUR79971</t>
+          <t>TRC98148</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>2Vvw-yPgX</t>
+          <t>ImK9-sJVr</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>VDD06679</t>
+          <t>TTS04230</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>9NFD-F33z</t>
+          <t>oJvJ-C0eE</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>VEQ81429</t>
+          <t>TXC42578</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>xnGV-gtxP</t>
+          <t>ttrI-HkEA</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>VPE32737</t>
+          <t>UUR79971</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>83SX-bO49</t>
+          <t>2Vvw-yPgX</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>WJH36041</t>
+          <t>VDD06679</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>yPk4-9kvI</t>
+          <t>9NFD-F33z</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>WNA57398</t>
+          <t>VEQ81429</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>CU9v-k8Hc</t>
+          <t>xnGV-gtxP</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>WUA13603</t>
+          <t>VPE32737</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>hdCj-fLq2</t>
+          <t>83SX-bO49</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>WUH93925</t>
+          <t>WEO81262</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>8m3J-Gzlk</t>
+          <t>L7ui-NKjF</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>WWS24235</t>
+          <t>WJH36041</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>dTMF-Ocal</t>
+          <t>yPk4-9kvI</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>XKS75480</t>
+          <t>WNA57398</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>c0hS-CdvD</t>
+          <t>CU9v-k8Hc</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>XOA75961</t>
+          <t>WUA13603</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>VRah-kBaa</t>
+          <t>hdCj-fLq2</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>XYT33259</t>
+          <t>WUH93925</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ahUH-85T2</t>
+          <t>8m3J-Gzlk</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>XYZ70850</t>
+          <t>WWS24235</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>jdV6-HalU</t>
+          <t>dTMF-Ocal</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>YBX87679</t>
+          <t>XKS75480</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>442D-goVh</t>
+          <t>c0hS-CdvD</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>YCN31679</t>
+          <t>XOA75961</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>SBfE-010a</t>
+          <t>VRah-kBaa</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>YFU10307</t>
+          <t>XYT33259</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>pv8C-S2qP</t>
+          <t>ahUH-85T2</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>YGP30798</t>
+          <t>XYZ70850</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>dZEv-nHKw</t>
+          <t>jdV6-HalU</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>YHZ51082</t>
+          <t>YBX87679</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>7j63-7HKa</t>
+          <t>442D-goVh</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>YOT12953</t>
+          <t>YCN31679</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SxGc-ZaIN</t>
+          <t>SBfE-010a</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>ZAM21080</t>
+          <t>YFU10307</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>COFy-pMla</t>
+          <t>pv8C-S2qP</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ZHU54125</t>
+          <t>YGP30798</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>5RJe-0r17</t>
+          <t>dZEv-nHKw</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ZLP77106</t>
+          <t>YHZ51082</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>djSn-TgS9</t>
+          <t>7j63-7HKa</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>ZNA23106</t>
+          <t>YOT12953</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SHid-kPC3</t>
+          <t>SxGc-ZaIN</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ZSU27095</t>
+          <t>ZAM21080</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>3TQp-7e2s</t>
+          <t>COFy-pMla</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
+          <t>ZHU54125</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>5RJe-0r17</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>ZLP77106</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>djSn-TgS9</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>ZNA23106</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>SHid-kPC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>ZSU27095</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>3TQp-7e2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
           <t>ZVK04224</t>
         </is>
       </c>
-      <c r="B187" t="inlineStr">
+      <c r="B191" t="inlineStr">
         <is>
           <t>9gaA-gLOl</t>
         </is>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B191"/>
+  <dimension ref="A1:B192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2495,226 +2495,238 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>WUA13603</t>
+          <t>WQS25133</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>hdCj-fLq2</t>
+          <t>Mg1K-yzvr</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>WUH93925</t>
+          <t>WUA13603</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>8m3J-Gzlk</t>
+          <t>hdCj-fLq2</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>WWS24235</t>
+          <t>WUH93925</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>dTMF-Ocal</t>
+          <t>8m3J-Gzlk</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>XKS75480</t>
+          <t>WWS24235</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>c0hS-CdvD</t>
+          <t>dTMF-Ocal</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>XOA75961</t>
+          <t>XKS75480</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>VRah-kBaa</t>
+          <t>c0hS-CdvD</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>XYT33259</t>
+          <t>XOA75961</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ahUH-85T2</t>
+          <t>VRah-kBaa</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>XYZ70850</t>
+          <t>XYT33259</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>jdV6-HalU</t>
+          <t>ahUH-85T2</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>YBX87679</t>
+          <t>XYZ70850</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>442D-goVh</t>
+          <t>jdV6-HalU</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>YCN31679</t>
+          <t>YBX87679</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SBfE-010a</t>
+          <t>442D-goVh</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>YFU10307</t>
+          <t>YCN31679</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>pv8C-S2qP</t>
+          <t>SBfE-010a</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>YGP30798</t>
+          <t>YFU10307</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>dZEv-nHKw</t>
+          <t>pv8C-S2qP</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>YHZ51082</t>
+          <t>YGP30798</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>7j63-7HKa</t>
+          <t>dZEv-nHKw</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>YOT12953</t>
+          <t>YHZ51082</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>SxGc-ZaIN</t>
+          <t>7j63-7HKa</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>ZAM21080</t>
+          <t>YOT12953</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>COFy-pMla</t>
+          <t>SxGc-ZaIN</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ZHU54125</t>
+          <t>ZAM21080</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>5RJe-0r17</t>
+          <t>COFy-pMla</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ZLP77106</t>
+          <t>ZHU54125</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>djSn-TgS9</t>
+          <t>5RJe-0r17</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ZNA23106</t>
+          <t>ZLP77106</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>SHid-kPC3</t>
+          <t>djSn-TgS9</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ZSU27095</t>
+          <t>ZNA23106</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>3TQp-7e2s</t>
+          <t>SHid-kPC3</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
+          <t>ZSU27095</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>3TQp-7e2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
           <t>ZVK04224</t>
         </is>
       </c>
-      <c r="B191" t="inlineStr">
+      <c r="B192" t="inlineStr">
         <is>
           <t>9gaA-gLOl</t>
         </is>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B192"/>
+  <dimension ref="A1:B193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2567,166 +2567,178 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>XYT33259</t>
+          <t>XRM79618</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ahUH-85T2</t>
+          <t>brgl-xEFq</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>XYZ70850</t>
+          <t>XYT33259</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>jdV6-HalU</t>
+          <t>ahUH-85T2</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>YBX87679</t>
+          <t>XYZ70850</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>442D-goVh</t>
+          <t>jdV6-HalU</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>YCN31679</t>
+          <t>YBX87679</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>SBfE-010a</t>
+          <t>442D-goVh</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>YFU10307</t>
+          <t>YCN31679</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>pv8C-S2qP</t>
+          <t>SBfE-010a</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>YGP30798</t>
+          <t>YFU10307</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>dZEv-nHKw</t>
+          <t>pv8C-S2qP</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>YHZ51082</t>
+          <t>YGP30798</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>7j63-7HKa</t>
+          <t>dZEv-nHKw</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>YOT12953</t>
+          <t>YHZ51082</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>SxGc-ZaIN</t>
+          <t>7j63-7HKa</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ZAM21080</t>
+          <t>YOT12953</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>COFy-pMla</t>
+          <t>SxGc-ZaIN</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ZHU54125</t>
+          <t>ZAM21080</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>5RJe-0r17</t>
+          <t>COFy-pMla</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ZLP77106</t>
+          <t>ZHU54125</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>djSn-TgS9</t>
+          <t>5RJe-0r17</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ZNA23106</t>
+          <t>ZLP77106</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>SHid-kPC3</t>
+          <t>djSn-TgS9</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ZSU27095</t>
+          <t>ZNA23106</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>3TQp-7e2s</t>
+          <t>SHid-kPC3</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
+          <t>ZSU27095</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>3TQp-7e2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
           <t>ZVK04224</t>
         </is>
       </c>
-      <c r="B192" t="inlineStr">
+      <c r="B193" t="inlineStr">
         <is>
           <t>9gaA-gLOl</t>
         </is>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B193"/>
+  <dimension ref="A1:B194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1835,910 +1835,922 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>NLP67632</t>
+          <t>NEE79704</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>b9F6-vbZ5</t>
+          <t>ed0x-qxBt</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>NPD00961</t>
+          <t>NLP67632</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>aI8u-zYiw</t>
+          <t>b9F6-vbZ5</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>NUI19784</t>
+          <t>NPD00961</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>mF1f-kCQW</t>
+          <t>aI8u-zYiw</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>NWX06153</t>
+          <t>NUI19784</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>N3G4-xe8w</t>
+          <t>mF1f-kCQW</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>NYF03161</t>
+          <t>NWX06153</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>zMxQ-K0fi</t>
+          <t>N3G4-xe8w</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>NZW46214</t>
+          <t>NYF03161</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>09st-zHFg</t>
+          <t>zMxQ-K0fi</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>NZZ50766</t>
+          <t>NZW46214</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>XINJ-KGsC</t>
+          <t>09st-zHFg</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>OBI75581</t>
+          <t>NZZ50766</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Mygc-BSFY</t>
+          <t>XINJ-KGsC</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>OKY47911</t>
+          <t>OBI75581</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>uSoZ-cHIn</t>
+          <t>Mygc-BSFY</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>ORR85927</t>
+          <t>OKY47911</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>JgtA-rF6p</t>
+          <t>uSoZ-cHIn</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ORT63362</t>
+          <t>ORR85927</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>XZT6-FxOF</t>
+          <t>JgtA-rF6p</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>OSB52441</t>
+          <t>ORT63362</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>I1Cv-DmRA</t>
+          <t>XZT6-FxOF</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>OWR55957</t>
+          <t>OSB52441</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5xs5-2GVm</t>
+          <t>I1Cv-DmRA</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>OXE34055</t>
+          <t>OWR55957</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>QMAt-FrNE</t>
+          <t>5xs5-2GVm</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>OYK39161</t>
+          <t>OXE34055</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>nDoT-dKaH</t>
+          <t>QMAt-FrNE</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>OYZ43696</t>
+          <t>OYK39161</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>NE1A-0H4Y</t>
+          <t>nDoT-dKaH</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>PDL18808</t>
+          <t>OYZ43696</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>AyIU-xTfq</t>
+          <t>NE1A-0H4Y</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PDY46515</t>
+          <t>PDL18808</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Gg8E-S2pr</t>
+          <t>AyIU-xTfq</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PEP57928</t>
+          <t>PDY46515</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>o921-Slsb</t>
+          <t>Gg8E-S2pr</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PJT16152</t>
+          <t>PEP57928</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ExFD-xCid</t>
+          <t>o921-Slsb</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PLL97657</t>
+          <t>PJT16152</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>NWjX-D2LF</t>
+          <t>ExFD-xCid</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PVU41752</t>
+          <t>PLL97657</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>ugqe-Crjb</t>
+          <t>NWjX-D2LF</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>QFN79396</t>
+          <t>PVU41752</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>jXUf-ZSmc</t>
+          <t>ugqe-Crjb</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>QFU06512</t>
+          <t>QFN79396</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>MNwE-V6p6</t>
+          <t>jXUf-ZSmc</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>QHB18956</t>
+          <t>QFU06512</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>B4nt-rvpd</t>
+          <t>MNwE-V6p6</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>QRB56514</t>
+          <t>QHB18956</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>ZmLU-WzDm</t>
+          <t>B4nt-rvpd</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>QUE22078</t>
+          <t>QRB56514</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>tCyA-Oi7m</t>
+          <t>ZmLU-WzDm</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>QYS77373</t>
+          <t>QUE22078</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>bdKc-q4v6</t>
+          <t>tCyA-Oi7m</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>RBA20127</t>
+          <t>QYS77373</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>oE79-b1Se</t>
+          <t>bdKc-q4v6</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>RLQ73857</t>
+          <t>RBA20127</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>QZVO-4p3B</t>
+          <t>oE79-b1Se</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RNL06004</t>
+          <t>RLQ73857</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>WaLc-sBJY</t>
+          <t>QZVO-4p3B</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>RSN71799</t>
+          <t>RNL06004</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>APKz-8tHA</t>
+          <t>WaLc-sBJY</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>SAF98648</t>
+          <t>RSN71799</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>JUDx-dQqy</t>
+          <t>APKz-8tHA</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SDE98641</t>
+          <t>SAF98648</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>E4LL-qV7u</t>
+          <t>JUDx-dQqy</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SEV98034</t>
+          <t>SDE98641</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>3FMv-ztV8</t>
+          <t>E4LL-qV7u</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SGE51092</t>
+          <t>SEV98034</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>9G7O-tS42</t>
+          <t>3FMv-ztV8</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SLP43775</t>
+          <t>SGE51092</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>JIk1-QTjm</t>
+          <t>9G7O-tS42</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SMF79012</t>
+          <t>SLP43775</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>NcnL-Ufev</t>
+          <t>JIk1-QTjm</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SNZ44527</t>
+          <t>SMF79012</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Idtr-Ef1p</t>
+          <t>NcnL-Ufev</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SPZ85652</t>
+          <t>SNZ44527</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>BqNU-jKbs</t>
+          <t>Idtr-Ef1p</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SQX65443</t>
+          <t>SPZ85652</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>2Y2u-Iexu</t>
+          <t>BqNU-jKbs</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SSU10232</t>
+          <t>SQX65443</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2s1b-MrBM</t>
+          <t>2Y2u-Iexu</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SYH46751</t>
+          <t>SSU10232</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>g47k-j3HG</t>
+          <t>2s1b-MrBM</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>TKW11810</t>
+          <t>SYH46751</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>XbfA-yocA</t>
+          <t>g47k-j3HG</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>TMJ36970</t>
+          <t>TKW11810</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NiMt-vJm1</t>
+          <t>XbfA-yocA</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TRC98148</t>
+          <t>TMJ36970</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>ImK9-sJVr</t>
+          <t>NiMt-vJm1</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TTS04230</t>
+          <t>TRC98148</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>oJvJ-C0eE</t>
+          <t>ImK9-sJVr</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TXC42578</t>
+          <t>TTS04230</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>ttrI-HkEA</t>
+          <t>oJvJ-C0eE</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>UUR79971</t>
+          <t>TXC42578</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>2Vvw-yPgX</t>
+          <t>ttrI-HkEA</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>VDD06679</t>
+          <t>UUR79971</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>9NFD-F33z</t>
+          <t>2Vvw-yPgX</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>VEQ81429</t>
+          <t>VDD06679</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>xnGV-gtxP</t>
+          <t>9NFD-F33z</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>VPE32737</t>
+          <t>VEQ81429</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>83SX-bO49</t>
+          <t>xnGV-gtxP</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>WEO81262</t>
+          <t>VPE32737</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>L7ui-NKjF</t>
+          <t>83SX-bO49</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>WJH36041</t>
+          <t>WEO81262</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>yPk4-9kvI</t>
+          <t>L7ui-NKjF</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>WNA57398</t>
+          <t>WJH36041</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>CU9v-k8Hc</t>
+          <t>yPk4-9kvI</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>WQS25133</t>
+          <t>WNA57398</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Mg1K-yzvr</t>
+          <t>CU9v-k8Hc</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>WUA13603</t>
+          <t>WQS25133</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>hdCj-fLq2</t>
+          <t>Mg1K-yzvr</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>WUH93925</t>
+          <t>WUA13603</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>8m3J-Gzlk</t>
+          <t>hdCj-fLq2</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>WWS24235</t>
+          <t>WUH93925</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>dTMF-Ocal</t>
+          <t>8m3J-Gzlk</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>XKS75480</t>
+          <t>WWS24235</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>c0hS-CdvD</t>
+          <t>dTMF-Ocal</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>XOA75961</t>
+          <t>XKS75480</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>VRah-kBaa</t>
+          <t>c0hS-CdvD</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>XRM79618</t>
+          <t>XOA75961</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>brgl-xEFq</t>
+          <t>VRah-kBaa</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>XYT33259</t>
+          <t>XRM79618</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ahUH-85T2</t>
+          <t>brgl-xEFq</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>XYZ70850</t>
+          <t>XYT33259</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>jdV6-HalU</t>
+          <t>ahUH-85T2</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>YBX87679</t>
+          <t>XYZ70850</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>442D-goVh</t>
+          <t>jdV6-HalU</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>YCN31679</t>
+          <t>YBX87679</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>SBfE-010a</t>
+          <t>442D-goVh</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>YFU10307</t>
+          <t>YCN31679</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>pv8C-S2qP</t>
+          <t>SBfE-010a</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>YGP30798</t>
+          <t>YFU10307</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>dZEv-nHKw</t>
+          <t>pv8C-S2qP</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>YHZ51082</t>
+          <t>YGP30798</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>7j63-7HKa</t>
+          <t>dZEv-nHKw</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>YOT12953</t>
+          <t>YHZ51082</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>SxGc-ZaIN</t>
+          <t>7j63-7HKa</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>ZAM21080</t>
+          <t>YOT12953</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>COFy-pMla</t>
+          <t>SxGc-ZaIN</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ZHU54125</t>
+          <t>ZAM21080</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>5RJe-0r17</t>
+          <t>COFy-pMla</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ZLP77106</t>
+          <t>ZHU54125</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>djSn-TgS9</t>
+          <t>5RJe-0r17</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ZNA23106</t>
+          <t>ZLP77106</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>SHid-kPC3</t>
+          <t>djSn-TgS9</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ZSU27095</t>
+          <t>ZNA23106</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>3TQp-7e2s</t>
+          <t>SHid-kPC3</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
+          <t>ZSU27095</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>3TQp-7e2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
           <t>ZVK04224</t>
         </is>
       </c>
-      <c r="B193" t="inlineStr">
+      <c r="B194" t="inlineStr">
         <is>
           <t>9gaA-gLOl</t>
         </is>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B194"/>
+  <dimension ref="A1:B261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,2302 +455,3106 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADC47471</t>
+          <t>ACP59950</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>bQGY-vJlV</t>
+          <t>zccK-zlnr</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AEF48923</t>
+          <t>ADC47471</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>zzMB-6A6j</t>
+          <t>bQGY-vJlV</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AJF14211</t>
+          <t>AEF48923</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CM6y-aUuk</t>
+          <t>zzMB-6A6j</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMX72670</t>
+          <t>AJF14211</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VEGx-hurW</t>
+          <t>CM6y-aUuk</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARC48959</t>
+          <t>AMX72670</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CK7z-JVnw</t>
+          <t>VEGx-hurW</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AVJ39759</t>
+          <t>ANW71835</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>utY7-yET8</t>
+          <t>BuMC-7KDd</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AXM21790</t>
+          <t>ARC48959</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>awKz-Dbz4</t>
+          <t>CK7z-JVnw</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AZJ82844</t>
+          <t>ARL55178</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>G2cX-0SFe</t>
+          <t>VwlE-Pvk6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>AVJ39759</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A1234</t>
+          <t>utY7-yET8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BBA65823</t>
+          <t>AXM21790</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>8InB-77sx</t>
+          <t>awKz-Dbz4</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BFI60670</t>
+          <t>AZJ82844</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>iOpa-quCx</t>
+          <t>G2cX-0SFe</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BGG58729</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3RgL-WsLQ</t>
+          <t>A1234</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BJH88419</t>
+          <t>BBA65823</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JwOH-onjo</t>
+          <t>8InB-77sx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BOZ64205</t>
+          <t>BFI60670</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Cqic-pxFH</t>
+          <t>iOpa-quCx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BUR49898</t>
+          <t>BGG58729</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>uP55-nNU2</t>
+          <t>3RgL-WsLQ</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CBP36635</t>
+          <t>BJH88419</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3o0E-H0eS</t>
+          <t>JwOH-onjo</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CEG78579</t>
+          <t>BJW79616</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>oGuY-hS6y</t>
+          <t>qjD9-x9pp</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CEV66266</t>
+          <t>BOI99795</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>595F-5DPV</t>
+          <t>cUwY-oMGA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CEX73283</t>
+          <t>BOZ64205</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BvrE-h4h6</t>
+          <t>Cqic-pxFH</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CGY86131</t>
+          <t>BQV35355</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5EJ5-nSOu</t>
+          <t>AMpg-NzcS</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CHZ14322</t>
+          <t>BUR49898</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>rJ50-xReo</t>
+          <t>uP55-nNU2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CNJ73848</t>
+          <t>CBP36635</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>uyHI-dehW</t>
+          <t>3o0E-H0eS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CNQ05106</t>
+          <t>CDG44201</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>JKLS-ZXPj</t>
+          <t>Z9V4-FCw2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CQL05471</t>
+          <t>CEG78579</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>k8LF-oP5k</t>
+          <t>oGuY-hS6y</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CWI21231</t>
+          <t>CEV66266</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>VERb-T6sQ</t>
+          <t>595F-5DPV</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CXY21844</t>
+          <t>CEX73283</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nAFY-KtfZ</t>
+          <t>BvrE-h4h6</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CYB55817</t>
+          <t>CGK70284</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>kyA4-BHSa</t>
+          <t>cgTX-Z1ru</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CYN09662</t>
+          <t>CGY86131</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>unqS-753q</t>
+          <t>5EJ5-nSOu</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>DCC25940</t>
+          <t>CHZ14322</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>9X56-vHTG</t>
+          <t>rJ50-xReo</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DGL58063</t>
+          <t>CMY62163</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>lQpJ-cvmL</t>
+          <t>X7qM-afE3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DHH79187</t>
+          <t>CNJ73848</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>kp6O-nXp3</t>
+          <t>uyHI-dehW</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DJK20638</t>
+          <t>CNQ05106</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ZJAv-brF5</t>
+          <t>JKLS-ZXPj</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>DLP45053</t>
+          <t>CQL05471</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>L7sf-MoLb</t>
+          <t>k8LF-oP5k</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>DQD33133</t>
+          <t>CQV21480</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>WX5H-LiPX</t>
+          <t>fPzD-uk5D</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>DTZ69845</t>
+          <t>CST44061</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FiA8-mFOt</t>
+          <t>1Xg7-FxRM</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DVJ66295</t>
+          <t>CWI21231</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8Bl3-qRML</t>
+          <t>VERb-T6sQ</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DZI77349</t>
+          <t>CWI74996</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>exKl-ZgTI</t>
+          <t>iP3y-7uci</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>EBT22822</t>
+          <t>CXY21844</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2lhq-XPz5</t>
+          <t>nAFY-KtfZ</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EWP70521</t>
+          <t>CYB55817</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>sAoe-qfVx</t>
+          <t>kyA4-BHSa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EYO38305</t>
+          <t>CYN09662</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>qbbV-unNd</t>
+          <t>unqS-753q</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FLQ72134</t>
+          <t>DCC25940</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Oj7z-iK7O</t>
+          <t>9X56-vHTG</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>FNU34959</t>
+          <t>DGL58063</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>6Rb4-9itD</t>
+          <t>lQpJ-cvmL</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>FOJ78948</t>
+          <t>DHH79187</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>z4ZP-wYr2</t>
+          <t>kp6O-nXp3</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>FQP62630</t>
+          <t>DJK20638</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>YPWV-F4Jw</t>
+          <t>ZJAv-brF5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>FRS19080</t>
+          <t>DLF24523</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8lEh-Ggjd</t>
+          <t>1Fps-H1ZW</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FUSURIN1</t>
+          <t>DLP45053</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>sQd2-HCth</t>
+          <t>L7sf-MoLb</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>FWZ82980</t>
+          <t>DQD33133</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Km0s-i1f3</t>
+          <t>WX5H-LiPX</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>FXB60927</t>
+          <t>DTZ69845</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>d20X-vLsV</t>
+          <t>FiA8-mFOt</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GCV61524</t>
+          <t>DUA61401</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Xhaf-F9mT</t>
+          <t>2vrj-OFZH</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>GEL08954</t>
+          <t>DVJ66295</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>zqti-TUKL</t>
+          <t>8Bl3-qRML</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>GEP48591</t>
+          <t>DXM69578</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ipb2-EtbP</t>
+          <t>gt5b-TF6d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>GFN61654</t>
+          <t>DZI77349</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nOpR-i46M</t>
+          <t>exKl-ZgTI</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>GIE22684</t>
+          <t>EBT22822</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>7YFY-lEPW</t>
+          <t>2lhq-XPz5</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>GKE90115</t>
+          <t>ECG95521</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZK3R-ekIU</t>
+          <t>weWw-hC7q</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>GLG55164</t>
+          <t>EWP70521</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>rMri-gCbQ</t>
+          <t>sAoe-qfVx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>GQG06884</t>
+          <t>EYO38305</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>yZSK-Cyby</t>
+          <t>qbbV-unNd</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>GSJ38697</t>
+          <t>FJV52310</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>dcc9-1DuY</t>
+          <t>LbRC-0Q2b</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GSY94523</t>
+          <t>FLQ72134</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CykC-fp9I</t>
+          <t>Oj7z-iK7O</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GVM53776</t>
+          <t>FNU34959</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>IUZs-UrSU</t>
+          <t>6Rb4-9itD</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>HBP33017</t>
+          <t>FOE41721</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>D3ly-X1Qr</t>
+          <t>SS6s-F64h</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>HNS34640</t>
+          <t>FOJ78948</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>dPb1-DHLF</t>
+          <t>z4ZP-wYr2</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HPT02640</t>
+          <t>FQP62630</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>c2kk-PGg8</t>
+          <t>YPWV-F4Jw</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HQH08532</t>
+          <t>FRS19080</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0fh0-QX5H</t>
+          <t>8lEh-Ggjd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HRY29891</t>
+          <t>FUSURIN1</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>UjZ9-SZGT</t>
+          <t>sQd2-HCth</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HWP25524</t>
+          <t>FVJ14662</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BWy7-13Ec</t>
+          <t>Jr5l-rtxM</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IAE88291</t>
+          <t>FWZ82980</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>4Ceg-RIv5</t>
+          <t>Km0s-i1f3</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IGN23276</t>
+          <t>FXB60927</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ZKGo-6azn</t>
+          <t>d20X-vLsV</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IGX57659</t>
+          <t>FXU60367</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>F8R5-Mhli</t>
+          <t>5JuP-8bMA</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ILO34901</t>
+          <t>GBS06994</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VPO5-2Unw</t>
+          <t>SpZ6-7ylH</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>IMW07942</t>
+          <t>GCV61524</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ors6-bajw</t>
+          <t>Xhaf-F9mT</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IQI33918</t>
+          <t>GEL08954</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>quU8-kFRw</t>
+          <t>zqti-TUKL</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>IUU53315</t>
+          <t>GEP48591</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>bHGN-Gt9k</t>
+          <t>ipb2-EtbP</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>IWX83001</t>
+          <t>GFN61654</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0hfb-VytH</t>
+          <t>nOpR-i46M</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>JJI69427</t>
+          <t>GIE22684</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mcpe-MdKl</t>
+          <t>7YFY-lEPW</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>JMV12916</t>
+          <t>GKE90115</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>wFYF-qjdW</t>
+          <t>ZK3R-ekIU</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>JNQ15800</t>
+          <t>GLG55164</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>UOVA-N6XO</t>
+          <t>rMri-gCbQ</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>JSH83558</t>
+          <t>GQG06884</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>NUAZ-lHPu</t>
+          <t>yZSK-Cyby</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>JSO81414</t>
+          <t>GSJ38697</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2SfQ-XyEl</t>
+          <t>dcc9-1DuY</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>JTN17189</t>
+          <t>GSY94523</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>wg9A-To8N</t>
+          <t>CykC-fp9I</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>JTQ20003</t>
+          <t>GVD45273</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>xXs3-0q1q</t>
+          <t>kljF-Ogjz</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>KCH53154</t>
+          <t>GVM53776</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>RwJm-IF1y</t>
+          <t>IUZs-UrSU</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>KCH80368</t>
+          <t>HBP33017</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>j6lG-9k2c</t>
+          <t>D3ly-X1Qr</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>KCS62207</t>
+          <t>HFX34792</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ge7V-N1Fb</t>
+          <t>gRZr-rn3f</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>KNB79119</t>
+          <t>HMD58733</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>BRVy-AfTK</t>
+          <t>jr4r-HFVO</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>KPJ23941</t>
+          <t>HNS34640</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>qcjI-pNgm</t>
+          <t>dPb1-DHLF</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>KQT40874</t>
+          <t>HPT02640</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>sgUM-aaYM</t>
+          <t>c2kk-PGg8</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>KRH18822</t>
+          <t>HQH08532</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>vMtE-4cYL</t>
+          <t>0fh0-QX5H</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>KTK81122</t>
+          <t>HRY29891</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>X8Dz-iKF1</t>
+          <t>UjZ9-SZGT</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>KVA96952</t>
+          <t>HTN73978</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>VuFC-8E26</t>
+          <t>XTGO-sHtm</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>KVU62139</t>
+          <t>HWP25524</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>LUI5-Geov</t>
+          <t>BWy7-13Ec</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>KWN66857</t>
+          <t>IAE88291</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Fv4Y-68ZM</t>
+          <t>4Ceg-RIv5</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>KXZ79956</t>
+          <t>IFQ76747</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>xmdQ-yw08</t>
+          <t>3Rh9-wgj4</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>KZL99357</t>
+          <t>IGN23276</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>14ZB-xFwZ</t>
+          <t>ZKGo-6azn</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>KZU53477</t>
+          <t>IGX57659</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1qwx-jHLR</t>
+          <t>F8R5-Mhli</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>LFA56301</t>
+          <t>ILO34901</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>trbu-XQWz</t>
+          <t>VPO5-2Unw</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>LGP73888</t>
+          <t>IMW07942</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DcIT-TKtd</t>
+          <t>ors6-bajw</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LHQ57930</t>
+          <t>IQI33918</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>cRpb-1kZX</t>
+          <t>quU8-kFRw</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>LJE73544</t>
+          <t>IUU53315</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>c8yU-Zgju</t>
+          <t>bHGN-Gt9k</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>LKG10504</t>
+          <t>IWX83001</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>t6Zj-7N4q</t>
+          <t>0hfb-VytH</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>LLI56060</t>
+          <t>JJI69427</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ePiy-wSTy</t>
+          <t>Mcpe-MdKl</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>LPM87075</t>
+          <t>JMV12916</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>AgXC-arDZ</t>
+          <t>wFYF-qjdW</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>MAI64055</t>
+          <t>JNQ15800</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Mzqj-Ky8q</t>
+          <t>UOVA-N6XO</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MDE12029</t>
+          <t>JSH83558</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>hhXj-vBGM</t>
+          <t>NUAZ-lHPu</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>MEG11153</t>
+          <t>JSO81414</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>QThA-UkVH</t>
+          <t>2SfQ-XyEl</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>MIJ60289</t>
+          <t>JTN17189</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>YgVT-De6l</t>
+          <t>wg9A-To8N</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>MNW15780</t>
+          <t>JTQ20003</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>6iUB-Vag7</t>
+          <t>xXs3-0q1q</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>MRQ02763</t>
+          <t>KCH53154</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>jkZw-MaOb</t>
+          <t>RwJm-IF1y</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>MUE50996</t>
+          <t>KCH80368</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>UIda-nQtd</t>
+          <t>j6lG-9k2c</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>MUX13896</t>
+          <t>KCS62207</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>r20R-BlFc</t>
+          <t>Ge7V-N1Fb</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>MXC93247</t>
+          <t>KNB79119</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>fcAI-rABo</t>
+          <t>BRVy-AfTK</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>MXM72788</t>
+          <t>KPJ23941</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>iRyF-IaTc</t>
+          <t>qcjI-pNgm</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>MYX47244</t>
+          <t>KQT40874</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>zpLV-zFXv</t>
+          <t>sgUM-aaYM</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>NAQ63112</t>
+          <t>KRH18822</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>vedO-3joS</t>
+          <t>vMtE-4cYL</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>NCL61296</t>
+          <t>KTK81122</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>MTj9-lIY8</t>
+          <t>X8Dz-iKF1</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>NDJ67099</t>
+          <t>KVA96952</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>hrBW-w842</t>
+          <t>VuFC-8E26</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>NEE79704</t>
+          <t>KVU62139</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ed0x-qxBt</t>
+          <t>LUI5-Geov</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>NLP67632</t>
+          <t>KWN66857</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>b9F6-vbZ5</t>
+          <t>Fv4Y-68ZM</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>NPD00961</t>
+          <t>KXZ79956</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>aI8u-zYiw</t>
+          <t>xmdQ-yw08</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>NUI19784</t>
+          <t>KZL99357</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>mF1f-kCQW</t>
+          <t>14ZB-xFwZ</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>NWX06153</t>
+          <t>KZU53477</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>N3G4-xe8w</t>
+          <t>1qwx-jHLR</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>NYF03161</t>
+          <t>LCT57577</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>zMxQ-K0fi</t>
+          <t>bZjA-qnuE</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>NZW46214</t>
+          <t>LFA56301</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>09st-zHFg</t>
+          <t>trbu-XQWz</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>NZZ50766</t>
+          <t>LGP73888</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>XINJ-KGsC</t>
+          <t>DcIT-TKtd</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>OBI75581</t>
+          <t>LHQ57930</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Mygc-BSFY</t>
+          <t>cRpb-1kZX</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>OKY47911</t>
+          <t>LJE73544</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>uSoZ-cHIn</t>
+          <t>c8yU-Zgju</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>ORR85927</t>
+          <t>LKG10504</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>JgtA-rF6p</t>
+          <t>t6Zj-7N4q</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>ORT63362</t>
+          <t>LLI56060</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>XZT6-FxOF</t>
+          <t>ePiy-wSTy</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>OSB52441</t>
+          <t>LPM87075</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>I1Cv-DmRA</t>
+          <t>AgXC-arDZ</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>OWR55957</t>
+          <t>MAI64055</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5xs5-2GVm</t>
+          <t>Mzqj-Ky8q</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>OXE34055</t>
+          <t>MDE12029</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>QMAt-FrNE</t>
+          <t>hhXj-vBGM</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>OYK39161</t>
+          <t>MEG11153</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>nDoT-dKaH</t>
+          <t>QThA-UkVH</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>OYZ43696</t>
+          <t>MIJ60289</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>NE1A-0H4Y</t>
+          <t>YgVT-De6l</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>PDL18808</t>
+          <t>MNW15780</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>AyIU-xTfq</t>
+          <t>6iUB-Vag7</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>PDY46515</t>
+          <t>MRQ02763</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Gg8E-S2pr</t>
+          <t>jkZw-MaOb</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>PEP57928</t>
+          <t>MUE50996</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>o921-Slsb</t>
+          <t>UIda-nQtd</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>PJT16152</t>
+          <t>MUX13896</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ExFD-xCid</t>
+          <t>r20R-BlFc</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>PLL97657</t>
+          <t>MXC93247</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>NWjX-D2LF</t>
+          <t>fcAI-rABo</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>PVU41752</t>
+          <t>MXM72788</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ugqe-Crjb</t>
+          <t>iRyF-IaTc</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>QFN79396</t>
+          <t>MYD82527</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>jXUf-ZSmc</t>
+          <t>1z7Z-Iwsk</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>QFU06512</t>
+          <t>MYX47244</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>MNwE-V6p6</t>
+          <t>zpLV-zFXv</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>QHB18956</t>
+          <t>NAQ63112</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>B4nt-rvpd</t>
+          <t>vedO-3joS</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>QRB56514</t>
+          <t>NCL61296</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ZmLU-WzDm</t>
+          <t>MTj9-lIY8</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>QUE22078</t>
+          <t>NDJ67099</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>tCyA-Oi7m</t>
+          <t>hrBW-w842</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>QYS77373</t>
+          <t>NEE79704</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>bdKc-q4v6</t>
+          <t>ed0x-qxBt</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>RBA20127</t>
+          <t>NIQ43372</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>oE79-b1Se</t>
+          <t>CXS1-PyNb</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>RLQ73857</t>
+          <t>NLP67632</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>QZVO-4p3B</t>
+          <t>b9F6-vbZ5</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>RNL06004</t>
+          <t>NPD00961</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>WaLc-sBJY</t>
+          <t>aI8u-zYiw</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>RSN71799</t>
+          <t>NUI19784</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>APKz-8tHA</t>
+          <t>mF1f-kCQW</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>SAF98648</t>
+          <t>NWX06153</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>JUDx-dQqy</t>
+          <t>N3G4-xe8w</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>SDE98641</t>
+          <t>NYF03161</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>E4LL-qV7u</t>
+          <t>zMxQ-K0fi</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>SEV98034</t>
+          <t>NZW46214</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>3FMv-ztV8</t>
+          <t>09st-zHFg</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>SGE51092</t>
+          <t>NZZ50766</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>9G7O-tS42</t>
+          <t>XINJ-KGsC</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>SLP43775</t>
+          <t>OAM83746</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>JIk1-QTjm</t>
+          <t>56vK-YHjW</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>SMF79012</t>
+          <t>OBI75581</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>NcnL-Ufev</t>
+          <t>Mygc-BSFY</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SNZ44527</t>
+          <t>ODU01918</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Idtr-Ef1p</t>
+          <t>ia7S-FLGr</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SPZ85652</t>
+          <t>OEJ86175</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>BqNU-jKbs</t>
+          <t>XJIi-fHfZ</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>SQX65443</t>
+          <t>OKY47911</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>2Y2u-Iexu</t>
+          <t>uSoZ-cHIn</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SSU10232</t>
+          <t>ORR85927</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>2s1b-MrBM</t>
+          <t>JgtA-rF6p</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>SYH46751</t>
+          <t>ORT63362</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>g47k-j3HG</t>
+          <t>XZT6-FxOF</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>TKW11810</t>
+          <t>OSB52441</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>XbfA-yocA</t>
+          <t>I1Cv-DmRA</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>TMJ36970</t>
+          <t>OWO93746</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>NiMt-vJm1</t>
+          <t>hGwl-3fWL</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>TRC98148</t>
+          <t>OWR55957</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>ImK9-sJVr</t>
+          <t>5xs5-2GVm</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>TTS04230</t>
+          <t>OXE34055</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>oJvJ-C0eE</t>
+          <t>QMAt-FrNE</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>TXC42578</t>
+          <t>OXH82758</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>ttrI-HkEA</t>
+          <t>dBG6-1GKl</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>UUR79971</t>
+          <t>OXK70326</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2Vvw-yPgX</t>
+          <t>Gkyl-27Tv</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>VDD06679</t>
+          <t>OYK39161</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>9NFD-F33z</t>
+          <t>nDoT-dKaH</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>VEQ81429</t>
+          <t>OYZ43696</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>xnGV-gtxP</t>
+          <t>NE1A-0H4Y</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>VPE32737</t>
+          <t>PDL18808</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>83SX-bO49</t>
+          <t>AyIU-xTfq</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>WEO81262</t>
+          <t>PDY46515</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>L7ui-NKjF</t>
+          <t>Gg8E-S2pr</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>WJH36041</t>
+          <t>PEP57928</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>yPk4-9kvI</t>
+          <t>o921-Slsb</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>WNA57398</t>
+          <t>PHT01595</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>CU9v-k8Hc</t>
+          <t>w3qg-ZFCf</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>WQS25133</t>
+          <t>PJT16152</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Mg1K-yzvr</t>
+          <t>ExFD-xCid</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>WUA13603</t>
+          <t>PLL97657</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>hdCj-fLq2</t>
+          <t>NWjX-D2LF</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>WUH93925</t>
+          <t>PSM82237</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>8m3J-Gzlk</t>
+          <t>eY7P-J7N7</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>WWS24235</t>
+          <t>PVU41752</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>dTMF-Ocal</t>
+          <t>ugqe-Crjb</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>XKS75480</t>
+          <t>QFN79396</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>c0hS-CdvD</t>
+          <t>jXUf-ZSmc</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>XOA75961</t>
+          <t>QFU06512</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>VRah-kBaa</t>
+          <t>MNwE-V6p6</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>XRM79618</t>
+          <t>QHB18956</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>brgl-xEFq</t>
+          <t>B4nt-rvpd</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>XYT33259</t>
+          <t>QKM89908</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ahUH-85T2</t>
+          <t>bL4O-ckL6</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>XYZ70850</t>
+          <t>QRB56514</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>jdV6-HalU</t>
+          <t>ZmLU-WzDm</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>YBX87679</t>
+          <t>QUE22078</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>442D-goVh</t>
+          <t>tCyA-Oi7m</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>YCN31679</t>
+          <t>QVI53832</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>SBfE-010a</t>
+          <t>eBOh-GY3U</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>YFU10307</t>
+          <t>QYS77373</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>pv8C-S2qP</t>
+          <t>bdKc-q4v6</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>YGP30798</t>
+          <t>QYU41690</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>dZEv-nHKw</t>
+          <t>UyLP-qGWT</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>YHZ51082</t>
+          <t>RAL78524</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>7j63-7HKa</t>
+          <t>4RvF-k9n0</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>YOT12953</t>
+          <t>RBA20127</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SxGc-ZaIN</t>
+          <t>oE79-b1Se</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>ZAM21080</t>
+          <t>RFD76685</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>COFy-pMla</t>
+          <t>ZHtK-ciCM</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>ZHU54125</t>
+          <t>RLQ73857</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>5RJe-0r17</t>
+          <t>QZVO-4p3B</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>ZLP77106</t>
+          <t>RMV88503</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>djSn-TgS9</t>
+          <t>fQqP-39VA</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>ZNA23106</t>
+          <t>RNL06004</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>SHid-kPC3</t>
+          <t>WaLc-sBJY</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>ZSU27095</t>
+          <t>RQV81451</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>3TQp-7e2s</t>
+          <t>asPu-gWes</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
+          <t>RSN71799</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>APKz-8tHA</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>RVG62147</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>cqJ7-uz8x</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>SAF98648</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>JUDx-dQqy</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>SDE98641</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>E4LL-qV7u</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>SEV98034</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>3FMv-ztV8</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>SGE51092</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>9G7O-tS42</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>SGY00276</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>GGz3-kW7s</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>SLP43775</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>JIk1-QTjm</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>SMF79012</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>NcnL-Ufev</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>SNZ44527</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Idtr-Ef1p</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>SPL79883</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>vFIR-WuRr</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>SPZ85652</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>BqNU-jKbs</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>SQX65443</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>2Y2u-Iexu</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>SSU10232</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>2s1b-MrBM</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>SWB32390</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>bPkJ-04s3</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>SXZ01554</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>pE9E-t8do</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>SYH46751</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>g47k-j3HG</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>TFD08485</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>657O-VCk5</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>TGM55607</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>wiKV-5PZ7</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>TKW11810</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>XbfA-yocA</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>TME86867</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>WM5K-oBsD</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>TMJ36970</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>NiMt-vJm1</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>TRC98148</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>ImK9-sJVr</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>TTS04230</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>oJvJ-C0eE</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>TXC42578</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>ttrI-HkEA</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>UIB17642</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>huhE-ve6K</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>UOI75021</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>DQg2-NKBW</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>UUR79971</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>2Vvw-yPgX</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>VDD06679</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>9NFD-F33z</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>VEC51795</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>ePpy-45qF</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>VEQ81429</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>xnGV-gtxP</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>VHB06952</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>0muJ-HK7N</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>VPE32737</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>83SX-bO49</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>VSG31611</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>DUQt-pvMj</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>VYM86842</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>0Veq-1X2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>WEO81262</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>L7ui-NKjF</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>WHV65431</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>hZeN-SKfM</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>WJH36041</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>yPk4-9kvI</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>WNA57398</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>CU9v-k8Hc</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>WQS25133</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Mg1K-yzvr</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>WUA13603</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>hdCj-fLq2</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>WUH93925</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>8m3J-Gzlk</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>WVY21466</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>uDNr-H0pJ</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>WWS24235</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>dTMF-Ocal</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>XED10282</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>vWlv-tJFL</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>XKS75480</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>c0hS-CdvD</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>XOA75961</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>VRah-kBaa</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>XOS17378</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>vOQe-IMOh</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>XRM79618</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>brgl-xEFq</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>XSL75240</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>71I9-XlWo</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>XYT33259</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>ahUH-85T2</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>XYZ70850</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>jdV6-HalU</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>XZC74148</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>0GQn-L0M5</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>YBX87679</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>442D-goVh</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>YCN31679</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>SBfE-010a</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>YEK78642</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>QkIs-wR1T</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>YFU10307</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>pv8C-S2qP</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>YGP30798</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>dZEv-nHKw</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>YHZ51082</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>7j63-7HKa</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>YOT12953</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>SxGc-ZaIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>ZAM21080</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>COFy-pMla</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>ZFB81591</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>RPpW-yrd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>ZHU54125</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>5RJe-0r17</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>ZLP77106</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>djSn-TgS9</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>ZNA23106</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>SHid-kPC3</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>ZPU29378</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>tb6L-01Ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>ZSU27095</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>3TQp-7e2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
           <t>ZVK04224</t>
         </is>
       </c>
-      <c r="B194" t="inlineStr">
+      <c r="B261" t="inlineStr">
         <is>
           <t>9gaA-gLOl</t>
         </is>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B261"/>
+  <dimension ref="A1:B262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2555,1006 +2555,1018 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>QFN79396</t>
+          <t>PWD33511</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>jXUf-ZSmc</t>
+          <t>kAEm-3um0</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>QFU06512</t>
+          <t>QFN79396</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>MNwE-V6p6</t>
+          <t>jXUf-ZSmc</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>QHB18956</t>
+          <t>QFU06512</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>B4nt-rvpd</t>
+          <t>MNwE-V6p6</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>QKM89908</t>
+          <t>QHB18956</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>bL4O-ckL6</t>
+          <t>B4nt-rvpd</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>QRB56514</t>
+          <t>QKM89908</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>ZmLU-WzDm</t>
+          <t>bL4O-ckL6</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>QUE22078</t>
+          <t>QRB56514</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>tCyA-Oi7m</t>
+          <t>ZmLU-WzDm</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>QVI53832</t>
+          <t>QUE22078</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>eBOh-GY3U</t>
+          <t>tCyA-Oi7m</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>QYS77373</t>
+          <t>QVI53832</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>bdKc-q4v6</t>
+          <t>eBOh-GY3U</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>QYU41690</t>
+          <t>QYS77373</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>UyLP-qGWT</t>
+          <t>bdKc-q4v6</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>RAL78524</t>
+          <t>QYU41690</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>4RvF-k9n0</t>
+          <t>UyLP-qGWT</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>RBA20127</t>
+          <t>RAL78524</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>oE79-b1Se</t>
+          <t>4RvF-k9n0</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RFD76685</t>
+          <t>RBA20127</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ZHtK-ciCM</t>
+          <t>oE79-b1Se</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RLQ73857</t>
+          <t>RFD76685</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>QZVO-4p3B</t>
+          <t>ZHtK-ciCM</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RMV88503</t>
+          <t>RLQ73857</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>fQqP-39VA</t>
+          <t>QZVO-4p3B</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>RNL06004</t>
+          <t>RMV88503</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>WaLc-sBJY</t>
+          <t>fQqP-39VA</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>RQV81451</t>
+          <t>RNL06004</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>asPu-gWes</t>
+          <t>WaLc-sBJY</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>RSN71799</t>
+          <t>RQV81451</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>APKz-8tHA</t>
+          <t>asPu-gWes</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>RVG62147</t>
+          <t>RSN71799</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>cqJ7-uz8x</t>
+          <t>APKz-8tHA</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SAF98648</t>
+          <t>RVG62147</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>JUDx-dQqy</t>
+          <t>cqJ7-uz8x</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SDE98641</t>
+          <t>SAF98648</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>E4LL-qV7u</t>
+          <t>JUDx-dQqy</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SEV98034</t>
+          <t>SDE98641</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>3FMv-ztV8</t>
+          <t>E4LL-qV7u</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SGE51092</t>
+          <t>SEV98034</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>9G7O-tS42</t>
+          <t>3FMv-ztV8</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SGY00276</t>
+          <t>SGE51092</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>GGz3-kW7s</t>
+          <t>9G7O-tS42</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SLP43775</t>
+          <t>SGY00276</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>JIk1-QTjm</t>
+          <t>GGz3-kW7s</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SMF79012</t>
+          <t>SLP43775</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>NcnL-Ufev</t>
+          <t>JIk1-QTjm</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SNZ44527</t>
+          <t>SMF79012</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Idtr-Ef1p</t>
+          <t>NcnL-Ufev</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SPL79883</t>
+          <t>SNZ44527</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>vFIR-WuRr</t>
+          <t>Idtr-Ef1p</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SPZ85652</t>
+          <t>SPL79883</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>BqNU-jKbs</t>
+          <t>vFIR-WuRr</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SQX65443</t>
+          <t>SPZ85652</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>2Y2u-Iexu</t>
+          <t>BqNU-jKbs</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SSU10232</t>
+          <t>SQX65443</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2s1b-MrBM</t>
+          <t>2Y2u-Iexu</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SWB32390</t>
+          <t>SSU10232</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>bPkJ-04s3</t>
+          <t>2s1b-MrBM</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SXZ01554</t>
+          <t>SWB32390</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>pE9E-t8do</t>
+          <t>bPkJ-04s3</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SYH46751</t>
+          <t>SXZ01554</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>g47k-j3HG</t>
+          <t>pE9E-t8do</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>TFD08485</t>
+          <t>SYH46751</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>657O-VCk5</t>
+          <t>g47k-j3HG</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>TGM55607</t>
+          <t>TFD08485</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>wiKV-5PZ7</t>
+          <t>657O-VCk5</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>TKW11810</t>
+          <t>TGM55607</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>XbfA-yocA</t>
+          <t>wiKV-5PZ7</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TME86867</t>
+          <t>TKW11810</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>WM5K-oBsD</t>
+          <t>XbfA-yocA</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TMJ36970</t>
+          <t>TME86867</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>NiMt-vJm1</t>
+          <t>WM5K-oBsD</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TRC98148</t>
+          <t>TMJ36970</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>ImK9-sJVr</t>
+          <t>NiMt-vJm1</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TTS04230</t>
+          <t>TRC98148</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>oJvJ-C0eE</t>
+          <t>ImK9-sJVr</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>TXC42578</t>
+          <t>TTS04230</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ttrI-HkEA</t>
+          <t>oJvJ-C0eE</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>UIB17642</t>
+          <t>TXC42578</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>huhE-ve6K</t>
+          <t>ttrI-HkEA</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>UOI75021</t>
+          <t>UIB17642</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>DQg2-NKBW</t>
+          <t>huhE-ve6K</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>UUR79971</t>
+          <t>UOI75021</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>2Vvw-yPgX</t>
+          <t>DQg2-NKBW</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>VDD06679</t>
+          <t>UUR79971</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>9NFD-F33z</t>
+          <t>2Vvw-yPgX</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>VEC51795</t>
+          <t>VDD06679</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ePpy-45qF</t>
+          <t>9NFD-F33z</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>VEQ81429</t>
+          <t>VEC51795</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>xnGV-gtxP</t>
+          <t>ePpy-45qF</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>VHB06952</t>
+          <t>VEQ81429</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>0muJ-HK7N</t>
+          <t>xnGV-gtxP</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>VPE32737</t>
+          <t>VHB06952</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>83SX-bO49</t>
+          <t>0muJ-HK7N</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>VSG31611</t>
+          <t>VPE32737</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>DUQt-pvMj</t>
+          <t>83SX-bO49</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>VYM86842</t>
+          <t>VSG31611</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>0Veq-1X2d</t>
+          <t>DUQt-pvMj</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>WEO81262</t>
+          <t>VYM86842</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>L7ui-NKjF</t>
+          <t>0Veq-1X2d</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>WHV65431</t>
+          <t>WEO81262</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>hZeN-SKfM</t>
+          <t>L7ui-NKjF</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>WJH36041</t>
+          <t>WHV65431</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>yPk4-9kvI</t>
+          <t>hZeN-SKfM</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>WNA57398</t>
+          <t>WJH36041</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>CU9v-k8Hc</t>
+          <t>yPk4-9kvI</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>WQS25133</t>
+          <t>WNA57398</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Mg1K-yzvr</t>
+          <t>CU9v-k8Hc</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>WUA13603</t>
+          <t>WQS25133</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>hdCj-fLq2</t>
+          <t>Mg1K-yzvr</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>WUH93925</t>
+          <t>WUA13603</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>8m3J-Gzlk</t>
+          <t>hdCj-fLq2</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>WVY21466</t>
+          <t>WUH93925</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>uDNr-H0pJ</t>
+          <t>8m3J-Gzlk</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>WWS24235</t>
+          <t>WVY21466</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>dTMF-Ocal</t>
+          <t>uDNr-H0pJ</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>XED10282</t>
+          <t>WWS24235</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>vWlv-tJFL</t>
+          <t>dTMF-Ocal</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>XKS75480</t>
+          <t>XED10282</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>c0hS-CdvD</t>
+          <t>vWlv-tJFL</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>XOA75961</t>
+          <t>XKS75480</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>VRah-kBaa</t>
+          <t>c0hS-CdvD</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>XOS17378</t>
+          <t>XOA75961</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>vOQe-IMOh</t>
+          <t>VRah-kBaa</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>XRM79618</t>
+          <t>XOS17378</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>brgl-xEFq</t>
+          <t>vOQe-IMOh</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>XSL75240</t>
+          <t>XRM79618</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>71I9-XlWo</t>
+          <t>brgl-xEFq</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>XYT33259</t>
+          <t>XSL75240</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>ahUH-85T2</t>
+          <t>71I9-XlWo</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>XYZ70850</t>
+          <t>XYT33259</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>jdV6-HalU</t>
+          <t>ahUH-85T2</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>XZC74148</t>
+          <t>XYZ70850</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>0GQn-L0M5</t>
+          <t>jdV6-HalU</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>YBX87679</t>
+          <t>XZC74148</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>442D-goVh</t>
+          <t>0GQn-L0M5</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>YCN31679</t>
+          <t>YBX87679</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>SBfE-010a</t>
+          <t>442D-goVh</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>YEK78642</t>
+          <t>YCN31679</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>QkIs-wR1T</t>
+          <t>SBfE-010a</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>YFU10307</t>
+          <t>YEK78642</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>pv8C-S2qP</t>
+          <t>QkIs-wR1T</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>YGP30798</t>
+          <t>YFU10307</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>dZEv-nHKw</t>
+          <t>pv8C-S2qP</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>YHZ51082</t>
+          <t>YGP30798</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>7j63-7HKa</t>
+          <t>dZEv-nHKw</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>YOT12953</t>
+          <t>YHZ51082</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>SxGc-ZaIN</t>
+          <t>7j63-7HKa</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ZAM21080</t>
+          <t>YOT12953</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>COFy-pMla</t>
+          <t>SxGc-ZaIN</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ZFB81591</t>
+          <t>ZAM21080</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>RPpW-yrd5</t>
+          <t>COFy-pMla</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ZHU54125</t>
+          <t>ZFB81591</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>5RJe-0r17</t>
+          <t>RPpW-yrd5</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ZLP77106</t>
+          <t>ZHU54125</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>djSn-TgS9</t>
+          <t>5RJe-0r17</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ZNA23106</t>
+          <t>ZLP77106</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>SHid-kPC3</t>
+          <t>djSn-TgS9</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ZPU29378</t>
+          <t>ZNA23106</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>tb6L-01Ac</t>
+          <t>SHid-kPC3</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ZSU27095</t>
+          <t>ZPU29378</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>3TQp-7e2s</t>
+          <t>tb6L-01Ac</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
+          <t>ZSU27095</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>3TQp-7e2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
           <t>ZVK04224</t>
         </is>
       </c>
-      <c r="B261" t="inlineStr">
+      <c r="B262" t="inlineStr">
         <is>
           <t>9gaA-gLOl</t>
         </is>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B262"/>
+  <dimension ref="A1:B263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2699,874 +2699,886 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RFD76685</t>
+          <t>RER39252</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ZHtK-ciCM</t>
+          <t>cNTo-jOTf</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RLQ73857</t>
+          <t>RFD76685</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>QZVO-4p3B</t>
+          <t>ZHtK-ciCM</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>RMV88503</t>
+          <t>RLQ73857</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>fQqP-39VA</t>
+          <t>QZVO-4p3B</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>RNL06004</t>
+          <t>RMV88503</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>WaLc-sBJY</t>
+          <t>fQqP-39VA</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>RQV81451</t>
+          <t>RNL06004</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>asPu-gWes</t>
+          <t>WaLc-sBJY</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>RSN71799</t>
+          <t>RQV81451</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>APKz-8tHA</t>
+          <t>asPu-gWes</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>RVG62147</t>
+          <t>RSN71799</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>cqJ7-uz8x</t>
+          <t>APKz-8tHA</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SAF98648</t>
+          <t>RVG62147</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>JUDx-dQqy</t>
+          <t>cqJ7-uz8x</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SDE98641</t>
+          <t>SAF98648</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>E4LL-qV7u</t>
+          <t>JUDx-dQqy</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SEV98034</t>
+          <t>SDE98641</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>3FMv-ztV8</t>
+          <t>E4LL-qV7u</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SGE51092</t>
+          <t>SEV98034</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>9G7O-tS42</t>
+          <t>3FMv-ztV8</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SGY00276</t>
+          <t>SGE51092</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>GGz3-kW7s</t>
+          <t>9G7O-tS42</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SLP43775</t>
+          <t>SGY00276</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>JIk1-QTjm</t>
+          <t>GGz3-kW7s</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SMF79012</t>
+          <t>SLP43775</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>NcnL-Ufev</t>
+          <t>JIk1-QTjm</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SNZ44527</t>
+          <t>SMF79012</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Idtr-Ef1p</t>
+          <t>NcnL-Ufev</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SPL79883</t>
+          <t>SNZ44527</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>vFIR-WuRr</t>
+          <t>Idtr-Ef1p</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SPZ85652</t>
+          <t>SPL79883</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>BqNU-jKbs</t>
+          <t>vFIR-WuRr</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SQX65443</t>
+          <t>SPZ85652</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>2Y2u-Iexu</t>
+          <t>BqNU-jKbs</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SSU10232</t>
+          <t>SQX65443</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2s1b-MrBM</t>
+          <t>2Y2u-Iexu</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SWB32390</t>
+          <t>SSU10232</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>bPkJ-04s3</t>
+          <t>2s1b-MrBM</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SXZ01554</t>
+          <t>SWB32390</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>pE9E-t8do</t>
+          <t>bPkJ-04s3</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SYH46751</t>
+          <t>SXZ01554</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>g47k-j3HG</t>
+          <t>pE9E-t8do</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>TFD08485</t>
+          <t>SYH46751</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>657O-VCk5</t>
+          <t>g47k-j3HG</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>TGM55607</t>
+          <t>TFD08485</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>wiKV-5PZ7</t>
+          <t>657O-VCk5</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TKW11810</t>
+          <t>TGM55607</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>XbfA-yocA</t>
+          <t>wiKV-5PZ7</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TME86867</t>
+          <t>TKW11810</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>WM5K-oBsD</t>
+          <t>XbfA-yocA</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TMJ36970</t>
+          <t>TME86867</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>NiMt-vJm1</t>
+          <t>WM5K-oBsD</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TRC98148</t>
+          <t>TMJ36970</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ImK9-sJVr</t>
+          <t>NiMt-vJm1</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>TTS04230</t>
+          <t>TRC98148</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>oJvJ-C0eE</t>
+          <t>ImK9-sJVr</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>TXC42578</t>
+          <t>TTS04230</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ttrI-HkEA</t>
+          <t>oJvJ-C0eE</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>UIB17642</t>
+          <t>TXC42578</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>huhE-ve6K</t>
+          <t>ttrI-HkEA</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>UOI75021</t>
+          <t>UIB17642</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>DQg2-NKBW</t>
+          <t>huhE-ve6K</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>UUR79971</t>
+          <t>UOI75021</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>2Vvw-yPgX</t>
+          <t>DQg2-NKBW</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>VDD06679</t>
+          <t>UUR79971</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>9NFD-F33z</t>
+          <t>2Vvw-yPgX</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>VEC51795</t>
+          <t>VDD06679</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>ePpy-45qF</t>
+          <t>9NFD-F33z</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>VEQ81429</t>
+          <t>VEC51795</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>xnGV-gtxP</t>
+          <t>ePpy-45qF</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>VHB06952</t>
+          <t>VEQ81429</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>0muJ-HK7N</t>
+          <t>xnGV-gtxP</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>VPE32737</t>
+          <t>VHB06952</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>83SX-bO49</t>
+          <t>0muJ-HK7N</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>VSG31611</t>
+          <t>VPE32737</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>DUQt-pvMj</t>
+          <t>83SX-bO49</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>VYM86842</t>
+          <t>VSG31611</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>0Veq-1X2d</t>
+          <t>DUQt-pvMj</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>WEO81262</t>
+          <t>VYM86842</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>L7ui-NKjF</t>
+          <t>0Veq-1X2d</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>WHV65431</t>
+          <t>WEO81262</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>hZeN-SKfM</t>
+          <t>L7ui-NKjF</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>WJH36041</t>
+          <t>WHV65431</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>yPk4-9kvI</t>
+          <t>hZeN-SKfM</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>WNA57398</t>
+          <t>WJH36041</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>CU9v-k8Hc</t>
+          <t>yPk4-9kvI</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>WQS25133</t>
+          <t>WNA57398</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Mg1K-yzvr</t>
+          <t>CU9v-k8Hc</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>WUA13603</t>
+          <t>WQS25133</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>hdCj-fLq2</t>
+          <t>Mg1K-yzvr</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>WUH93925</t>
+          <t>WUA13603</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>8m3J-Gzlk</t>
+          <t>hdCj-fLq2</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>WVY21466</t>
+          <t>WUH93925</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>uDNr-H0pJ</t>
+          <t>8m3J-Gzlk</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>WWS24235</t>
+          <t>WVY21466</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>dTMF-Ocal</t>
+          <t>uDNr-H0pJ</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>XED10282</t>
+          <t>WWS24235</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>vWlv-tJFL</t>
+          <t>dTMF-Ocal</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>XKS75480</t>
+          <t>XED10282</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>c0hS-CdvD</t>
+          <t>vWlv-tJFL</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>XOA75961</t>
+          <t>XKS75480</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>VRah-kBaa</t>
+          <t>c0hS-CdvD</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>XOS17378</t>
+          <t>XOA75961</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>vOQe-IMOh</t>
+          <t>VRah-kBaa</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>XRM79618</t>
+          <t>XOS17378</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>brgl-xEFq</t>
+          <t>vOQe-IMOh</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>XSL75240</t>
+          <t>XRM79618</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>71I9-XlWo</t>
+          <t>brgl-xEFq</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>XYT33259</t>
+          <t>XSL75240</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>ahUH-85T2</t>
+          <t>71I9-XlWo</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>XYZ70850</t>
+          <t>XYT33259</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>jdV6-HalU</t>
+          <t>ahUH-85T2</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>XZC74148</t>
+          <t>XYZ70850</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>0GQn-L0M5</t>
+          <t>jdV6-HalU</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>YBX87679</t>
+          <t>XZC74148</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>442D-goVh</t>
+          <t>0GQn-L0M5</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>YCN31679</t>
+          <t>YBX87679</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>SBfE-010a</t>
+          <t>442D-goVh</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>YEK78642</t>
+          <t>YCN31679</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>QkIs-wR1T</t>
+          <t>SBfE-010a</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>YFU10307</t>
+          <t>YEK78642</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>pv8C-S2qP</t>
+          <t>QkIs-wR1T</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>YGP30798</t>
+          <t>YFU10307</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>dZEv-nHKw</t>
+          <t>pv8C-S2qP</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>YHZ51082</t>
+          <t>YGP30798</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>7j63-7HKa</t>
+          <t>dZEv-nHKw</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>YOT12953</t>
+          <t>YHZ51082</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>SxGc-ZaIN</t>
+          <t>7j63-7HKa</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ZAM21080</t>
+          <t>YOT12953</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>COFy-pMla</t>
+          <t>SxGc-ZaIN</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ZFB81591</t>
+          <t>ZAM21080</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>RPpW-yrd5</t>
+          <t>COFy-pMla</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ZHU54125</t>
+          <t>ZFB81591</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>5RJe-0r17</t>
+          <t>RPpW-yrd5</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ZLP77106</t>
+          <t>ZHU54125</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>djSn-TgS9</t>
+          <t>5RJe-0r17</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ZNA23106</t>
+          <t>ZLP77106</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>SHid-kPC3</t>
+          <t>djSn-TgS9</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ZPU29378</t>
+          <t>ZNA23106</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>tb6L-01Ac</t>
+          <t>SHid-kPC3</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ZSU27095</t>
+          <t>ZPU29378</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>3TQp-7e2s</t>
+          <t>tb6L-01Ac</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
+          <t>ZSU27095</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>3TQp-7e2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
           <t>ZVK04224</t>
         </is>
       </c>
-      <c r="B262" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>9gaA-gLOl</t>
         </is>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B263"/>
+  <dimension ref="A1:B264"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2039,1546 +2039,1558 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MNW15780</t>
+          <t>MND74401</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>6iUB-Vag7</t>
+          <t>ENc9-yDXA</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MRQ02763</t>
+          <t>MNW15780</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>jkZw-MaOb</t>
+          <t>6iUB-Vag7</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MUE50996</t>
+          <t>MRQ02763</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>UIda-nQtd</t>
+          <t>jkZw-MaOb</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MUX13896</t>
+          <t>MUE50996</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>r20R-BlFc</t>
+          <t>UIda-nQtd</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MXC93247</t>
+          <t>MUX13896</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>fcAI-rABo</t>
+          <t>r20R-BlFc</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MXM72788</t>
+          <t>MXC93247</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>iRyF-IaTc</t>
+          <t>fcAI-rABo</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MYD82527</t>
+          <t>MXM72788</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>1z7Z-Iwsk</t>
+          <t>iRyF-IaTc</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MYX47244</t>
+          <t>MYD82527</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>zpLV-zFXv</t>
+          <t>1z7Z-Iwsk</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>NAQ63112</t>
+          <t>MYX47244</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>vedO-3joS</t>
+          <t>zpLV-zFXv</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>NCL61296</t>
+          <t>NAQ63112</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>MTj9-lIY8</t>
+          <t>vedO-3joS</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NDJ67099</t>
+          <t>NCL61296</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>hrBW-w842</t>
+          <t>MTj9-lIY8</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NEE79704</t>
+          <t>NDJ67099</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>ed0x-qxBt</t>
+          <t>hrBW-w842</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>NIQ43372</t>
+          <t>NEE79704</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CXS1-PyNb</t>
+          <t>ed0x-qxBt</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NLP67632</t>
+          <t>NIQ43372</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>b9F6-vbZ5</t>
+          <t>CXS1-PyNb</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>NPD00961</t>
+          <t>NLP67632</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>aI8u-zYiw</t>
+          <t>b9F6-vbZ5</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>NUI19784</t>
+          <t>NPD00961</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>mF1f-kCQW</t>
+          <t>aI8u-zYiw</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NWX06153</t>
+          <t>NUI19784</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>N3G4-xe8w</t>
+          <t>mF1f-kCQW</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>NYF03161</t>
+          <t>NWX06153</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>zMxQ-K0fi</t>
+          <t>N3G4-xe8w</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>NZW46214</t>
+          <t>NYF03161</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>09st-zHFg</t>
+          <t>zMxQ-K0fi</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>NZZ50766</t>
+          <t>NZW46214</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>XINJ-KGsC</t>
+          <t>09st-zHFg</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>OAM83746</t>
+          <t>NZZ50766</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>56vK-YHjW</t>
+          <t>XINJ-KGsC</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OBI75581</t>
+          <t>OAM83746</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Mygc-BSFY</t>
+          <t>56vK-YHjW</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ODU01918</t>
+          <t>OBI75581</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>ia7S-FLGr</t>
+          <t>Mygc-BSFY</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>OEJ86175</t>
+          <t>ODU01918</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>XJIi-fHfZ</t>
+          <t>ia7S-FLGr</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>OKY47911</t>
+          <t>OEJ86175</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>uSoZ-cHIn</t>
+          <t>XJIi-fHfZ</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ORR85927</t>
+          <t>OKY47911</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>JgtA-rF6p</t>
+          <t>uSoZ-cHIn</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ORT63362</t>
+          <t>ORR85927</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>XZT6-FxOF</t>
+          <t>JgtA-rF6p</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>OSB52441</t>
+          <t>ORT63362</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>I1Cv-DmRA</t>
+          <t>XZT6-FxOF</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>OWO93746</t>
+          <t>OSB52441</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>hGwl-3fWL</t>
+          <t>I1Cv-DmRA</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>OWR55957</t>
+          <t>OWO93746</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5xs5-2GVm</t>
+          <t>hGwl-3fWL</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>OXE34055</t>
+          <t>OWR55957</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>QMAt-FrNE</t>
+          <t>5xs5-2GVm</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>OXH82758</t>
+          <t>OXE34055</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>dBG6-1GKl</t>
+          <t>QMAt-FrNE</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>OXK70326</t>
+          <t>OXH82758</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Gkyl-27Tv</t>
+          <t>dBG6-1GKl</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>OYK39161</t>
+          <t>OXK70326</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>nDoT-dKaH</t>
+          <t>Gkyl-27Tv</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>OYZ43696</t>
+          <t>OYK39161</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>NE1A-0H4Y</t>
+          <t>nDoT-dKaH</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PDL18808</t>
+          <t>OYZ43696</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>AyIU-xTfq</t>
+          <t>NE1A-0H4Y</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PDY46515</t>
+          <t>PDL18808</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Gg8E-S2pr</t>
+          <t>AyIU-xTfq</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PEP57928</t>
+          <t>PDY46515</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>o921-Slsb</t>
+          <t>Gg8E-S2pr</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PHT01595</t>
+          <t>PEP57928</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>w3qg-ZFCf</t>
+          <t>o921-Slsb</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PJT16152</t>
+          <t>PHT01595</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ExFD-xCid</t>
+          <t>w3qg-ZFCf</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PLL97657</t>
+          <t>PJT16152</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>NWjX-D2LF</t>
+          <t>ExFD-xCid</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PSM82237</t>
+          <t>PLL97657</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>eY7P-J7N7</t>
+          <t>NWjX-D2LF</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PVU41752</t>
+          <t>PSM82237</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>ugqe-Crjb</t>
+          <t>eY7P-J7N7</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PWD33511</t>
+          <t>PVU41752</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>kAEm-3um0</t>
+          <t>ugqe-Crjb</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>QFN79396</t>
+          <t>PWD33511</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>jXUf-ZSmc</t>
+          <t>kAEm-3um0</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>QFU06512</t>
+          <t>QFN79396</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>MNwE-V6p6</t>
+          <t>jXUf-ZSmc</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>QHB18956</t>
+          <t>QFU06512</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>B4nt-rvpd</t>
+          <t>MNwE-V6p6</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>QKM89908</t>
+          <t>QHB18956</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>bL4O-ckL6</t>
+          <t>B4nt-rvpd</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>QRB56514</t>
+          <t>QKM89908</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>ZmLU-WzDm</t>
+          <t>bL4O-ckL6</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>QUE22078</t>
+          <t>QRB56514</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>tCyA-Oi7m</t>
+          <t>ZmLU-WzDm</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>QVI53832</t>
+          <t>QUE22078</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>eBOh-GY3U</t>
+          <t>tCyA-Oi7m</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>QYS77373</t>
+          <t>QVI53832</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>bdKc-q4v6</t>
+          <t>eBOh-GY3U</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>QYU41690</t>
+          <t>QYS77373</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>UyLP-qGWT</t>
+          <t>bdKc-q4v6</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>RAL78524</t>
+          <t>QYU41690</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>4RvF-k9n0</t>
+          <t>UyLP-qGWT</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RBA20127</t>
+          <t>RAL78524</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>oE79-b1Se</t>
+          <t>4RvF-k9n0</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RER39252</t>
+          <t>RBA20127</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>cNTo-jOTf</t>
+          <t>oE79-b1Se</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RFD76685</t>
+          <t>RER39252</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ZHtK-ciCM</t>
+          <t>cNTo-jOTf</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>RLQ73857</t>
+          <t>RFD76685</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>QZVO-4p3B</t>
+          <t>ZHtK-ciCM</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>RMV88503</t>
+          <t>RLQ73857</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>fQqP-39VA</t>
+          <t>QZVO-4p3B</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>RNL06004</t>
+          <t>RMV88503</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>WaLc-sBJY</t>
+          <t>fQqP-39VA</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>RQV81451</t>
+          <t>RNL06004</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>asPu-gWes</t>
+          <t>WaLc-sBJY</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>RSN71799</t>
+          <t>RQV81451</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>APKz-8tHA</t>
+          <t>asPu-gWes</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>RVG62147</t>
+          <t>RSN71799</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>cqJ7-uz8x</t>
+          <t>APKz-8tHA</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SAF98648</t>
+          <t>RVG62147</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>JUDx-dQqy</t>
+          <t>cqJ7-uz8x</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SDE98641</t>
+          <t>SAF98648</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>E4LL-qV7u</t>
+          <t>JUDx-dQqy</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SEV98034</t>
+          <t>SDE98641</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>3FMv-ztV8</t>
+          <t>E4LL-qV7u</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SGE51092</t>
+          <t>SEV98034</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>9G7O-tS42</t>
+          <t>3FMv-ztV8</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SGY00276</t>
+          <t>SGE51092</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>GGz3-kW7s</t>
+          <t>9G7O-tS42</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SLP43775</t>
+          <t>SGY00276</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>JIk1-QTjm</t>
+          <t>GGz3-kW7s</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SMF79012</t>
+          <t>SLP43775</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>NcnL-Ufev</t>
+          <t>JIk1-QTjm</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SNZ44527</t>
+          <t>SMF79012</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Idtr-Ef1p</t>
+          <t>NcnL-Ufev</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SPL79883</t>
+          <t>SNZ44527</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>vFIR-WuRr</t>
+          <t>Idtr-Ef1p</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SPZ85652</t>
+          <t>SPL79883</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>BqNU-jKbs</t>
+          <t>vFIR-WuRr</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SQX65443</t>
+          <t>SPZ85652</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>2Y2u-Iexu</t>
+          <t>BqNU-jKbs</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SSU10232</t>
+          <t>SQX65443</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2s1b-MrBM</t>
+          <t>2Y2u-Iexu</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SWB32390</t>
+          <t>SSU10232</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>bPkJ-04s3</t>
+          <t>2s1b-MrBM</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SXZ01554</t>
+          <t>SWB32390</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>pE9E-t8do</t>
+          <t>bPkJ-04s3</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SYH46751</t>
+          <t>SXZ01554</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>g47k-j3HG</t>
+          <t>pE9E-t8do</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>TFD08485</t>
+          <t>SYH46751</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>657O-VCk5</t>
+          <t>g47k-j3HG</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TGM55607</t>
+          <t>TFD08485</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>wiKV-5PZ7</t>
+          <t>657O-VCk5</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TKW11810</t>
+          <t>TGM55607</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>XbfA-yocA</t>
+          <t>wiKV-5PZ7</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TME86867</t>
+          <t>TKW11810</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>WM5K-oBsD</t>
+          <t>XbfA-yocA</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TMJ36970</t>
+          <t>TME86867</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>NiMt-vJm1</t>
+          <t>WM5K-oBsD</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>TRC98148</t>
+          <t>TMJ36970</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ImK9-sJVr</t>
+          <t>NiMt-vJm1</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>TTS04230</t>
+          <t>TRC98148</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>oJvJ-C0eE</t>
+          <t>ImK9-sJVr</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>TXC42578</t>
+          <t>TTS04230</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ttrI-HkEA</t>
+          <t>oJvJ-C0eE</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>UIB17642</t>
+          <t>TXC42578</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>huhE-ve6K</t>
+          <t>ttrI-HkEA</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>UOI75021</t>
+          <t>UIB17642</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>DQg2-NKBW</t>
+          <t>huhE-ve6K</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>UUR79971</t>
+          <t>UOI75021</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>2Vvw-yPgX</t>
+          <t>DQg2-NKBW</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>VDD06679</t>
+          <t>UUR79971</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>9NFD-F33z</t>
+          <t>2Vvw-yPgX</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>VEC51795</t>
+          <t>VDD06679</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>ePpy-45qF</t>
+          <t>9NFD-F33z</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>VEQ81429</t>
+          <t>VEC51795</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>xnGV-gtxP</t>
+          <t>ePpy-45qF</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>VHB06952</t>
+          <t>VEQ81429</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>0muJ-HK7N</t>
+          <t>xnGV-gtxP</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>VPE32737</t>
+          <t>VHB06952</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>83SX-bO49</t>
+          <t>0muJ-HK7N</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>VSG31611</t>
+          <t>VPE32737</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>DUQt-pvMj</t>
+          <t>83SX-bO49</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>VYM86842</t>
+          <t>VSG31611</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>0Veq-1X2d</t>
+          <t>DUQt-pvMj</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>WEO81262</t>
+          <t>VYM86842</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>L7ui-NKjF</t>
+          <t>0Veq-1X2d</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>WHV65431</t>
+          <t>WEO81262</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>hZeN-SKfM</t>
+          <t>L7ui-NKjF</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>WJH36041</t>
+          <t>WHV65431</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>yPk4-9kvI</t>
+          <t>hZeN-SKfM</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>WNA57398</t>
+          <t>WJH36041</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>CU9v-k8Hc</t>
+          <t>yPk4-9kvI</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>WQS25133</t>
+          <t>WNA57398</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Mg1K-yzvr</t>
+          <t>CU9v-k8Hc</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>WUA13603</t>
+          <t>WQS25133</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>hdCj-fLq2</t>
+          <t>Mg1K-yzvr</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>WUH93925</t>
+          <t>WUA13603</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>8m3J-Gzlk</t>
+          <t>hdCj-fLq2</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>WVY21466</t>
+          <t>WUH93925</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>uDNr-H0pJ</t>
+          <t>8m3J-Gzlk</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>WWS24235</t>
+          <t>WVY21466</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>dTMF-Ocal</t>
+          <t>uDNr-H0pJ</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>XED10282</t>
+          <t>WWS24235</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>vWlv-tJFL</t>
+          <t>dTMF-Ocal</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>XKS75480</t>
+          <t>XED10282</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>c0hS-CdvD</t>
+          <t>vWlv-tJFL</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>XOA75961</t>
+          <t>XKS75480</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>VRah-kBaa</t>
+          <t>c0hS-CdvD</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>XOS17378</t>
+          <t>XOA75961</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>vOQe-IMOh</t>
+          <t>VRah-kBaa</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>XRM79618</t>
+          <t>XOS17378</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>brgl-xEFq</t>
+          <t>vOQe-IMOh</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>XSL75240</t>
+          <t>XRM79618</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>71I9-XlWo</t>
+          <t>brgl-xEFq</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>XYT33259</t>
+          <t>XSL75240</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>ahUH-85T2</t>
+          <t>71I9-XlWo</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>XYZ70850</t>
+          <t>XYT33259</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>jdV6-HalU</t>
+          <t>ahUH-85T2</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>XZC74148</t>
+          <t>XYZ70850</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>0GQn-L0M5</t>
+          <t>jdV6-HalU</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>YBX87679</t>
+          <t>XZC74148</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>442D-goVh</t>
+          <t>0GQn-L0M5</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>YCN31679</t>
+          <t>YBX87679</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>SBfE-010a</t>
+          <t>442D-goVh</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>YEK78642</t>
+          <t>YCN31679</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>QkIs-wR1T</t>
+          <t>SBfE-010a</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>YFU10307</t>
+          <t>YEK78642</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>pv8C-S2qP</t>
+          <t>QkIs-wR1T</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>YGP30798</t>
+          <t>YFU10307</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>dZEv-nHKw</t>
+          <t>pv8C-S2qP</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>YHZ51082</t>
+          <t>YGP30798</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>7j63-7HKa</t>
+          <t>dZEv-nHKw</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>YOT12953</t>
+          <t>YHZ51082</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>SxGc-ZaIN</t>
+          <t>7j63-7HKa</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ZAM21080</t>
+          <t>YOT12953</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>COFy-pMla</t>
+          <t>SxGc-ZaIN</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ZFB81591</t>
+          <t>ZAM21080</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>RPpW-yrd5</t>
+          <t>COFy-pMla</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ZHU54125</t>
+          <t>ZFB81591</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>5RJe-0r17</t>
+          <t>RPpW-yrd5</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ZLP77106</t>
+          <t>ZHU54125</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>djSn-TgS9</t>
+          <t>5RJe-0r17</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ZNA23106</t>
+          <t>ZLP77106</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>SHid-kPC3</t>
+          <t>djSn-TgS9</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ZPU29378</t>
+          <t>ZNA23106</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>tb6L-01Ac</t>
+          <t>SHid-kPC3</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ZSU27095</t>
+          <t>ZPU29378</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>3TQp-7e2s</t>
+          <t>tb6L-01Ac</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
+          <t>ZSU27095</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>3TQp-7e2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
           <t>ZVK04224</t>
         </is>
       </c>
-      <c r="B263" t="inlineStr">
+      <c r="B264" t="inlineStr">
         <is>
           <t>9gaA-gLOl</t>
         </is>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B264"/>
+  <dimension ref="A1:B265"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2795,802 +2795,814 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>RVG62147</t>
+          <t>RSV50349</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>cqJ7-uz8x</t>
+          <t>gUKK-rzSk</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SAF98648</t>
+          <t>RVG62147</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>JUDx-dQqy</t>
+          <t>cqJ7-uz8x</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SDE98641</t>
+          <t>SAF98648</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>E4LL-qV7u</t>
+          <t>JUDx-dQqy</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SEV98034</t>
+          <t>SDE98641</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>3FMv-ztV8</t>
+          <t>E4LL-qV7u</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SGE51092</t>
+          <t>SEV98034</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>9G7O-tS42</t>
+          <t>3FMv-ztV8</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SGY00276</t>
+          <t>SGE51092</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>GGz3-kW7s</t>
+          <t>9G7O-tS42</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SLP43775</t>
+          <t>SGY00276</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>JIk1-QTjm</t>
+          <t>GGz3-kW7s</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SMF79012</t>
+          <t>SLP43775</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>NcnL-Ufev</t>
+          <t>JIk1-QTjm</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SNZ44527</t>
+          <t>SMF79012</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Idtr-Ef1p</t>
+          <t>NcnL-Ufev</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SPL79883</t>
+          <t>SNZ44527</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>vFIR-WuRr</t>
+          <t>Idtr-Ef1p</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SPZ85652</t>
+          <t>SPL79883</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>BqNU-jKbs</t>
+          <t>vFIR-WuRr</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SQX65443</t>
+          <t>SPZ85652</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>2Y2u-Iexu</t>
+          <t>BqNU-jKbs</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SSU10232</t>
+          <t>SQX65443</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2s1b-MrBM</t>
+          <t>2Y2u-Iexu</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SWB32390</t>
+          <t>SSU10232</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>bPkJ-04s3</t>
+          <t>2s1b-MrBM</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SXZ01554</t>
+          <t>SWB32390</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>pE9E-t8do</t>
+          <t>bPkJ-04s3</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SYH46751</t>
+          <t>SXZ01554</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>g47k-j3HG</t>
+          <t>pE9E-t8do</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TFD08485</t>
+          <t>SYH46751</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>657O-VCk5</t>
+          <t>g47k-j3HG</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TGM55607</t>
+          <t>TFD08485</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>wiKV-5PZ7</t>
+          <t>657O-VCk5</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TKW11810</t>
+          <t>TGM55607</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>XbfA-yocA</t>
+          <t>wiKV-5PZ7</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TME86867</t>
+          <t>TKW11810</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>WM5K-oBsD</t>
+          <t>XbfA-yocA</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>TMJ36970</t>
+          <t>TME86867</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>NiMt-vJm1</t>
+          <t>WM5K-oBsD</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>TRC98148</t>
+          <t>TMJ36970</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>ImK9-sJVr</t>
+          <t>NiMt-vJm1</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>TTS04230</t>
+          <t>TRC98148</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>oJvJ-C0eE</t>
+          <t>ImK9-sJVr</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>TXC42578</t>
+          <t>TTS04230</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>ttrI-HkEA</t>
+          <t>oJvJ-C0eE</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>UIB17642</t>
+          <t>TXC42578</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>huhE-ve6K</t>
+          <t>ttrI-HkEA</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>UOI75021</t>
+          <t>UIB17642</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>DQg2-NKBW</t>
+          <t>huhE-ve6K</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>UUR79971</t>
+          <t>UOI75021</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>2Vvw-yPgX</t>
+          <t>DQg2-NKBW</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>VDD06679</t>
+          <t>UUR79971</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>9NFD-F33z</t>
+          <t>2Vvw-yPgX</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>VEC51795</t>
+          <t>VDD06679</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>ePpy-45qF</t>
+          <t>9NFD-F33z</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>VEQ81429</t>
+          <t>VEC51795</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>xnGV-gtxP</t>
+          <t>ePpy-45qF</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>VHB06952</t>
+          <t>VEQ81429</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>0muJ-HK7N</t>
+          <t>xnGV-gtxP</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>VPE32737</t>
+          <t>VHB06952</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>83SX-bO49</t>
+          <t>0muJ-HK7N</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>VSG31611</t>
+          <t>VPE32737</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>DUQt-pvMj</t>
+          <t>83SX-bO49</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>VYM86842</t>
+          <t>VSG31611</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>0Veq-1X2d</t>
+          <t>DUQt-pvMj</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>WEO81262</t>
+          <t>VYM86842</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>L7ui-NKjF</t>
+          <t>0Veq-1X2d</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>WHV65431</t>
+          <t>WEO81262</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>hZeN-SKfM</t>
+          <t>L7ui-NKjF</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>WJH36041</t>
+          <t>WHV65431</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>yPk4-9kvI</t>
+          <t>hZeN-SKfM</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>WNA57398</t>
+          <t>WJH36041</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>CU9v-k8Hc</t>
+          <t>yPk4-9kvI</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>WQS25133</t>
+          <t>WNA57398</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Mg1K-yzvr</t>
+          <t>CU9v-k8Hc</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>WUA13603</t>
+          <t>WQS25133</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>hdCj-fLq2</t>
+          <t>Mg1K-yzvr</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>WUH93925</t>
+          <t>WUA13603</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>8m3J-Gzlk</t>
+          <t>hdCj-fLq2</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>WVY21466</t>
+          <t>WUH93925</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>uDNr-H0pJ</t>
+          <t>8m3J-Gzlk</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>WWS24235</t>
+          <t>WVY21466</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>dTMF-Ocal</t>
+          <t>uDNr-H0pJ</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>XED10282</t>
+          <t>WWS24235</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>vWlv-tJFL</t>
+          <t>dTMF-Ocal</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>XKS75480</t>
+          <t>XED10282</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>c0hS-CdvD</t>
+          <t>vWlv-tJFL</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>XOA75961</t>
+          <t>XKS75480</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>VRah-kBaa</t>
+          <t>c0hS-CdvD</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>XOS17378</t>
+          <t>XOA75961</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>vOQe-IMOh</t>
+          <t>VRah-kBaa</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>XRM79618</t>
+          <t>XOS17378</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>brgl-xEFq</t>
+          <t>vOQe-IMOh</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>XSL75240</t>
+          <t>XRM79618</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>71I9-XlWo</t>
+          <t>brgl-xEFq</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>XYT33259</t>
+          <t>XSL75240</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>ahUH-85T2</t>
+          <t>71I9-XlWo</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>XYZ70850</t>
+          <t>XYT33259</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>jdV6-HalU</t>
+          <t>ahUH-85T2</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>XZC74148</t>
+          <t>XYZ70850</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>0GQn-L0M5</t>
+          <t>jdV6-HalU</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>YBX87679</t>
+          <t>XZC74148</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>442D-goVh</t>
+          <t>0GQn-L0M5</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>YCN31679</t>
+          <t>YBX87679</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>SBfE-010a</t>
+          <t>442D-goVh</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>YEK78642</t>
+          <t>YCN31679</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>QkIs-wR1T</t>
+          <t>SBfE-010a</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>YFU10307</t>
+          <t>YEK78642</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>pv8C-S2qP</t>
+          <t>QkIs-wR1T</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>YGP30798</t>
+          <t>YFU10307</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>dZEv-nHKw</t>
+          <t>pv8C-S2qP</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>YHZ51082</t>
+          <t>YGP30798</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>7j63-7HKa</t>
+          <t>dZEv-nHKw</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>YOT12953</t>
+          <t>YHZ51082</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>SxGc-ZaIN</t>
+          <t>7j63-7HKa</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ZAM21080</t>
+          <t>YOT12953</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>COFy-pMla</t>
+          <t>SxGc-ZaIN</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ZFB81591</t>
+          <t>ZAM21080</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>RPpW-yrd5</t>
+          <t>COFy-pMla</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ZHU54125</t>
+          <t>ZFB81591</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>5RJe-0r17</t>
+          <t>RPpW-yrd5</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ZLP77106</t>
+          <t>ZHU54125</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>djSn-TgS9</t>
+          <t>5RJe-0r17</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ZNA23106</t>
+          <t>ZLP77106</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>SHid-kPC3</t>
+          <t>djSn-TgS9</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ZPU29378</t>
+          <t>ZNA23106</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>tb6L-01Ac</t>
+          <t>SHid-kPC3</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ZSU27095</t>
+          <t>ZPU29378</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>3TQp-7e2s</t>
+          <t>tb6L-01Ac</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
+          <t>ZSU27095</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>3TQp-7e2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
           <t>ZVK04224</t>
         </is>
       </c>
-      <c r="B264" t="inlineStr">
+      <c r="B265" t="inlineStr">
         <is>
           <t>9gaA-gLOl</t>
         </is>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B265"/>
+  <dimension ref="A1:B266"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -947,2662 +947,2674 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DGL58063</t>
+          <t>DEI55654</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>lQpJ-cvmL</t>
+          <t>dpkR-1tH2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DHH79187</t>
+          <t>DGL58063</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kp6O-nXp3</t>
+          <t>lQpJ-cvmL</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DJK20638</t>
+          <t>DHH79187</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ZJAv-brF5</t>
+          <t>kp6O-nXp3</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DLF24523</t>
+          <t>DJK20638</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1Fps-H1ZW</t>
+          <t>ZJAv-brF5</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DLP45053</t>
+          <t>DLF24523</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>L7sf-MoLb</t>
+          <t>1Fps-H1ZW</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DQD33133</t>
+          <t>DLP45053</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>WX5H-LiPX</t>
+          <t>L7sf-MoLb</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DTZ69845</t>
+          <t>DQD33133</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FiA8-mFOt</t>
+          <t>WX5H-LiPX</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DUA61401</t>
+          <t>DTZ69845</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2vrj-OFZH</t>
+          <t>FiA8-mFOt</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DVJ66295</t>
+          <t>DUA61401</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>8Bl3-qRML</t>
+          <t>2vrj-OFZH</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DXM69578</t>
+          <t>DVJ66295</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>gt5b-TF6d</t>
+          <t>8Bl3-qRML</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DZI77349</t>
+          <t>DXM69578</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>exKl-ZgTI</t>
+          <t>gt5b-TF6d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EBT22822</t>
+          <t>DZI77349</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2lhq-XPz5</t>
+          <t>exKl-ZgTI</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ECG95521</t>
+          <t>EBT22822</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>weWw-hC7q</t>
+          <t>2lhq-XPz5</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EWP70521</t>
+          <t>ECG95521</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>sAoe-qfVx</t>
+          <t>weWw-hC7q</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EYO38305</t>
+          <t>EWP70521</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>qbbV-unNd</t>
+          <t>sAoe-qfVx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FJV52310</t>
+          <t>EYO38305</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LbRC-0Q2b</t>
+          <t>qbbV-unNd</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FLQ72134</t>
+          <t>FJV52310</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Oj7z-iK7O</t>
+          <t>LbRC-0Q2b</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FNU34959</t>
+          <t>FLQ72134</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6Rb4-9itD</t>
+          <t>Oj7z-iK7O</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FOE41721</t>
+          <t>FNU34959</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SS6s-F64h</t>
+          <t>6Rb4-9itD</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FOJ78948</t>
+          <t>FOE41721</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>z4ZP-wYr2</t>
+          <t>SS6s-F64h</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FQP62630</t>
+          <t>FOJ78948</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>YPWV-F4Jw</t>
+          <t>z4ZP-wYr2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FRS19080</t>
+          <t>FQP62630</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>8lEh-Ggjd</t>
+          <t>YPWV-F4Jw</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FUSURIN1</t>
+          <t>FRS19080</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>sQd2-HCth</t>
+          <t>8lEh-Ggjd</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FVJ14662</t>
+          <t>FUSURIN1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Jr5l-rtxM</t>
+          <t>sQd2-HCth</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FWZ82980</t>
+          <t>FVJ14662</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Km0s-i1f3</t>
+          <t>Jr5l-rtxM</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FXB60927</t>
+          <t>FWZ82980</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>d20X-vLsV</t>
+          <t>Km0s-i1f3</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FXU60367</t>
+          <t>FXB60927</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>5JuP-8bMA</t>
+          <t>d20X-vLsV</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GBS06994</t>
+          <t>FXU60367</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SpZ6-7ylH</t>
+          <t>5JuP-8bMA</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GCV61524</t>
+          <t>GBS06994</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Xhaf-F9mT</t>
+          <t>SpZ6-7ylH</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GEL08954</t>
+          <t>GCV61524</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>zqti-TUKL</t>
+          <t>Xhaf-F9mT</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GEP48591</t>
+          <t>GEL08954</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ipb2-EtbP</t>
+          <t>zqti-TUKL</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GFN61654</t>
+          <t>GEP48591</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>nOpR-i46M</t>
+          <t>ipb2-EtbP</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GIE22684</t>
+          <t>GFN61654</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7YFY-lEPW</t>
+          <t>nOpR-i46M</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GKE90115</t>
+          <t>GIE22684</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ZK3R-ekIU</t>
+          <t>7YFY-lEPW</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GLG55164</t>
+          <t>GKE90115</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>rMri-gCbQ</t>
+          <t>ZK3R-ekIU</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GQG06884</t>
+          <t>GLG55164</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>yZSK-Cyby</t>
+          <t>rMri-gCbQ</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GSJ38697</t>
+          <t>GQG06884</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>dcc9-1DuY</t>
+          <t>yZSK-Cyby</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GSY94523</t>
+          <t>GSJ38697</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CykC-fp9I</t>
+          <t>dcc9-1DuY</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>GVD45273</t>
+          <t>GSY94523</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>kljF-Ogjz</t>
+          <t>CykC-fp9I</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GVM53776</t>
+          <t>GVD45273</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IUZs-UrSU</t>
+          <t>kljF-Ogjz</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HBP33017</t>
+          <t>GVM53776</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>D3ly-X1Qr</t>
+          <t>IUZs-UrSU</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HFX34792</t>
+          <t>HBP33017</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>gRZr-rn3f</t>
+          <t>D3ly-X1Qr</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HMD58733</t>
+          <t>HFX34792</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>jr4r-HFVO</t>
+          <t>gRZr-rn3f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HNS34640</t>
+          <t>HMD58733</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>dPb1-DHLF</t>
+          <t>jr4r-HFVO</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HPT02640</t>
+          <t>HNS34640</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>c2kk-PGg8</t>
+          <t>dPb1-DHLF</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HQH08532</t>
+          <t>HPT02640</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0fh0-QX5H</t>
+          <t>c2kk-PGg8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HRY29891</t>
+          <t>HQH08532</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>UjZ9-SZGT</t>
+          <t>0fh0-QX5H</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HTN73978</t>
+          <t>HRY29891</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>XTGO-sHtm</t>
+          <t>UjZ9-SZGT</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HWP25524</t>
+          <t>HTN73978</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>BWy7-13Ec</t>
+          <t>XTGO-sHtm</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>IAE88291</t>
+          <t>HWP25524</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>4Ceg-RIv5</t>
+          <t>BWy7-13Ec</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IFQ76747</t>
+          <t>IAE88291</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>3Rh9-wgj4</t>
+          <t>4Ceg-RIv5</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IGN23276</t>
+          <t>IFQ76747</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ZKGo-6azn</t>
+          <t>3Rh9-wgj4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>IGX57659</t>
+          <t>IGN23276</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>F8R5-Mhli</t>
+          <t>ZKGo-6azn</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ILO34901</t>
+          <t>IGX57659</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>VPO5-2Unw</t>
+          <t>F8R5-Mhli</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>IMW07942</t>
+          <t>ILO34901</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ors6-bajw</t>
+          <t>VPO5-2Unw</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IQI33918</t>
+          <t>IMW07942</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>quU8-kFRw</t>
+          <t>ors6-bajw</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>IUU53315</t>
+          <t>IQI33918</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>bHGN-Gt9k</t>
+          <t>quU8-kFRw</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>IWX83001</t>
+          <t>IUU53315</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0hfb-VytH</t>
+          <t>bHGN-Gt9k</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>JJI69427</t>
+          <t>IWX83001</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Mcpe-MdKl</t>
+          <t>0hfb-VytH</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>JMV12916</t>
+          <t>JJI69427</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>wFYF-qjdW</t>
+          <t>Mcpe-MdKl</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>JNQ15800</t>
+          <t>JMV12916</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>UOVA-N6XO</t>
+          <t>wFYF-qjdW</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>JSH83558</t>
+          <t>JNQ15800</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>NUAZ-lHPu</t>
+          <t>UOVA-N6XO</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>JSO81414</t>
+          <t>JSH83558</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2SfQ-XyEl</t>
+          <t>NUAZ-lHPu</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>JTN17189</t>
+          <t>JSO81414</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>wg9A-To8N</t>
+          <t>2SfQ-XyEl</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>JTQ20003</t>
+          <t>JTN17189</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>xXs3-0q1q</t>
+          <t>wg9A-To8N</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>KCH53154</t>
+          <t>JTQ20003</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>RwJm-IF1y</t>
+          <t>xXs3-0q1q</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KCH80368</t>
+          <t>KCH53154</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>j6lG-9k2c</t>
+          <t>RwJm-IF1y</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>KCS62207</t>
+          <t>KCH80368</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Ge7V-N1Fb</t>
+          <t>j6lG-9k2c</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>KNB79119</t>
+          <t>KCS62207</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>BRVy-AfTK</t>
+          <t>Ge7V-N1Fb</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>KPJ23941</t>
+          <t>KNB79119</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>qcjI-pNgm</t>
+          <t>BRVy-AfTK</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>KQT40874</t>
+          <t>KPJ23941</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>sgUM-aaYM</t>
+          <t>qcjI-pNgm</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>KRH18822</t>
+          <t>KQT40874</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>vMtE-4cYL</t>
+          <t>sgUM-aaYM</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>KTK81122</t>
+          <t>KRH18822</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>X8Dz-iKF1</t>
+          <t>vMtE-4cYL</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>KVA96952</t>
+          <t>KTK81122</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>VuFC-8E26</t>
+          <t>X8Dz-iKF1</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>KVU62139</t>
+          <t>KVA96952</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LUI5-Geov</t>
+          <t>VuFC-8E26</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KWN66857</t>
+          <t>KVU62139</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Fv4Y-68ZM</t>
+          <t>LUI5-Geov</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>KXZ79956</t>
+          <t>KWN66857</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>xmdQ-yw08</t>
+          <t>Fv4Y-68ZM</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>KZL99357</t>
+          <t>KXZ79956</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>14ZB-xFwZ</t>
+          <t>xmdQ-yw08</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>KZU53477</t>
+          <t>KZL99357</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>1qwx-jHLR</t>
+          <t>14ZB-xFwZ</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>LCT57577</t>
+          <t>KZU53477</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>bZjA-qnuE</t>
+          <t>1qwx-jHLR</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>LFA56301</t>
+          <t>LCT57577</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>trbu-XQWz</t>
+          <t>bZjA-qnuE</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>LGP73888</t>
+          <t>LFA56301</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>DcIT-TKtd</t>
+          <t>trbu-XQWz</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>LHQ57930</t>
+          <t>LGP73888</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>cRpb-1kZX</t>
+          <t>DcIT-TKtd</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>LJE73544</t>
+          <t>LHQ57930</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>c8yU-Zgju</t>
+          <t>cRpb-1kZX</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>LKG10504</t>
+          <t>LJE73544</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>t6Zj-7N4q</t>
+          <t>c8yU-Zgju</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>LLI56060</t>
+          <t>LKG10504</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ePiy-wSTy</t>
+          <t>t6Zj-7N4q</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>LPM87075</t>
+          <t>LLI56060</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>AgXC-arDZ</t>
+          <t>ePiy-wSTy</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MAI64055</t>
+          <t>LPM87075</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Mzqj-Ky8q</t>
+          <t>AgXC-arDZ</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MDE12029</t>
+          <t>MAI64055</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>hhXj-vBGM</t>
+          <t>Mzqj-Ky8q</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MEG11153</t>
+          <t>MDE12029</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>QThA-UkVH</t>
+          <t>hhXj-vBGM</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MIJ60289</t>
+          <t>MEG11153</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>YgVT-De6l</t>
+          <t>QThA-UkVH</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MND74401</t>
+          <t>MIJ60289</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ENc9-yDXA</t>
+          <t>YgVT-De6l</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MNW15780</t>
+          <t>MND74401</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6iUB-Vag7</t>
+          <t>ENc9-yDXA</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MRQ02763</t>
+          <t>MNW15780</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>jkZw-MaOb</t>
+          <t>6iUB-Vag7</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MUE50996</t>
+          <t>MRQ02763</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>UIda-nQtd</t>
+          <t>jkZw-MaOb</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MUX13896</t>
+          <t>MUE50996</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>r20R-BlFc</t>
+          <t>UIda-nQtd</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MXC93247</t>
+          <t>MUX13896</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>fcAI-rABo</t>
+          <t>r20R-BlFc</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MXM72788</t>
+          <t>MXC93247</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>iRyF-IaTc</t>
+          <t>fcAI-rABo</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MYD82527</t>
+          <t>MXM72788</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>1z7Z-Iwsk</t>
+          <t>iRyF-IaTc</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MYX47244</t>
+          <t>MYD82527</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>zpLV-zFXv</t>
+          <t>1z7Z-Iwsk</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>NAQ63112</t>
+          <t>MYX47244</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>vedO-3joS</t>
+          <t>zpLV-zFXv</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NCL61296</t>
+          <t>NAQ63112</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>MTj9-lIY8</t>
+          <t>vedO-3joS</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NDJ67099</t>
+          <t>NCL61296</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>hrBW-w842</t>
+          <t>MTj9-lIY8</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>NEE79704</t>
+          <t>NDJ67099</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>ed0x-qxBt</t>
+          <t>hrBW-w842</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NIQ43372</t>
+          <t>NEE79704</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>CXS1-PyNb</t>
+          <t>ed0x-qxBt</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>NLP67632</t>
+          <t>NIQ43372</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>b9F6-vbZ5</t>
+          <t>CXS1-PyNb</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>NPD00961</t>
+          <t>NLP67632</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>aI8u-zYiw</t>
+          <t>b9F6-vbZ5</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NUI19784</t>
+          <t>NPD00961</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>mF1f-kCQW</t>
+          <t>aI8u-zYiw</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>NWX06153</t>
+          <t>NUI19784</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>N3G4-xe8w</t>
+          <t>mF1f-kCQW</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>NYF03161</t>
+          <t>NWX06153</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>zMxQ-K0fi</t>
+          <t>N3G4-xe8w</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>NZW46214</t>
+          <t>NYF03161</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>09st-zHFg</t>
+          <t>zMxQ-K0fi</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>NZZ50766</t>
+          <t>NZW46214</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>XINJ-KGsC</t>
+          <t>09st-zHFg</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OAM83746</t>
+          <t>NZZ50766</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>56vK-YHjW</t>
+          <t>XINJ-KGsC</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>OBI75581</t>
+          <t>OAM83746</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Mygc-BSFY</t>
+          <t>56vK-YHjW</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ODU01918</t>
+          <t>OBI75581</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>ia7S-FLGr</t>
+          <t>Mygc-BSFY</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>OEJ86175</t>
+          <t>ODU01918</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>XJIi-fHfZ</t>
+          <t>ia7S-FLGr</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>OKY47911</t>
+          <t>OEJ86175</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>uSoZ-cHIn</t>
+          <t>XJIi-fHfZ</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ORR85927</t>
+          <t>OKY47911</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>JgtA-rF6p</t>
+          <t>uSoZ-cHIn</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ORT63362</t>
+          <t>ORR85927</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>XZT6-FxOF</t>
+          <t>JgtA-rF6p</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>OSB52441</t>
+          <t>ORT63362</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>I1Cv-DmRA</t>
+          <t>XZT6-FxOF</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>OWO93746</t>
+          <t>OSB52441</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>hGwl-3fWL</t>
+          <t>I1Cv-DmRA</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>OWR55957</t>
+          <t>OWO93746</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>5xs5-2GVm</t>
+          <t>hGwl-3fWL</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>OXE34055</t>
+          <t>OWR55957</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>QMAt-FrNE</t>
+          <t>5xs5-2GVm</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>OXH82758</t>
+          <t>OXE34055</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>dBG6-1GKl</t>
+          <t>QMAt-FrNE</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>OXK70326</t>
+          <t>OXH82758</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Gkyl-27Tv</t>
+          <t>dBG6-1GKl</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>OYK39161</t>
+          <t>OXK70326</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>nDoT-dKaH</t>
+          <t>Gkyl-27Tv</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>OYZ43696</t>
+          <t>OYK39161</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>NE1A-0H4Y</t>
+          <t>nDoT-dKaH</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PDL18808</t>
+          <t>OYZ43696</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>AyIU-xTfq</t>
+          <t>NE1A-0H4Y</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PDY46515</t>
+          <t>PDL18808</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Gg8E-S2pr</t>
+          <t>AyIU-xTfq</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PEP57928</t>
+          <t>PDY46515</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>o921-Slsb</t>
+          <t>Gg8E-S2pr</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PHT01595</t>
+          <t>PEP57928</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>w3qg-ZFCf</t>
+          <t>o921-Slsb</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PJT16152</t>
+          <t>PHT01595</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>ExFD-xCid</t>
+          <t>w3qg-ZFCf</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PLL97657</t>
+          <t>PJT16152</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>NWjX-D2LF</t>
+          <t>ExFD-xCid</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PSM82237</t>
+          <t>PLL97657</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>eY7P-J7N7</t>
+          <t>NWjX-D2LF</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PVU41752</t>
+          <t>PSM82237</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>ugqe-Crjb</t>
+          <t>eY7P-J7N7</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PWD33511</t>
+          <t>PVU41752</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>kAEm-3um0</t>
+          <t>ugqe-Crjb</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>QFN79396</t>
+          <t>PWD33511</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>jXUf-ZSmc</t>
+          <t>kAEm-3um0</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>QFU06512</t>
+          <t>QFN79396</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>MNwE-V6p6</t>
+          <t>jXUf-ZSmc</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>QHB18956</t>
+          <t>QFU06512</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>B4nt-rvpd</t>
+          <t>MNwE-V6p6</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>QKM89908</t>
+          <t>QHB18956</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>bL4O-ckL6</t>
+          <t>B4nt-rvpd</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>QRB56514</t>
+          <t>QKM89908</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ZmLU-WzDm</t>
+          <t>bL4O-ckL6</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>QUE22078</t>
+          <t>QRB56514</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>tCyA-Oi7m</t>
+          <t>ZmLU-WzDm</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>QVI53832</t>
+          <t>QUE22078</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>eBOh-GY3U</t>
+          <t>tCyA-Oi7m</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>QYS77373</t>
+          <t>QVI53832</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>bdKc-q4v6</t>
+          <t>eBOh-GY3U</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>QYU41690</t>
+          <t>QYS77373</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>UyLP-qGWT</t>
+          <t>bdKc-q4v6</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RAL78524</t>
+          <t>QYU41690</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>4RvF-k9n0</t>
+          <t>UyLP-qGWT</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RBA20127</t>
+          <t>RAL78524</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>oE79-b1Se</t>
+          <t>4RvF-k9n0</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RER39252</t>
+          <t>RBA20127</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>cNTo-jOTf</t>
+          <t>oE79-b1Se</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>RFD76685</t>
+          <t>RER39252</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ZHtK-ciCM</t>
+          <t>cNTo-jOTf</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>RLQ73857</t>
+          <t>RFD76685</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>QZVO-4p3B</t>
+          <t>ZHtK-ciCM</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>RMV88503</t>
+          <t>RLQ73857</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>fQqP-39VA</t>
+          <t>QZVO-4p3B</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>RNL06004</t>
+          <t>RMV88503</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>WaLc-sBJY</t>
+          <t>fQqP-39VA</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>RQV81451</t>
+          <t>RNL06004</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>asPu-gWes</t>
+          <t>WaLc-sBJY</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>RSN71799</t>
+          <t>RQV81451</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>APKz-8tHA</t>
+          <t>asPu-gWes</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>RSV50349</t>
+          <t>RSN71799</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>gUKK-rzSk</t>
+          <t>APKz-8tHA</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>RVG62147</t>
+          <t>RSV50349</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>cqJ7-uz8x</t>
+          <t>gUKK-rzSk</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SAF98648</t>
+          <t>RVG62147</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>JUDx-dQqy</t>
+          <t>cqJ7-uz8x</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SDE98641</t>
+          <t>SAF98648</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>E4LL-qV7u</t>
+          <t>JUDx-dQqy</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SEV98034</t>
+          <t>SDE98641</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>3FMv-ztV8</t>
+          <t>E4LL-qV7u</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SGE51092</t>
+          <t>SEV98034</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>9G7O-tS42</t>
+          <t>3FMv-ztV8</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SGY00276</t>
+          <t>SGE51092</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>GGz3-kW7s</t>
+          <t>9G7O-tS42</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SLP43775</t>
+          <t>SGY00276</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JIk1-QTjm</t>
+          <t>GGz3-kW7s</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SMF79012</t>
+          <t>SLP43775</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>NcnL-Ufev</t>
+          <t>JIk1-QTjm</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SNZ44527</t>
+          <t>SMF79012</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Idtr-Ef1p</t>
+          <t>NcnL-Ufev</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SPL79883</t>
+          <t>SNZ44527</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>vFIR-WuRr</t>
+          <t>Idtr-Ef1p</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SPZ85652</t>
+          <t>SPL79883</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>BqNU-jKbs</t>
+          <t>vFIR-WuRr</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SQX65443</t>
+          <t>SPZ85652</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>2Y2u-Iexu</t>
+          <t>BqNU-jKbs</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SSU10232</t>
+          <t>SQX65443</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2s1b-MrBM</t>
+          <t>2Y2u-Iexu</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SWB32390</t>
+          <t>SSU10232</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>bPkJ-04s3</t>
+          <t>2s1b-MrBM</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SXZ01554</t>
+          <t>SWB32390</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>pE9E-t8do</t>
+          <t>bPkJ-04s3</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SYH46751</t>
+          <t>SXZ01554</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>g47k-j3HG</t>
+          <t>pE9E-t8do</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>TFD08485</t>
+          <t>SYH46751</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>657O-VCk5</t>
+          <t>g47k-j3HG</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TGM55607</t>
+          <t>TFD08485</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>wiKV-5PZ7</t>
+          <t>657O-VCk5</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TKW11810</t>
+          <t>TGM55607</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>XbfA-yocA</t>
+          <t>wiKV-5PZ7</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>TME86867</t>
+          <t>TKW11810</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>WM5K-oBsD</t>
+          <t>XbfA-yocA</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>TMJ36970</t>
+          <t>TME86867</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>NiMt-vJm1</t>
+          <t>WM5K-oBsD</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>TRC98148</t>
+          <t>TMJ36970</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ImK9-sJVr</t>
+          <t>NiMt-vJm1</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>TTS04230</t>
+          <t>TRC98148</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>oJvJ-C0eE</t>
+          <t>ImK9-sJVr</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>TXC42578</t>
+          <t>TTS04230</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>ttrI-HkEA</t>
+          <t>oJvJ-C0eE</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>UIB17642</t>
+          <t>TXC42578</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>huhE-ve6K</t>
+          <t>ttrI-HkEA</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>UOI75021</t>
+          <t>UIB17642</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>DQg2-NKBW</t>
+          <t>huhE-ve6K</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>UUR79971</t>
+          <t>UOI75021</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>2Vvw-yPgX</t>
+          <t>DQg2-NKBW</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>VDD06679</t>
+          <t>UUR79971</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>9NFD-F33z</t>
+          <t>2Vvw-yPgX</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>VEC51795</t>
+          <t>VDD06679</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>ePpy-45qF</t>
+          <t>9NFD-F33z</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>VEQ81429</t>
+          <t>VEC51795</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>xnGV-gtxP</t>
+          <t>ePpy-45qF</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>VHB06952</t>
+          <t>VEQ81429</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>0muJ-HK7N</t>
+          <t>xnGV-gtxP</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>VPE32737</t>
+          <t>VHB06952</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>83SX-bO49</t>
+          <t>0muJ-HK7N</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>VSG31611</t>
+          <t>VPE32737</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>DUQt-pvMj</t>
+          <t>83SX-bO49</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>VYM86842</t>
+          <t>VSG31611</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>0Veq-1X2d</t>
+          <t>DUQt-pvMj</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>WEO81262</t>
+          <t>VYM86842</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>L7ui-NKjF</t>
+          <t>0Veq-1X2d</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>WHV65431</t>
+          <t>WEO81262</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>hZeN-SKfM</t>
+          <t>L7ui-NKjF</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>WJH36041</t>
+          <t>WHV65431</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>yPk4-9kvI</t>
+          <t>hZeN-SKfM</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>WNA57398</t>
+          <t>WJH36041</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>CU9v-k8Hc</t>
+          <t>yPk4-9kvI</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>WQS25133</t>
+          <t>WNA57398</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Mg1K-yzvr</t>
+          <t>CU9v-k8Hc</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>WUA13603</t>
+          <t>WQS25133</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>hdCj-fLq2</t>
+          <t>Mg1K-yzvr</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>WUH93925</t>
+          <t>WUA13603</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>8m3J-Gzlk</t>
+          <t>hdCj-fLq2</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>WVY21466</t>
+          <t>WUH93925</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>uDNr-H0pJ</t>
+          <t>8m3J-Gzlk</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>WWS24235</t>
+          <t>WVY21466</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>dTMF-Ocal</t>
+          <t>uDNr-H0pJ</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>XED10282</t>
+          <t>WWS24235</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>vWlv-tJFL</t>
+          <t>dTMF-Ocal</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>XKS75480</t>
+          <t>XED10282</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>c0hS-CdvD</t>
+          <t>vWlv-tJFL</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>XOA75961</t>
+          <t>XKS75480</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>VRah-kBaa</t>
+          <t>c0hS-CdvD</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>XOS17378</t>
+          <t>XOA75961</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>vOQe-IMOh</t>
+          <t>VRah-kBaa</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>XRM79618</t>
+          <t>XOS17378</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>brgl-xEFq</t>
+          <t>vOQe-IMOh</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>XSL75240</t>
+          <t>XRM79618</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>71I9-XlWo</t>
+          <t>brgl-xEFq</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>XYT33259</t>
+          <t>XSL75240</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>ahUH-85T2</t>
+          <t>71I9-XlWo</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>XYZ70850</t>
+          <t>XYT33259</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>jdV6-HalU</t>
+          <t>ahUH-85T2</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>XZC74148</t>
+          <t>XYZ70850</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>0GQn-L0M5</t>
+          <t>jdV6-HalU</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>YBX87679</t>
+          <t>XZC74148</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>442D-goVh</t>
+          <t>0GQn-L0M5</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>YCN31679</t>
+          <t>YBX87679</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>SBfE-010a</t>
+          <t>442D-goVh</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>YEK78642</t>
+          <t>YCN31679</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>QkIs-wR1T</t>
+          <t>SBfE-010a</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>YFU10307</t>
+          <t>YEK78642</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>pv8C-S2qP</t>
+          <t>QkIs-wR1T</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>YGP30798</t>
+          <t>YFU10307</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>dZEv-nHKw</t>
+          <t>pv8C-S2qP</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>YHZ51082</t>
+          <t>YGP30798</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>7j63-7HKa</t>
+          <t>dZEv-nHKw</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>YOT12953</t>
+          <t>YHZ51082</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>SxGc-ZaIN</t>
+          <t>7j63-7HKa</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>ZAM21080</t>
+          <t>YOT12953</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>COFy-pMla</t>
+          <t>SxGc-ZaIN</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ZFB81591</t>
+          <t>ZAM21080</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>RPpW-yrd5</t>
+          <t>COFy-pMla</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>ZHU54125</t>
+          <t>ZFB81591</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>5RJe-0r17</t>
+          <t>RPpW-yrd5</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>ZLP77106</t>
+          <t>ZHU54125</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>djSn-TgS9</t>
+          <t>5RJe-0r17</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>ZNA23106</t>
+          <t>ZLP77106</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>SHid-kPC3</t>
+          <t>djSn-TgS9</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>ZPU29378</t>
+          <t>ZNA23106</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>tb6L-01Ac</t>
+          <t>SHid-kPC3</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>ZSU27095</t>
+          <t>ZPU29378</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>3TQp-7e2s</t>
+          <t>tb6L-01Ac</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
+          <t>ZSU27095</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>3TQp-7e2s</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
           <t>ZVK04224</t>
         </is>
       </c>
-      <c r="B265" t="inlineStr">
+      <c r="B266" t="inlineStr">
         <is>
           <t>9gaA-gLOl</t>
         </is>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B266"/>
+  <dimension ref="A1:B251"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>aRyD-3qVo</t>
+          <t>7x7N-CByY</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>zccK-zlnr</t>
+          <t>8eig-ubih</t>
         </is>
       </c>
     </row>
@@ -472,3151 +472,2971 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>bQGY-vJlV</t>
+          <t>i7i0-e8kj</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AEF48923</t>
+          <t>AJF14211</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>zzMB-6A6j</t>
+          <t>QTDp-w4Ul</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AJF14211</t>
+          <t>AMX72670</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CM6y-aUuk</t>
+          <t>8RIT-6eGj</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMX72670</t>
+          <t>ANW71835</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>VEGx-hurW</t>
+          <t>Gw4k-eVdh</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ANW71835</t>
+          <t>ARC48959</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BuMC-7KDd</t>
+          <t>0sus-cISx</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARC48959</t>
+          <t>ARL55178</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CK7z-JVnw</t>
+          <t>28sS-bH73</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ARL55178</t>
+          <t>AVJ39759</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VwlE-Pvk6</t>
+          <t>qWtK-DL52</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AVJ39759</t>
+          <t>AXM21790</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>utY7-yET8</t>
+          <t>RKoN-BLdg</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AXM21790</t>
+          <t>AZJ82844</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>awKz-Dbz4</t>
+          <t>CkIk-L3vB</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AZJ82844</t>
+          <t>BBA65823</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>G2cX-0SFe</t>
+          <t>k7oY-1K9F</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>BFI60670</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>A1234</t>
+          <t>Tz1e-eJnf</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BBA65823</t>
+          <t>BGG58729</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>8InB-77sx</t>
+          <t>jd8A-U0X4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BFI60670</t>
+          <t>BJH88419</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>iOpa-quCx</t>
+          <t>DkdX-43ju</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BGG58729</t>
+          <t>BJW79616</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3RgL-WsLQ</t>
+          <t>eeke-VFFW</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BJH88419</t>
+          <t>BOI99795</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JwOH-onjo</t>
+          <t>JkgN-Q0tw</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BJW79616</t>
+          <t>BOZ64205</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>qjD9-x9pp</t>
+          <t>fU3x-314s</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BOI99795</t>
+          <t>BQV35355</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>cUwY-oMGA</t>
+          <t>4PKO-EkoE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BOZ64205</t>
+          <t>BUR49898</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cqic-pxFH</t>
+          <t>W5lR-IDy9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BQV35355</t>
+          <t>CBP36635</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>AMpg-NzcS</t>
+          <t>5CYi-2g29</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BUR49898</t>
+          <t>CDG44201</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>uP55-nNU2</t>
+          <t>qAo6-xUOY</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CBP36635</t>
+          <t>CEG78579</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>3o0E-H0eS</t>
+          <t>QC9b-Krx2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CDG44201</t>
+          <t>CEV66266</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Z9V4-FCw2</t>
+          <t>HKm0-UrGK</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CEG78579</t>
+          <t>CEX73283</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>oGuY-hS6y</t>
+          <t>jKkT-uw8G</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CEV66266</t>
+          <t>CGK70284</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>595F-5DPV</t>
+          <t>yC6J-NtKX</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CEX73283</t>
+          <t>CGY86131</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BvrE-h4h6</t>
+          <t>iesr-mHIv</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CGK70284</t>
+          <t>CHZ14322</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>cgTX-Z1ru</t>
+          <t>vA2K-I0j8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CGY86131</t>
+          <t>CMY62163</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5EJ5-nSOu</t>
+          <t>W358-deTm</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CHZ14322</t>
+          <t>CNJ73848</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>rJ50-xReo</t>
+          <t>Q2B9-GZ4n</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CMY62163</t>
+          <t>CNQ05106</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>X7qM-afE3</t>
+          <t>aJ1r-FHI5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CNJ73848</t>
+          <t>CQL05471</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>uyHI-dehW</t>
+          <t>DvlB-F5Tt</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CNQ05106</t>
+          <t>CQV21480</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JKLS-ZXPj</t>
+          <t>Jtoe-rd80</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CQL05471</t>
+          <t>CST44061</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>k8LF-oP5k</t>
+          <t>fZCQ-1wPj</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CQV21480</t>
+          <t>CWI21231</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>fPzD-uk5D</t>
+          <t>Vuqk-89L0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CST44061</t>
+          <t>CWI74996</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1Xg7-FxRM</t>
+          <t>rljY-Fzhm</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CWI21231</t>
+          <t>CXY21844</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>VERb-T6sQ</t>
+          <t>iBYD-sA2l</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CWI74996</t>
+          <t>CYN09662</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>iP3y-7uci</t>
+          <t>2bSg-DXbe</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CXY21844</t>
+          <t>DCC25940</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>nAFY-KtfZ</t>
+          <t>HQuT-cXpZ</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CYB55817</t>
+          <t>DEI55654</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>kyA4-BHSa</t>
+          <t>J0AS-zb82</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CYN09662</t>
+          <t>DGL58063</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>unqS-753q</t>
+          <t>fkog-ixB2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DCC25940</t>
+          <t>DHH79187</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>9X56-vHTG</t>
+          <t>0wjM-DXVa</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DEI55654</t>
+          <t>DJK20638</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>dpkR-1tH2</t>
+          <t>RAcn-mP9A</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DGL58063</t>
+          <t>DLF24523</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>lQpJ-cvmL</t>
+          <t>R9tM-c1TI</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DHH79187</t>
+          <t>DLP45053</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>kp6O-nXp3</t>
+          <t>wesf-67x6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DJK20638</t>
+          <t>DQD33133</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ZJAv-brF5</t>
+          <t>At1f-Lruc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DLF24523</t>
+          <t>DTZ69845</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1Fps-H1ZW</t>
+          <t>smd1-VlnM</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DLP45053</t>
+          <t>DUA61401</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>L7sf-MoLb</t>
+          <t>D6mr-DCYd</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DQD33133</t>
+          <t>DVJ66295</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>WX5H-LiPX</t>
+          <t>dbjW-kvqB</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DTZ69845</t>
+          <t>DXM69578</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FiA8-mFOt</t>
+          <t>tDDW-iTON</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DUA61401</t>
+          <t>DZI77349</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2vrj-OFZH</t>
+          <t>IpeV-V3uk</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DVJ66295</t>
+          <t>EBT22822</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>8Bl3-qRML</t>
+          <t>wFj5-Viny</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DXM69578</t>
+          <t>ECG95521</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>gt5b-TF6d</t>
+          <t>yH7e-sQgN</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DZI77349</t>
+          <t>EWP70521</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>exKl-ZgTI</t>
+          <t>5pf7-KpLl</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EBT22822</t>
+          <t>EYO38305</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2lhq-XPz5</t>
+          <t>DCIA-x6gX</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ECG95521</t>
+          <t>FJV52310</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>weWw-hC7q</t>
+          <t>3kSr-gmCf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EWP70521</t>
+          <t>FLQ72134</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>sAoe-qfVx</t>
+          <t>52xk-RT2i</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EYO38305</t>
+          <t>FNU34959</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>qbbV-unNd</t>
+          <t>W5NW-tqJZ</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FJV52310</t>
+          <t>FOE41721</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>LbRC-0Q2b</t>
+          <t>OU26-hkn9</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FLQ72134</t>
+          <t>FOJ78948</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Oj7z-iK7O</t>
+          <t>NJQe-rjle</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FNU34959</t>
+          <t>FQP62630</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6Rb4-9itD</t>
+          <t>vZrW-7GKt</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FOE41721</t>
+          <t>FUSURIN1</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SS6s-F64h</t>
+          <t>Wv4p-cau5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FOJ78948</t>
+          <t>FVJ14662</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>z4ZP-wYr2</t>
+          <t>N79x-nKo6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FQP62630</t>
+          <t>FWZ82980</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>YPWV-F4Jw</t>
+          <t>qgWf-rHvd</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FRS19080</t>
+          <t>FXB60927</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>8lEh-Ggjd</t>
+          <t>gCHc-CCdL</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FUSURIN1</t>
+          <t>FXU60367</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>sQd2-HCth</t>
+          <t>fPHc-oxtP</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FVJ14662</t>
+          <t>GBS06994</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jr5l-rtxM</t>
+          <t>d7GQ-v6S7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FWZ82980</t>
+          <t>GCV61524</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Km0s-i1f3</t>
+          <t>w5a4-Jc1l</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FXB60927</t>
+          <t>GEL08954</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>d20X-vLsV</t>
+          <t>iqBH-ARJW</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>FXU60367</t>
+          <t>GEP48591</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5JuP-8bMA</t>
+          <t>Ts7J-llLb</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GBS06994</t>
+          <t>GFN61654</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SpZ6-7ylH</t>
+          <t>hMLy-CFVC</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GCV61524</t>
+          <t>GIE22684</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Xhaf-F9mT</t>
+          <t>eZnK-oWlU</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GEL08954</t>
+          <t>GKE90115</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>zqti-TUKL</t>
+          <t>nRrT-z0aK</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GEP48591</t>
+          <t>GLG55164</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ipb2-EtbP</t>
+          <t>OZct-hAV2</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GFN61654</t>
+          <t>GQG06884</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>nOpR-i46M</t>
+          <t>oHVZ-Ub10</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GIE22684</t>
+          <t>GSY94523</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7YFY-lEPW</t>
+          <t>7lym-qKjk</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GKE90115</t>
+          <t>GVD45273</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ZK3R-ekIU</t>
+          <t>JAQE-asZl</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GLG55164</t>
+          <t>GVM53776</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>rMri-gCbQ</t>
+          <t>yB0f-59Hv</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GQG06884</t>
+          <t>HBP33017</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>yZSK-Cyby</t>
+          <t>qf6t-5pFD</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GSJ38697</t>
+          <t>HFX34792</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>dcc9-1DuY</t>
+          <t>MHzA-t35v</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>GSY94523</t>
+          <t>HMD58733</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>CykC-fp9I</t>
+          <t>sJeO-zseo</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>GVD45273</t>
+          <t>HNS34640</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>kljF-Ogjz</t>
+          <t>MZTs-CGSN</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>GVM53776</t>
+          <t>HPT02640</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>IUZs-UrSU</t>
+          <t>MgKF-XVd0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HBP33017</t>
+          <t>HQH08532</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>D3ly-X1Qr</t>
+          <t>UJ8m-II3K</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HFX34792</t>
+          <t>HRY29891</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>gRZr-rn3f</t>
+          <t>xdCz-HH09</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HMD58733</t>
+          <t>HTN73978</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>jr4r-HFVO</t>
+          <t>6Xz1-cnCb</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HNS34640</t>
+          <t>HWP25524</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>dPb1-DHLF</t>
+          <t>htg0-Tvd1</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HPT02640</t>
+          <t>IAE88291</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>c2kk-PGg8</t>
+          <t>EjNm-iddY</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HQH08532</t>
+          <t>IFQ76747</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0fh0-QX5H</t>
+          <t>vpRK-WNI2</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HRY29891</t>
+          <t>IGN23276</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>UjZ9-SZGT</t>
+          <t>teQH-pR1T</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HTN73978</t>
+          <t>IGX57659</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>XTGO-sHtm</t>
+          <t>RyFz-M4ZM</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>HWP25524</t>
+          <t>ILO34901</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BWy7-13Ec</t>
+          <t>Klch-z5dR</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IAE88291</t>
+          <t>IMW07942</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>4Ceg-RIv5</t>
+          <t>Tc2A-XvL1</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IFQ76747</t>
+          <t>IQI33918</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>3Rh9-wgj4</t>
+          <t>UfRV-Jp6H</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>IGN23276</t>
+          <t>IUU53315</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>ZKGo-6azn</t>
+          <t>rrc0-FNhr</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>IGX57659</t>
+          <t>IWX83001</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>F8R5-Mhli</t>
+          <t>F5RM-C69k</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ILO34901</t>
+          <t>JJI69427</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>VPO5-2Unw</t>
+          <t>eWAA-JT4U</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IMW07942</t>
+          <t>JMV12916</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ors6-bajw</t>
+          <t>Aena-f214</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>IQI33918</t>
+          <t>JNQ15800</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>quU8-kFRw</t>
+          <t>oUX6-LAT7</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>IUU53315</t>
+          <t>JSH83558</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>bHGN-Gt9k</t>
+          <t>1qCN-8Dez</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>IWX83001</t>
+          <t>JSO81414</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0hfb-VytH</t>
+          <t>pcYj-Faea</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>JJI69427</t>
+          <t>JTN17189</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Mcpe-MdKl</t>
+          <t>lWHk-2q6W</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>JMV12916</t>
+          <t>JTQ20003</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>wFYF-qjdW</t>
+          <t>TrQD-Bx9T</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>JNQ15800</t>
+          <t>KCH80368</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>UOVA-N6XO</t>
+          <t>RK4o-Y4YY</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>JSH83558</t>
+          <t>KCS62207</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NUAZ-lHPu</t>
+          <t>oUnE-AlE8</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>JSO81414</t>
+          <t>KNB79119</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2SfQ-XyEl</t>
+          <t>O0XY-kES6</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>JTN17189</t>
+          <t>KPJ23941</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>wg9A-To8N</t>
+          <t>V3JI-Zd0w</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>JTQ20003</t>
+          <t>KTK81122</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>xXs3-0q1q</t>
+          <t>CHG0-TMTH</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KCH53154</t>
+          <t>KVA96952</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>RwJm-IF1y</t>
+          <t>cm2V-8B6C</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>KCH80368</t>
+          <t>KVU62139</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>j6lG-9k2c</t>
+          <t>R30J-cy5a</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>KCS62207</t>
+          <t>KWN66857</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ge7V-N1Fb</t>
+          <t>0WUn-m5Ol</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>KNB79119</t>
+          <t>KZL99357</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BRVy-AfTK</t>
+          <t>MPY4-LkcS</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>KPJ23941</t>
+          <t>KZU53477</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>qcjI-pNgm</t>
+          <t>ubLD-oa3e</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>KQT40874</t>
+          <t>LCT57577</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>sgUM-aaYM</t>
+          <t>ITlt-bhSB</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>KRH18822</t>
+          <t>LFA56301</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>vMtE-4cYL</t>
+          <t>Qcbr-l0pO</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>KTK81122</t>
+          <t>LHQ57930</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>X8Dz-iKF1</t>
+          <t>YFze-wczu</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>KVA96952</t>
+          <t>LJE73544</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>VuFC-8E26</t>
+          <t>Pjc5-sLHz</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>KVU62139</t>
+          <t>LKG10504</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>LUI5-Geov</t>
+          <t>5aga-eHr2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>KWN66857</t>
+          <t>LLI56060</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Fv4Y-68ZM</t>
+          <t>tLTE-S3eY</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>KXZ79956</t>
+          <t>LPM87075</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>xmdQ-yw08</t>
+          <t>XYqU-BdEI</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>KZL99357</t>
+          <t>MAI64055</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>14ZB-xFwZ</t>
+          <t>I5FA-YJBe</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>KZU53477</t>
+          <t>MDE12029</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1qwx-jHLR</t>
+          <t>N6a6-umQW</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>LCT57577</t>
+          <t>MEG11153</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>bZjA-qnuE</t>
+          <t>b7uV-Kw5y</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>LFA56301</t>
+          <t>MIJ60289</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>trbu-XQWz</t>
+          <t>FxU2-TC3u</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>LGP73888</t>
+          <t>MND74401</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>DcIT-TKtd</t>
+          <t>JmQg-IDSH</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>LHQ57930</t>
+          <t>MNW15780</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>cRpb-1kZX</t>
+          <t>Jxms-wTtT</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>LJE73544</t>
+          <t>MRQ02763</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>c8yU-Zgju</t>
+          <t>OVrZ-hLXn</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>LKG10504</t>
+          <t>MUX13896</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>t6Zj-7N4q</t>
+          <t>m1Tj-BneA</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>LLI56060</t>
+          <t>MXC93247</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>ePiy-wSTy</t>
+          <t>lGMJ-8v0U</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>LPM87075</t>
+          <t>MXM72788</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>AgXC-arDZ</t>
+          <t>mhWI-yFlB</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MAI64055</t>
+          <t>MYD82527</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Mzqj-Ky8q</t>
+          <t>mZ2I-9GVo</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MDE12029</t>
+          <t>MYX47244</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>hhXj-vBGM</t>
+          <t>t3KY-YCGx</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MEG11153</t>
+          <t>NAQ63112</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>QThA-UkVH</t>
+          <t>xuiH-o5ew</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MIJ60289</t>
+          <t>NCL61296</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>YgVT-De6l</t>
+          <t>7nfV-khpG</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MND74401</t>
+          <t>NDJ67099</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ENc9-yDXA</t>
+          <t>eB1m-bEK1</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MNW15780</t>
+          <t>NEE79704</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>6iUB-Vag7</t>
+          <t>Qoxm-C6e0</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>MRQ02763</t>
+          <t>NIQ43372</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>jkZw-MaOb</t>
+          <t>Pgff-sZV0</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>MUE50996</t>
+          <t>NLP67632</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>UIda-nQtd</t>
+          <t>G26I-YJvn</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>MUX13896</t>
+          <t>NPD00961</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>r20R-BlFc</t>
+          <t>dGx0-g7i7</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>MXC93247</t>
+          <t>NUI19784</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>fcAI-rABo</t>
+          <t>KjYw-2ZeV</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>MXM72788</t>
+          <t>NWX06153</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>iRyF-IaTc</t>
+          <t>0FKv-DaZa</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>MYD82527</t>
+          <t>NYF03161</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1z7Z-Iwsk</t>
+          <t>MRRm-gI9q</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>MYX47244</t>
+          <t>NZW46214</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>zpLV-zFXv</t>
+          <t>jgd9-Nw5i</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NAQ63112</t>
+          <t>OAM83746</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>vedO-3joS</t>
+          <t>p43U-422C</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NCL61296</t>
+          <t>OBI75581</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>MTj9-lIY8</t>
+          <t>lrAR-L75c</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>NDJ67099</t>
+          <t>ODU01918</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>hrBW-w842</t>
+          <t>Rcwk-E1qr</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NEE79704</t>
+          <t>OEJ86175</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ed0x-qxBt</t>
+          <t>rpo8-FfdU</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>NIQ43372</t>
+          <t>OKY47911</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>CXS1-PyNb</t>
+          <t>WRyX-WvR5</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>NLP67632</t>
+          <t>ORR85927</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>b9F6-vbZ5</t>
+          <t>yCyK-gWSp</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>NPD00961</t>
+          <t>ORT63362</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>aI8u-zYiw</t>
+          <t>MMBi-X00f</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>NUI19784</t>
+          <t>OSB52441</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>mF1f-kCQW</t>
+          <t>ECpb-JeTn</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>NWX06153</t>
+          <t>OWO93746</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>N3G4-xe8w</t>
+          <t>Rsm2-G5Ea</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>NYF03161</t>
+          <t>OWR55957</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>zMxQ-K0fi</t>
+          <t>eVIV-cqgo</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>NZW46214</t>
+          <t>OXE34055</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>09st-zHFg</t>
+          <t>H3yH-x89x</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>NZZ50766</t>
+          <t>OXH82758</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>XINJ-KGsC</t>
+          <t>XG5T-OT4H</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>OAM83746</t>
+          <t>OXK70326</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>56vK-YHjW</t>
+          <t>p1ZP-spZX</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>OBI75581</t>
+          <t>OYK39161</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Mygc-BSFY</t>
+          <t>v7Br-YvYY</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ODU01918</t>
+          <t>OYZ43696</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>ia7S-FLGr</t>
+          <t>H87b-wCME</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>OEJ86175</t>
+          <t>PDL18808</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>XJIi-fHfZ</t>
+          <t>Wfoy-O83h</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>OKY47911</t>
+          <t>PDY46515</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>uSoZ-cHIn</t>
+          <t>X9Fr-wj93</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>ORR85927</t>
+          <t>PHT01595</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>JgtA-rF6p</t>
+          <t>PLJT-gdQI</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>ORT63362</t>
+          <t>PJT16152</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>XZT6-FxOF</t>
+          <t>19wH-4KKj</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>OSB52441</t>
+          <t>PLL97657</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>I1Cv-DmRA</t>
+          <t>TFqR-oQcQ</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>OWO93746</t>
+          <t>PSM82237</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>hGwl-3fWL</t>
+          <t>1EKx-iXrp</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>OWR55957</t>
+          <t>PVU41752</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5xs5-2GVm</t>
+          <t>kHlv-oMQv</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>OXE34055</t>
+          <t>PWD33511</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>QMAt-FrNE</t>
+          <t>bO63-HhLX</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>OXH82758</t>
+          <t>QFN79396</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>dBG6-1GKl</t>
+          <t>XfwW-8gPx</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>OXK70326</t>
+          <t>QHB18956</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Gkyl-27Tv</t>
+          <t>K3FX-lsng</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>OYK39161</t>
+          <t>QKM89908</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>nDoT-dKaH</t>
+          <t>8izY-kkwJ</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>OYZ43696</t>
+          <t>QRB56514</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>NE1A-0H4Y</t>
+          <t>xweI-ZTse</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PDL18808</t>
+          <t>QUE22078</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>AyIU-xTfq</t>
+          <t>Zj9K-11ez</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PDY46515</t>
+          <t>QVI53832</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Gg8E-S2pr</t>
+          <t>eAYI-1Lul</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PEP57928</t>
+          <t>QYS77373</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>o921-Slsb</t>
+          <t>nnZt-RXf2</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PHT01595</t>
+          <t>QYU41690</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>w3qg-ZFCf</t>
+          <t>VKU3-fltH</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PJT16152</t>
+          <t>RAL78524</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ExFD-xCid</t>
+          <t>3HFU-5jAS</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PLL97657</t>
+          <t>RBA20127</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>NWjX-D2LF</t>
+          <t>k8Ub-RvYM</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PSM82237</t>
+          <t>RER39252</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>eY7P-J7N7</t>
+          <t>oIRY-HIGt</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PVU41752</t>
+          <t>RFD76685</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>ugqe-Crjb</t>
+          <t>Z6Uz-KOt4</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PWD33511</t>
+          <t>RLQ73857</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>kAEm-3um0</t>
+          <t>VVBl-kyCk</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>QFN79396</t>
+          <t>RMV88503</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>jXUf-ZSmc</t>
+          <t>l5GC-qtvN</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>QFU06512</t>
+          <t>RNL06004</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>MNwE-V6p6</t>
+          <t>04GO-n8Zl</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>QHB18956</t>
+          <t>RQV81451</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>B4nt-rvpd</t>
+          <t>doHe-sFf8</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>QKM89908</t>
+          <t>RSN71799</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>bL4O-ckL6</t>
+          <t>Of3K-0FUb</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>QRB56514</t>
+          <t>RSV50349</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>ZmLU-WzDm</t>
+          <t>uRKp-tHwT</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>QUE22078</t>
+          <t>RVG62147</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>tCyA-Oi7m</t>
+          <t>G6Lt-ddUX</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>QVI53832</t>
+          <t>SAF98648</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>eBOh-GY3U</t>
+          <t>L4wk-qm05</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>QYS77373</t>
+          <t>SDE98641</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>bdKc-q4v6</t>
+          <t>8Dt1-817l</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>QYU41690</t>
+          <t>SEV98034</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>UyLP-qGWT</t>
+          <t>qIzI-PsSA</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RAL78524</t>
+          <t>SGE51092</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>4RvF-k9n0</t>
+          <t>cK7r-rECz</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RBA20127</t>
+          <t>SGY00276</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>oE79-b1Se</t>
+          <t>5AC3-MVfi</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>RER39252</t>
+          <t>SLP43775</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>cNTo-jOTf</t>
+          <t>DZQr-Ms4e</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>RFD76685</t>
+          <t>SMF79012</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>ZHtK-ciCM</t>
+          <t>WJJ5-BPKA</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>RLQ73857</t>
+          <t>SNZ44527</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>QZVO-4p3B</t>
+          <t>hS1z-GdVq</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>RMV88503</t>
+          <t>SPL79883</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>fQqP-39VA</t>
+          <t>X3EC-VukC</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>RNL06004</t>
+          <t>SPZ85652</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>WaLc-sBJY</t>
+          <t>tCCD-vKBv</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>RQV81451</t>
+          <t>SQX65443</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>asPu-gWes</t>
+          <t>iBD9-QBfw</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>RSN71799</t>
+          <t>SSU10232</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>APKz-8tHA</t>
+          <t>Dgwb-wzap</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>RSV50349</t>
+          <t>SWB32390</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>gUKK-rzSk</t>
+          <t>Rmvw-y17L</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>RVG62147</t>
+          <t>SXZ01554</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>cqJ7-uz8x</t>
+          <t>XHI4-VNhm</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SAF98648</t>
+          <t>SYH46751</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>JUDx-dQqy</t>
+          <t>T9yS-XsEZ</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SDE98641</t>
+          <t>TFD08485</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>E4LL-qV7u</t>
+          <t>cqKo-jTMW</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SEV98034</t>
+          <t>TGM55607</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>3FMv-ztV8</t>
+          <t>5l7A-8dA2</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SGE51092</t>
+          <t>TKW11810</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>9G7O-tS42</t>
+          <t>syNJ-n29j</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SGY00276</t>
+          <t>TME86867</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>GGz3-kW7s</t>
+          <t>8f0t-67z8</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SLP43775</t>
+          <t>TMJ36970</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>JIk1-QTjm</t>
+          <t>luCZ-xG99</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>SMF79012</t>
+          <t>TRC98148</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>NcnL-Ufev</t>
+          <t>CkWP-IIuu</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>SNZ44527</t>
+          <t>TTS04230</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Idtr-Ef1p</t>
+          <t>UkpF-MzhJ</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>SPL79883</t>
+          <t>TXC42578</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>vFIR-WuRr</t>
+          <t>oY9D-RtJr</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>SPZ85652</t>
+          <t>UIB17642</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>BqNU-jKbs</t>
+          <t>t9j7-OaHI</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>SQX65443</t>
+          <t>UOI75021</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>2Y2u-Iexu</t>
+          <t>BO84-LiMk</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>SSU10232</t>
+          <t>UUR79971</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>2s1b-MrBM</t>
+          <t>CgRJ-Iffg</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>SWB32390</t>
+          <t>VDD06679</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>bPkJ-04s3</t>
+          <t>Xn7o-8QwA</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>SXZ01554</t>
+          <t>VEC51795</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>pE9E-t8do</t>
+          <t>7o7e-Ys2v</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>SYH46751</t>
+          <t>VEQ81429</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>g47k-j3HG</t>
+          <t>Z4PP-w7Dx</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>TFD08485</t>
+          <t>VHB06952</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>657O-VCk5</t>
+          <t>EbIx-mO9U</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TGM55607</t>
+          <t>VPE32737</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>wiKV-5PZ7</t>
+          <t>9YTA-0S79</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>TKW11810</t>
+          <t>VSG31611</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>XbfA-yocA</t>
+          <t>OEtm-TY67</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>TME86867</t>
+          <t>VYM86842</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>WM5K-oBsD</t>
+          <t>6Uyt-oDgH</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>TMJ36970</t>
+          <t>WEO81262</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>NiMt-vJm1</t>
+          <t>LirM-6qX1</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>TRC98148</t>
+          <t>WHV65431</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>ImK9-sJVr</t>
+          <t>jZIw-KaBG</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>TTS04230</t>
+          <t>WJH36041</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>oJvJ-C0eE</t>
+          <t>qeSS-uuGX</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>TXC42578</t>
+          <t>WNA57398</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ttrI-HkEA</t>
+          <t>a2SZ-m4rM</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>UIB17642</t>
+          <t>WQS25133</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>huhE-ve6K</t>
+          <t>A5nv-6jK5</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>UOI75021</t>
+          <t>WUA13603</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>DQg2-NKBW</t>
+          <t>o3Y4-LoV8</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>UUR79971</t>
+          <t>WUH93925</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>2Vvw-yPgX</t>
+          <t>Eu6b-AJmW</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>VDD06679</t>
+          <t>WVY21466</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>9NFD-F33z</t>
+          <t>HNAq-apYy</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>VEC51795</t>
+          <t>WWS24235</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>ePpy-45qF</t>
+          <t>tWXg-cLSl</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>VEQ81429</t>
+          <t>XED10282</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>xnGV-gtxP</t>
+          <t>Wx7G-exjH</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>VHB06952</t>
+          <t>XKS75480</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>0muJ-HK7N</t>
+          <t>ihbk-B9U5</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>VPE32737</t>
+          <t>XOA75961</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>83SX-bO49</t>
+          <t>momN-PLUk</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>VSG31611</t>
+          <t>XOS17378</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>DUQt-pvMj</t>
+          <t>VdMu-M2km</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>VYM86842</t>
+          <t>XRM79618</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>0Veq-1X2d</t>
+          <t>IMMo-FmrO</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>WEO81262</t>
+          <t>XSL75240</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>L7ui-NKjF</t>
+          <t>8Lih-YInS</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>WHV65431</t>
+          <t>XYT33259</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>hZeN-SKfM</t>
+          <t>NjpP-fHAN</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>WJH36041</t>
+          <t>XYZ70850</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>yPk4-9kvI</t>
+          <t>zODf-YauK</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>WNA57398</t>
+          <t>XZC74148</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>CU9v-k8Hc</t>
+          <t>HrEJ-qmLC</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>WQS25133</t>
+          <t>YBX87679</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Mg1K-yzvr</t>
+          <t>jM1A-EZBI</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>WUA13603</t>
+          <t>YCN31679</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>hdCj-fLq2</t>
+          <t>Qn5L-fpGL</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>WUH93925</t>
+          <t>YEK78642</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>8m3J-Gzlk</t>
+          <t>HuXY-h0Vu</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>WVY21466</t>
+          <t>YFU10307</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>uDNr-H0pJ</t>
+          <t>4GlE-mH69</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>WWS24235</t>
+          <t>YHZ51082</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>dTMF-Ocal</t>
+          <t>9WMp-Jyqa</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>XED10282</t>
+          <t>YOT12953</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>vWlv-tJFL</t>
+          <t>jzsr-KBhf</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>XKS75480</t>
+          <t>ZAM21080</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>c0hS-CdvD</t>
+          <t>p586-lzFB</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>XOA75961</t>
+          <t>ZFB81591</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>VRah-kBaa</t>
+          <t>Yper-OE8A</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>XOS17378</t>
+          <t>ZHU54125</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>vOQe-IMOh</t>
+          <t>nkcl-fjM3</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>XRM79618</t>
+          <t>ZLP77106</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>brgl-xEFq</t>
+          <t>hKZY-GPlI</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>XSL75240</t>
+          <t>ZNA23106</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>71I9-XlWo</t>
+          <t>boBL-XIe6</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>XYT33259</t>
+          <t>ZPU29378</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>ahUH-85T2</t>
+          <t>IhHd-siNh</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>XYZ70850</t>
+          <t>ZSU27095</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>jdV6-HalU</t>
+          <t>K1Uf-lXGf</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>XZC74148</t>
+          <t>ZVK04224</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>0GQn-L0M5</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>YBX87679</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>442D-goVh</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>YCN31679</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>SBfE-010a</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>YEK78642</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>QkIs-wR1T</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" t="inlineStr">
-        <is>
-          <t>YFU10307</t>
-        </is>
-      </c>
-      <c r="B255" t="inlineStr">
-        <is>
-          <t>pv8C-S2qP</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>YGP30798</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>dZEv-nHKw</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" t="inlineStr">
-        <is>
-          <t>YHZ51082</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>7j63-7HKa</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr">
-        <is>
-          <t>YOT12953</t>
-        </is>
-      </c>
-      <c r="B258" t="inlineStr">
-        <is>
-          <t>SxGc-ZaIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>ZAM21080</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>COFy-pMla</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>ZFB81591</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>RPpW-yrd5</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>ZHU54125</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>5RJe-0r17</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>ZLP77106</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>djSn-TgS9</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>ZNA23106</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>SHid-kPC3</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>ZPU29378</t>
-        </is>
-      </c>
-      <c r="B264" t="inlineStr">
-        <is>
-          <t>tb6L-01Ac</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>ZSU27095</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>3TQp-7e2s</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>ZVK04224</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
-          <t>9gaA-gLOl</t>
+          <t>EwLE-nnZZ</t>
         </is>
       </c>
     </row>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>7x7N-CByY</t>
+          <t>mON3-AQ1Y</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8eig-ubih</t>
+          <t>8VHa-g1cr</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>i7i0-e8kj</t>
+          <t>om9p-74TO</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>QTDp-w4Ul</t>
+          <t>x9dq-sQ1I</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>8RIT-6eGj</t>
+          <t>xYWr-5qBv</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Gw4k-eVdh</t>
+          <t>CyW8-uIEP</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0sus-cISx</t>
+          <t>bv8f-IiFI</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>28sS-bH73</t>
+          <t>C7iA-kl1r</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>qWtK-DL52</t>
+          <t>HKEr-T1iH</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RKoN-BLdg</t>
+          <t>Q4gH-zBcs</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CkIk-L3vB</t>
+          <t>SLv8-tCuX</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>k7oY-1K9F</t>
+          <t>ZIky-5Da0</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tz1e-eJnf</t>
+          <t>rRnx-JJ0S</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>jd8A-U0X4</t>
+          <t>EHkt-ocPW</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DkdX-43ju</t>
+          <t>gl2b-jVjg</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>eeke-VFFW</t>
+          <t>8e8H-Lk2S</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JkgN-Q0tw</t>
+          <t>yjZL-5bAd</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>fU3x-314s</t>
+          <t>tNQE-Expo</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4PKO-EkoE</t>
+          <t>aqxb-pMS2</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>W5lR-IDy9</t>
+          <t>RECa-FDFw</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5CYi-2g29</t>
+          <t>rKKN-EBeu</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>qAo6-xUOY</t>
+          <t>PY9K-soC4</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>QC9b-Krx2</t>
+          <t>r1OC-jMuj</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>HKm0-UrGK</t>
+          <t>kbbC-eE8y</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>jKkT-uw8G</t>
+          <t>Z0je-jzg0</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>yC6J-NtKX</t>
+          <t>gHjo-yge0</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>iesr-mHIv</t>
+          <t>wKKz-0bho</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>vA2K-I0j8</t>
+          <t>aujr-jNu8</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>W358-deTm</t>
+          <t>YrxY-9Otl</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Q2B9-GZ4n</t>
+          <t>vJB4-tLhK</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>aJ1r-FHI5</t>
+          <t>9Q5I-rRoq</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DvlB-F5Tt</t>
+          <t>p1Xw-X3A5</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Jtoe-rd80</t>
+          <t>3xXf-BNKG</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>fZCQ-1wPj</t>
+          <t>D9UH-Nxzp</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Vuqk-89L0</t>
+          <t>AuNd-QsRp</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>rljY-Fzhm</t>
+          <t>nG6H-AmkC</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>iBYD-sA2l</t>
+          <t>ogMP-07nZ</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2bSg-DXbe</t>
+          <t>wC1N-HAyl</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HQuT-cXpZ</t>
+          <t>J5vJ-Nrpp</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>J0AS-zb82</t>
+          <t>9p9N-jJUC</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>fkog-ixB2</t>
+          <t>YG4P-1YE8</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0wjM-DXVa</t>
+          <t>SgvZ-J2r1</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RAcn-mP9A</t>
+          <t>pLgL-IWuc</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>R9tM-c1TI</t>
+          <t>2AqD-UkQo</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>wesf-67x6</t>
+          <t>F0dj-YEFu</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>At1f-Lruc</t>
+          <t>n988-zYCB</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>smd1-VlnM</t>
+          <t>5VO5-5NKL</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>D6mr-DCYd</t>
+          <t>6CiY-WDHs</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>dbjW-kvqB</t>
+          <t>ByTE-NZtV</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>tDDW-iTON</t>
+          <t>I1a7-3yFs</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>IpeV-V3uk</t>
+          <t>mSEc-oQ6a</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>wFj5-Viny</t>
+          <t>RNge-C2Ff</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>yH7e-sQgN</t>
+          <t>Dlvz-1r0a</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5pf7-KpLl</t>
+          <t>eZm3-26ln</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DCIA-x6gX</t>
+          <t>AB9v-cfae</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>3kSr-gmCf</t>
+          <t>cZKy-Lb86</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>52xk-RT2i</t>
+          <t>UOnU-gbtK</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>W5NW-tqJZ</t>
+          <t>hyjg-fDeb</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>OU26-hkn9</t>
+          <t>sdqQ-S333</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NJQe-rjle</t>
+          <t>pX79-vnJk</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>vZrW-7GKt</t>
+          <t>KK1H-zWii</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Wv4p-cau5</t>
+          <t>edAB-bCJW</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>N79x-nKo6</t>
+          <t>AytK-WVkP</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>qgWf-rHvd</t>
+          <t>ZNgM-6hLg</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>gCHc-CCdL</t>
+          <t>qUvM-ac7x</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>fPHc-oxtP</t>
+          <t>t8eQ-yBwP</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>d7GQ-v6S7</t>
+          <t>l5Zs-pWPI</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>w5a4-Jc1l</t>
+          <t>AMeK-AofI</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>iqBH-ARJW</t>
+          <t>BjUh-N72s</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ts7J-llLb</t>
+          <t>K4OC-yj5v</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>hMLy-CFVC</t>
+          <t>1z9m-eHFe</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>eZnK-oWlU</t>
+          <t>0Uo7-ImDA</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nRrT-z0aK</t>
+          <t>Kdbo-vk5F</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>OZct-hAV2</t>
+          <t>gPqO-OIci</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>oHVZ-Ub10</t>
+          <t>7Oq4-Ln1M</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7lym-qKjk</t>
+          <t>Nzvq-ijhb</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JAQE-asZl</t>
+          <t>I2aB-HYao</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>yB0f-59Hv</t>
+          <t>dvhB-IjPZ</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>qf6t-5pFD</t>
+          <t>oP3A-KQ7z</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>MHzA-t35v</t>
+          <t>ENe8-6kV0</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>sJeO-zseo</t>
+          <t>5Nar-y0y9</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MZTs-CGSN</t>
+          <t>GPhR-2jr5</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MgKF-XVd0</t>
+          <t>Nmwl-Asv3</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>UJ8m-II3K</t>
+          <t>lBWi-EO7O</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>xdCz-HH09</t>
+          <t>pDN4-TeSt</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>6Xz1-cnCb</t>
+          <t>sAuq-nZjw</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>htg0-Tvd1</t>
+          <t>z6cR-BwE0</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EjNm-iddY</t>
+          <t>5us0-f3Oq</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>vpRK-WNI2</t>
+          <t>a2an-iNrK</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>teQH-pR1T</t>
+          <t>t7Kp-j7Fj</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RyFz-M4ZM</t>
+          <t>trz6-GXbR</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Klch-z5dR</t>
+          <t>lE8m-9u92</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tc2A-XvL1</t>
+          <t>eKob-MCPc</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>UfRV-Jp6H</t>
+          <t>1GtT-k2k9</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>rrc0-FNhr</t>
+          <t>n5hY-Jy20</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>F5RM-C69k</t>
+          <t>izdi-G8Vg</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>eWAA-JT4U</t>
+          <t>rJHT-mTAb</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Aena-f214</t>
+          <t>FqFe-VggO</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>oUX6-LAT7</t>
+          <t>lHc7-xJ6q</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1qCN-8Dez</t>
+          <t>u6ek-m3yv</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>pcYj-Faea</t>
+          <t>uwLe-kKDZ</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>lWHk-2q6W</t>
+          <t>dWi9-LU09</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>TrQD-Bx9T</t>
+          <t>7Vpo-iUPU</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>RK4o-Y4YY</t>
+          <t>CrVw-8nPN</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>oUnE-AlE8</t>
+          <t>QW3e-VDl7</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>O0XY-kES6</t>
+          <t>l3kt-Tf5g</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>V3JI-Zd0w</t>
+          <t>fAWk-5Pwb</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CHG0-TMTH</t>
+          <t>Ngr0-eI9i</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>cm2V-8B6C</t>
+          <t>kALb-E0V9</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>R30J-cy5a</t>
+          <t>pCdv-BzY1</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0WUn-m5Ol</t>
+          <t>6Xtm-BzEK</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>MPY4-LkcS</t>
+          <t>wvAR-C2lf</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ubLD-oa3e</t>
+          <t>d2BU-gYhP</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ITlt-bhSB</t>
+          <t>cGqI-BtrQ</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Qcbr-l0pO</t>
+          <t>0e5n-MQ3H</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>YFze-wczu</t>
+          <t>tjJI-HmPN</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Pjc5-sLHz</t>
+          <t>17bG-B3xc</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>5aga-eHr2</t>
+          <t>iRRt-CBPu</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>tLTE-S3eY</t>
+          <t>JH3b-ons3</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>XYqU-BdEI</t>
+          <t>JaeJ-ND7R</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>I5FA-YJBe</t>
+          <t>mVRw-YgG2</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>N6a6-umQW</t>
+          <t>ynDK-e2ua</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>b7uV-Kw5y</t>
+          <t>Bu9x-qNCX</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>FxU2-TC3u</t>
+          <t>kmZ9-fhQv</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>JmQg-IDSH</t>
+          <t>dmhu-OpXg</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Jxms-wTtT</t>
+          <t>o7d3-2OJ7</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>OVrZ-hLXn</t>
+          <t>gmiE-t4jf</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>m1Tj-BneA</t>
+          <t>7Eww-PYBW</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>lGMJ-8v0U</t>
+          <t>f9BM-5DP9</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>mhWI-yFlB</t>
+          <t>vbq4-X5l5</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>mZ2I-9GVo</t>
+          <t>D30g-lcGf</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>t3KY-YCGx</t>
+          <t>HgHI-Hsho</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>xuiH-o5ew</t>
+          <t>xbT8-sG1L</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>7nfV-khpG</t>
+          <t>Cjhu-KcJA</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>eB1m-bEK1</t>
+          <t>XFT3-ilqF</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Qoxm-C6e0</t>
+          <t>Smyq-QWMJ</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Pgff-sZV0</t>
+          <t>neXx-dRaj</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>G26I-YJvn</t>
+          <t>HjR2-BdGh</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>dGx0-g7i7</t>
+          <t>Yybk-aBjF</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>KjYw-2ZeV</t>
+          <t>ITbO-dd00</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0FKv-DaZa</t>
+          <t>VJPV-uBK8</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>MRRm-gI9q</t>
+          <t>GoXO-nL1k</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>jgd9-Nw5i</t>
+          <t>YlZi-GMsM</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>p43U-422C</t>
+          <t>SAJE-RkFT</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>lrAR-L75c</t>
+          <t>4dvS-NlT3</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Rcwk-E1qr</t>
+          <t>SSM9-Tfr3</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>rpo8-FfdU</t>
+          <t>K9Tu-hlpt</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>WRyX-WvR5</t>
+          <t>L25G-2xoa</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>yCyK-gWSp</t>
+          <t>zXmM-xtNL</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>MMBi-X00f</t>
+          <t>4XD7-4u2t</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ECpb-JeTn</t>
+          <t>Us0n-zyyA</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Rsm2-G5Ea</t>
+          <t>6vWc-hdY2</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>eVIV-cqgo</t>
+          <t>OK4J-SfxV</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>H3yH-x89x</t>
+          <t>a710-qa6o</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>XG5T-OT4H</t>
+          <t>IwxQ-4IkV</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>p1ZP-spZX</t>
+          <t>fWI5-Qfd1</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>v7Br-YvYY</t>
+          <t>CzDq-YySJ</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>H87b-wCME</t>
+          <t>sefE-Jifo</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Wfoy-O83h</t>
+          <t>u6Vi-oEl9</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>X9Fr-wj93</t>
+          <t>pV47-zTie</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PLJT-gdQI</t>
+          <t>nbR2-qvHR</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>19wH-4KKj</t>
+          <t>Haup-RKIA</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>TFqR-oQcQ</t>
+          <t>No86-xkiT</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1EKx-iXrp</t>
+          <t>B4di-jimU</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>kHlv-oMQv</t>
+          <t>dIIu-XuuJ</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>bO63-HhLX</t>
+          <t>JtDJ-OlZR</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>XfwW-8gPx</t>
+          <t>jhRk-SKjL</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>K3FX-lsng</t>
+          <t>R1Bs-uyGa</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>8izY-kkwJ</t>
+          <t>lfiW-JLp7</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>xweI-ZTse</t>
+          <t>z57C-9RNi</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Zj9K-11ez</t>
+          <t>JXdA-VMYJ</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>eAYI-1Lul</t>
+          <t>6Cr5-uC3D</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>nnZt-RXf2</t>
+          <t>hZq5-rNYI</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>VKU3-fltH</t>
+          <t>NLUm-GDBe</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>3HFU-5jAS</t>
+          <t>wB16-EsPJ</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>k8Ub-RvYM</t>
+          <t>xEhb-Iimc</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>oIRY-HIGt</t>
+          <t>8jsb-b1IH</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Z6Uz-KOt4</t>
+          <t>SakO-Zwqk</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>VVBl-kyCk</t>
+          <t>bopR-ESO6</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>l5GC-qtvN</t>
+          <t>lgwu-icSe</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>04GO-n8Zl</t>
+          <t>NciA-i34W</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>doHe-sFf8</t>
+          <t>MIFY-gNMF</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Of3K-0FUb</t>
+          <t>cJN3-PnZy</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>uRKp-tHwT</t>
+          <t>pOT6-y4n1</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>G6Lt-ddUX</t>
+          <t>6QSU-37kS</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>L4wk-qm05</t>
+          <t>9ihz-kjsD</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>8Dt1-817l</t>
+          <t>ZJmG-OAfd</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>qIzI-PsSA</t>
+          <t>M3oL-N6xE</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>cK7r-rECz</t>
+          <t>xW7L-gDDC</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>5AC3-MVfi</t>
+          <t>oOMz-9Ohq</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>DZQr-Ms4e</t>
+          <t>1PhI-8WBd</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>WJJ5-BPKA</t>
+          <t>aqV0-4nxI</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>hS1z-GdVq</t>
+          <t>g963-RzUp</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>X3EC-VukC</t>
+          <t>CPpj-pdtY</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>tCCD-vKBv</t>
+          <t>FXZK-A3Ji</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>iBD9-QBfw</t>
+          <t>yjQn-84fW</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Dgwb-wzap</t>
+          <t>4WgA-jw6b</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Rmvw-y17L</t>
+          <t>bsOG-dq3W</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>XHI4-VNhm</t>
+          <t>6Gcw-2NdI</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>T9yS-XsEZ</t>
+          <t>FZhk-HKIH</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>cqKo-jTMW</t>
+          <t>hAF3-B9JO</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>5l7A-8dA2</t>
+          <t>Igwh-WILA</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>syNJ-n29j</t>
+          <t>vFGc-jhYf</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>8f0t-67z8</t>
+          <t>JwBH-mo7f</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>luCZ-xG99</t>
+          <t>Qvgo-x1sD</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>CkWP-IIuu</t>
+          <t>uRxn-Sjq5</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>UkpF-MzhJ</t>
+          <t>4SBz-xNnw</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>oY9D-RtJr</t>
+          <t>zvUn-gzY8</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>t9j7-OaHI</t>
+          <t>wzZF-madJ</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>BO84-LiMk</t>
+          <t>aIoM-VM43</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>CgRJ-Iffg</t>
+          <t>lejx-UhZ1</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Xn7o-8QwA</t>
+          <t>sjK5-AWK5</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>7o7e-Ys2v</t>
+          <t>SlPo-kPqt</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Z4PP-w7Dx</t>
+          <t>yvy4-or5H</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>EbIx-mO9U</t>
+          <t>bmhN-dsHP</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>9YTA-0S79</t>
+          <t>vQOy-57ph</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>OEtm-TY67</t>
+          <t>EwTE-lUo4</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>6Uyt-oDgH</t>
+          <t>Nn9g-AMoK</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>LirM-6qX1</t>
+          <t>GmBo-nMD5</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>jZIw-KaBG</t>
+          <t>30Si-VkHN</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>qeSS-uuGX</t>
+          <t>eGUF-CWJ1</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>a2SZ-m4rM</t>
+          <t>qBh6-EDT4</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>A5nv-6jK5</t>
+          <t>LgRf-Ba54</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>o3Y4-LoV8</t>
+          <t>d5VF-nmUB</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Eu6b-AJmW</t>
+          <t>TIbx-je2h</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>HNAq-apYy</t>
+          <t>PT5x-Xu6X</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>tWXg-cLSl</t>
+          <t>tQ07-j4qO</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Wx7G-exjH</t>
+          <t>EJ2M-8tVX</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>ihbk-B9U5</t>
+          <t>ovyX-mZDn</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>momN-PLUk</t>
+          <t>6SRv-QBFh</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>VdMu-M2km</t>
+          <t>foE4-rxKE</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>IMMo-FmrO</t>
+          <t>MUHM-5AJW</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>8Lih-YInS</t>
+          <t>1mZJ-bVT4</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>NjpP-fHAN</t>
+          <t>hp2K-RU6O</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>zODf-YauK</t>
+          <t>8tHQ-BkOR</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>HrEJ-qmLC</t>
+          <t>XQaV-JEI3</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>jM1A-EZBI</t>
+          <t>pM0a-f3V8</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Qn5L-fpGL</t>
+          <t>YKMG-TNE6</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>HuXY-h0Vu</t>
+          <t>yI6d-w0yS</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>4GlE-mH69</t>
+          <t>FL4p-3Rjt</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>9WMp-Jyqa</t>
+          <t>QvSI-g3Yr</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>jzsr-KBhf</t>
+          <t>YQ0C-N8r1</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>p586-lzFB</t>
+          <t>3mma-r1ed</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Yper-OE8A</t>
+          <t>W54B-oXXj</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>nkcl-fjM3</t>
+          <t>Gevi-m3bB</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>hKZY-GPlI</t>
+          <t>cjIb-jF16</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>boBL-XIe6</t>
+          <t>gmHL-cC4S</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>IhHd-siNh</t>
+          <t>UjE1-N11L</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>K1Uf-lXGf</t>
+          <t>ebWb-W9qX</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>EwLE-nnZZ</t>
+          <t>YesC-PAja</t>
         </is>
       </c>
     </row>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B251"/>
+  <dimension ref="A1:B252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2183,1258 +2183,1270 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>ODU01918</t>
+          <t>OBL79766</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SSM9-Tfr3</t>
+          <t>QFVY-YJcC</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>OEJ86175</t>
+          <t>ODU01918</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>K9Tu-hlpt</t>
+          <t>SSM9-Tfr3</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>OKY47911</t>
+          <t>OEJ86175</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>L25G-2xoa</t>
+          <t>K9Tu-hlpt</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>ORR85927</t>
+          <t>OKY47911</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>zXmM-xtNL</t>
+          <t>L25G-2xoa</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ORT63362</t>
+          <t>ORR85927</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>4XD7-4u2t</t>
+          <t>zXmM-xtNL</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>OSB52441</t>
+          <t>ORT63362</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Us0n-zyyA</t>
+          <t>4XD7-4u2t</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>OWO93746</t>
+          <t>OSB52441</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>6vWc-hdY2</t>
+          <t>Us0n-zyyA</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>OWR55957</t>
+          <t>OWO93746</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>OK4J-SfxV</t>
+          <t>6vWc-hdY2</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>OXE34055</t>
+          <t>OWR55957</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>a710-qa6o</t>
+          <t>OK4J-SfxV</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OXH82758</t>
+          <t>OXE34055</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>IwxQ-4IkV</t>
+          <t>a710-qa6o</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>OXK70326</t>
+          <t>OXH82758</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>fWI5-Qfd1</t>
+          <t>IwxQ-4IkV</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>OYK39161</t>
+          <t>OXK70326</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>CzDq-YySJ</t>
+          <t>fWI5-Qfd1</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>OYZ43696</t>
+          <t>OYK39161</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>sefE-Jifo</t>
+          <t>CzDq-YySJ</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>PDL18808</t>
+          <t>OYZ43696</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>u6Vi-oEl9</t>
+          <t>sefE-Jifo</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>PDY46515</t>
+          <t>PDL18808</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>pV47-zTie</t>
+          <t>u6Vi-oEl9</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PHT01595</t>
+          <t>PDY46515</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>nbR2-qvHR</t>
+          <t>pV47-zTie</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PJT16152</t>
+          <t>PHT01595</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Haup-RKIA</t>
+          <t>nbR2-qvHR</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PLL97657</t>
+          <t>PJT16152</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>No86-xkiT</t>
+          <t>Haup-RKIA</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PSM82237</t>
+          <t>PLL97657</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>B4di-jimU</t>
+          <t>No86-xkiT</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PVU41752</t>
+          <t>PSM82237</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>dIIu-XuuJ</t>
+          <t>B4di-jimU</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PWD33511</t>
+          <t>PVU41752</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>JtDJ-OlZR</t>
+          <t>dIIu-XuuJ</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>QFN79396</t>
+          <t>PWD33511</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>jhRk-SKjL</t>
+          <t>JtDJ-OlZR</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>QHB18956</t>
+          <t>QFN79396</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>R1Bs-uyGa</t>
+          <t>jhRk-SKjL</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>QKM89908</t>
+          <t>QHB18956</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>lfiW-JLp7</t>
+          <t>R1Bs-uyGa</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>QRB56514</t>
+          <t>QKM89908</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>z57C-9RNi</t>
+          <t>lfiW-JLp7</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>QUE22078</t>
+          <t>QRB56514</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>JXdA-VMYJ</t>
+          <t>z57C-9RNi</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>QVI53832</t>
+          <t>QUE22078</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>6Cr5-uC3D</t>
+          <t>JXdA-VMYJ</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>QYS77373</t>
+          <t>QVI53832</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>hZq5-rNYI</t>
+          <t>6Cr5-uC3D</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>QYU41690</t>
+          <t>QYS77373</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>NLUm-GDBe</t>
+          <t>hZq5-rNYI</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>RAL78524</t>
+          <t>QYU41690</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>wB16-EsPJ</t>
+          <t>NLUm-GDBe</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>RBA20127</t>
+          <t>RAL78524</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>xEhb-Iimc</t>
+          <t>wB16-EsPJ</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>RER39252</t>
+          <t>RBA20127</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>8jsb-b1IH</t>
+          <t>xEhb-Iimc</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>RFD76685</t>
+          <t>RER39252</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>SakO-Zwqk</t>
+          <t>8jsb-b1IH</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>RLQ73857</t>
+          <t>RFD76685</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>bopR-ESO6</t>
+          <t>SakO-Zwqk</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>RMV88503</t>
+          <t>RLQ73857</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>lgwu-icSe</t>
+          <t>bopR-ESO6</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>RNL06004</t>
+          <t>RMV88503</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>NciA-i34W</t>
+          <t>lgwu-icSe</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RQV81451</t>
+          <t>RNL06004</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>MIFY-gNMF</t>
+          <t>NciA-i34W</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>RSN71799</t>
+          <t>RQV81451</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>cJN3-PnZy</t>
+          <t>MIFY-gNMF</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RSV50349</t>
+          <t>RSN71799</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>pOT6-y4n1</t>
+          <t>cJN3-PnZy</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RVG62147</t>
+          <t>RSV50349</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>6QSU-37kS</t>
+          <t>pOT6-y4n1</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SAF98648</t>
+          <t>RVG62147</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>9ihz-kjsD</t>
+          <t>6QSU-37kS</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SDE98641</t>
+          <t>SAF98648</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>ZJmG-OAfd</t>
+          <t>9ihz-kjsD</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SEV98034</t>
+          <t>SDE98641</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>M3oL-N6xE</t>
+          <t>ZJmG-OAfd</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SGE51092</t>
+          <t>SEV98034</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>xW7L-gDDC</t>
+          <t>M3oL-N6xE</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SGY00276</t>
+          <t>SGE51092</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>oOMz-9Ohq</t>
+          <t>xW7L-gDDC</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SLP43775</t>
+          <t>SGY00276</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>1PhI-8WBd</t>
+          <t>oOMz-9Ohq</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SMF79012</t>
+          <t>SLP43775</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>aqV0-4nxI</t>
+          <t>1PhI-8WBd</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SNZ44527</t>
+          <t>SMF79012</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>g963-RzUp</t>
+          <t>aqV0-4nxI</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SPL79883</t>
+          <t>SNZ44527</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>CPpj-pdtY</t>
+          <t>g963-RzUp</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SPZ85652</t>
+          <t>SPL79883</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>FXZK-A3Ji</t>
+          <t>CPpj-pdtY</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SQX65443</t>
+          <t>SPZ85652</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>yjQn-84fW</t>
+          <t>FXZK-A3Ji</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SSU10232</t>
+          <t>SQX65443</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>4WgA-jw6b</t>
+          <t>yjQn-84fW</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SWB32390</t>
+          <t>SSU10232</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>bsOG-dq3W</t>
+          <t>4WgA-jw6b</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SXZ01554</t>
+          <t>SWB32390</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>6Gcw-2NdI</t>
+          <t>bsOG-dq3W</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SYH46751</t>
+          <t>SXZ01554</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>FZhk-HKIH</t>
+          <t>6Gcw-2NdI</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>TFD08485</t>
+          <t>SYH46751</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>hAF3-B9JO</t>
+          <t>FZhk-HKIH</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TGM55607</t>
+          <t>TFD08485</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Igwh-WILA</t>
+          <t>hAF3-B9JO</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>TKW11810</t>
+          <t>TGM55607</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>vFGc-jhYf</t>
+          <t>Igwh-WILA</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TME86867</t>
+          <t>TKW11810</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>JwBH-mo7f</t>
+          <t>vFGc-jhYf</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>TMJ36970</t>
+          <t>TME86867</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Qvgo-x1sD</t>
+          <t>JwBH-mo7f</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TRC98148</t>
+          <t>TMJ36970</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>uRxn-Sjq5</t>
+          <t>Qvgo-x1sD</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TTS04230</t>
+          <t>TRC98148</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>4SBz-xNnw</t>
+          <t>uRxn-Sjq5</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>TXC42578</t>
+          <t>TTS04230</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>zvUn-gzY8</t>
+          <t>4SBz-xNnw</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>UIB17642</t>
+          <t>TXC42578</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>wzZF-madJ</t>
+          <t>zvUn-gzY8</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>UOI75021</t>
+          <t>UIB17642</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>aIoM-VM43</t>
+          <t>wzZF-madJ</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>UUR79971</t>
+          <t>UOI75021</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>lejx-UhZ1</t>
+          <t>aIoM-VM43</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>VDD06679</t>
+          <t>UUR79971</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>sjK5-AWK5</t>
+          <t>lejx-UhZ1</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>VEC51795</t>
+          <t>VDD06679</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>SlPo-kPqt</t>
+          <t>sjK5-AWK5</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>VEQ81429</t>
+          <t>VEC51795</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>yvy4-or5H</t>
+          <t>SlPo-kPqt</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>VHB06952</t>
+          <t>VEQ81429</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>bmhN-dsHP</t>
+          <t>yvy4-or5H</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>VPE32737</t>
+          <t>VHB06952</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>vQOy-57ph</t>
+          <t>bmhN-dsHP</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>VSG31611</t>
+          <t>VPE32737</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>EwTE-lUo4</t>
+          <t>vQOy-57ph</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>VYM86842</t>
+          <t>VSG31611</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Nn9g-AMoK</t>
+          <t>EwTE-lUo4</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>WEO81262</t>
+          <t>VYM86842</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>GmBo-nMD5</t>
+          <t>Nn9g-AMoK</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>WHV65431</t>
+          <t>WEO81262</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>30Si-VkHN</t>
+          <t>GmBo-nMD5</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>WJH36041</t>
+          <t>WHV65431</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>eGUF-CWJ1</t>
+          <t>30Si-VkHN</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>WNA57398</t>
+          <t>WJH36041</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>qBh6-EDT4</t>
+          <t>eGUF-CWJ1</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>WQS25133</t>
+          <t>WNA57398</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>LgRf-Ba54</t>
+          <t>qBh6-EDT4</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>WUA13603</t>
+          <t>WQS25133</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>d5VF-nmUB</t>
+          <t>LgRf-Ba54</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>WUH93925</t>
+          <t>WUA13603</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>TIbx-je2h</t>
+          <t>d5VF-nmUB</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>WVY21466</t>
+          <t>WUH93925</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>PT5x-Xu6X</t>
+          <t>TIbx-je2h</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>WWS24235</t>
+          <t>WVY21466</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>tQ07-j4qO</t>
+          <t>PT5x-Xu6X</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>XED10282</t>
+          <t>WWS24235</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>EJ2M-8tVX</t>
+          <t>tQ07-j4qO</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>XKS75480</t>
+          <t>XED10282</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>ovyX-mZDn</t>
+          <t>EJ2M-8tVX</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>XOA75961</t>
+          <t>XKS75480</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>6SRv-QBFh</t>
+          <t>ovyX-mZDn</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>XOS17378</t>
+          <t>XOA75961</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>foE4-rxKE</t>
+          <t>6SRv-QBFh</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>XRM79618</t>
+          <t>XOS17378</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>MUHM-5AJW</t>
+          <t>foE4-rxKE</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>XSL75240</t>
+          <t>XRM79618</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>1mZJ-bVT4</t>
+          <t>MUHM-5AJW</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>XYT33259</t>
+          <t>XSL75240</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>hp2K-RU6O</t>
+          <t>1mZJ-bVT4</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>XYZ70850</t>
+          <t>XYT33259</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>8tHQ-BkOR</t>
+          <t>hp2K-RU6O</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>XZC74148</t>
+          <t>XYZ70850</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>XQaV-JEI3</t>
+          <t>8tHQ-BkOR</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>YBX87679</t>
+          <t>XZC74148</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>pM0a-f3V8</t>
+          <t>XQaV-JEI3</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>YCN31679</t>
+          <t>YBX87679</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>YKMG-TNE6</t>
+          <t>pM0a-f3V8</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>YEK78642</t>
+          <t>YCN31679</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>yI6d-w0yS</t>
+          <t>YKMG-TNE6</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>YFU10307</t>
+          <t>YEK78642</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>FL4p-3Rjt</t>
+          <t>yI6d-w0yS</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>YHZ51082</t>
+          <t>YFU10307</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>QvSI-g3Yr</t>
+          <t>FL4p-3Rjt</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>YOT12953</t>
+          <t>YHZ51082</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>YQ0C-N8r1</t>
+          <t>QvSI-g3Yr</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ZAM21080</t>
+          <t>YOT12953</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>3mma-r1ed</t>
+          <t>YQ0C-N8r1</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ZFB81591</t>
+          <t>ZAM21080</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>W54B-oXXj</t>
+          <t>3mma-r1ed</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ZHU54125</t>
+          <t>ZFB81591</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Gevi-m3bB</t>
+          <t>W54B-oXXj</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ZLP77106</t>
+          <t>ZHU54125</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>cjIb-jF16</t>
+          <t>Gevi-m3bB</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ZNA23106</t>
+          <t>ZLP77106</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>gmHL-cC4S</t>
+          <t>cjIb-jF16</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ZPU29378</t>
+          <t>ZNA23106</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>UjE1-N11L</t>
+          <t>gmHL-cC4S</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ZSU27095</t>
+          <t>ZPU29378</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>ebWb-W9qX</t>
+          <t>UjE1-N11L</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
+          <t>ZSU27095</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>ebWb-W9qX</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
           <t>ZVK04224</t>
         </is>
       </c>
-      <c r="B251" t="inlineStr">
+      <c r="B252" t="inlineStr">
         <is>
           <t>YesC-PAja</t>
         </is>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B252"/>
+  <dimension ref="A1:B253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2051,1402 +2051,1414 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NDJ67099</t>
+          <t>NCM04473</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>XFT3-ilqF</t>
+          <t>LDHI-zed7</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NEE79704</t>
+          <t>NDJ67099</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Smyq-QWMJ</t>
+          <t>XFT3-ilqF</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NIQ43372</t>
+          <t>NEE79704</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>neXx-dRaj</t>
+          <t>Smyq-QWMJ</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NLP67632</t>
+          <t>NIQ43372</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>HjR2-BdGh</t>
+          <t>neXx-dRaj</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NPD00961</t>
+          <t>NLP67632</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Yybk-aBjF</t>
+          <t>HjR2-BdGh</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NUI19784</t>
+          <t>NPD00961</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ITbO-dd00</t>
+          <t>Yybk-aBjF</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>NWX06153</t>
+          <t>NUI19784</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>VJPV-uBK8</t>
+          <t>ITbO-dd00</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>NYF03161</t>
+          <t>NWX06153</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>GoXO-nL1k</t>
+          <t>VJPV-uBK8</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>NZW46214</t>
+          <t>NYF03161</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>YlZi-GMsM</t>
+          <t>GoXO-nL1k</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>OAM83746</t>
+          <t>NZW46214</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SAJE-RkFT</t>
+          <t>YlZi-GMsM</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>OBI75581</t>
+          <t>OAM83746</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>4dvS-NlT3</t>
+          <t>SAJE-RkFT</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>OBL79766</t>
+          <t>OBI75581</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>QFVY-YJcC</t>
+          <t>4dvS-NlT3</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>ODU01918</t>
+          <t>OBL79766</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SSM9-Tfr3</t>
+          <t>QFVY-YJcC</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>OEJ86175</t>
+          <t>ODU01918</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>K9Tu-hlpt</t>
+          <t>SSM9-Tfr3</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>OKY47911</t>
+          <t>OEJ86175</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>L25G-2xoa</t>
+          <t>K9Tu-hlpt</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>ORR85927</t>
+          <t>OKY47911</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>zXmM-xtNL</t>
+          <t>L25G-2xoa</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ORT63362</t>
+          <t>ORR85927</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>4XD7-4u2t</t>
+          <t>zXmM-xtNL</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>OSB52441</t>
+          <t>ORT63362</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Us0n-zyyA</t>
+          <t>4XD7-4u2t</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>OWO93746</t>
+          <t>OSB52441</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>6vWc-hdY2</t>
+          <t>Us0n-zyyA</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>OWR55957</t>
+          <t>OWO93746</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>OK4J-SfxV</t>
+          <t>6vWc-hdY2</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OXE34055</t>
+          <t>OWR55957</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>a710-qa6o</t>
+          <t>OK4J-SfxV</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>OXH82758</t>
+          <t>OXE34055</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>IwxQ-4IkV</t>
+          <t>a710-qa6o</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>OXK70326</t>
+          <t>OXH82758</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>fWI5-Qfd1</t>
+          <t>IwxQ-4IkV</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>OYK39161</t>
+          <t>OXK70326</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>CzDq-YySJ</t>
+          <t>fWI5-Qfd1</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>OYZ43696</t>
+          <t>OYK39161</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>sefE-Jifo</t>
+          <t>CzDq-YySJ</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>PDL18808</t>
+          <t>OYZ43696</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>u6Vi-oEl9</t>
+          <t>sefE-Jifo</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PDY46515</t>
+          <t>PDL18808</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>pV47-zTie</t>
+          <t>u6Vi-oEl9</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PHT01595</t>
+          <t>PDY46515</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>nbR2-qvHR</t>
+          <t>pV47-zTie</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PJT16152</t>
+          <t>PHT01595</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Haup-RKIA</t>
+          <t>nbR2-qvHR</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PLL97657</t>
+          <t>PJT16152</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>No86-xkiT</t>
+          <t>Haup-RKIA</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PSM82237</t>
+          <t>PLL97657</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>B4di-jimU</t>
+          <t>No86-xkiT</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PVU41752</t>
+          <t>PSM82237</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>dIIu-XuuJ</t>
+          <t>B4di-jimU</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PWD33511</t>
+          <t>PVU41752</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>JtDJ-OlZR</t>
+          <t>dIIu-XuuJ</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>QFN79396</t>
+          <t>PWD33511</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>jhRk-SKjL</t>
+          <t>JtDJ-OlZR</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>QHB18956</t>
+          <t>QFN79396</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>R1Bs-uyGa</t>
+          <t>jhRk-SKjL</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>QKM89908</t>
+          <t>QHB18956</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>lfiW-JLp7</t>
+          <t>R1Bs-uyGa</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>QRB56514</t>
+          <t>QKM89908</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>z57C-9RNi</t>
+          <t>lfiW-JLp7</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>QUE22078</t>
+          <t>QRB56514</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JXdA-VMYJ</t>
+          <t>z57C-9RNi</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>QVI53832</t>
+          <t>QUE22078</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>6Cr5-uC3D</t>
+          <t>JXdA-VMYJ</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>QYS77373</t>
+          <t>QVI53832</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>hZq5-rNYI</t>
+          <t>6Cr5-uC3D</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>QYU41690</t>
+          <t>QYS77373</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>NLUm-GDBe</t>
+          <t>hZq5-rNYI</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>RAL78524</t>
+          <t>QYU41690</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>wB16-EsPJ</t>
+          <t>NLUm-GDBe</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>RBA20127</t>
+          <t>RAL78524</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>xEhb-Iimc</t>
+          <t>wB16-EsPJ</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>RER39252</t>
+          <t>RBA20127</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>8jsb-b1IH</t>
+          <t>xEhb-Iimc</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>RFD76685</t>
+          <t>RER39252</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>SakO-Zwqk</t>
+          <t>8jsb-b1IH</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>RLQ73857</t>
+          <t>RFD76685</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>bopR-ESO6</t>
+          <t>SakO-Zwqk</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>RMV88503</t>
+          <t>RLQ73857</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>lgwu-icSe</t>
+          <t>bopR-ESO6</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RNL06004</t>
+          <t>RMV88503</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>NciA-i34W</t>
+          <t>lgwu-icSe</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>RQV81451</t>
+          <t>RNL06004</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>MIFY-gNMF</t>
+          <t>NciA-i34W</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RSN71799</t>
+          <t>RQV81451</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>cJN3-PnZy</t>
+          <t>MIFY-gNMF</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RSV50349</t>
+          <t>RSN71799</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>pOT6-y4n1</t>
+          <t>cJN3-PnZy</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>RVG62147</t>
+          <t>RSV50349</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>6QSU-37kS</t>
+          <t>pOT6-y4n1</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SAF98648</t>
+          <t>RVG62147</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>9ihz-kjsD</t>
+          <t>6QSU-37kS</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SDE98641</t>
+          <t>SAF98648</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ZJmG-OAfd</t>
+          <t>9ihz-kjsD</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SEV98034</t>
+          <t>SDE98641</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>M3oL-N6xE</t>
+          <t>ZJmG-OAfd</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SGE51092</t>
+          <t>SEV98034</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>xW7L-gDDC</t>
+          <t>M3oL-N6xE</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SGY00276</t>
+          <t>SGE51092</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>oOMz-9Ohq</t>
+          <t>xW7L-gDDC</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SLP43775</t>
+          <t>SGY00276</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>1PhI-8WBd</t>
+          <t>oOMz-9Ohq</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SMF79012</t>
+          <t>SLP43775</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>aqV0-4nxI</t>
+          <t>1PhI-8WBd</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SNZ44527</t>
+          <t>SMF79012</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>g963-RzUp</t>
+          <t>aqV0-4nxI</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SPL79883</t>
+          <t>SNZ44527</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>CPpj-pdtY</t>
+          <t>g963-RzUp</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SPZ85652</t>
+          <t>SPL79883</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>FXZK-A3Ji</t>
+          <t>CPpj-pdtY</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SQX65443</t>
+          <t>SPZ85652</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>yjQn-84fW</t>
+          <t>FXZK-A3Ji</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SSU10232</t>
+          <t>SQX65443</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>4WgA-jw6b</t>
+          <t>yjQn-84fW</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SWB32390</t>
+          <t>SSU10232</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>bsOG-dq3W</t>
+          <t>4WgA-jw6b</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SXZ01554</t>
+          <t>SWB32390</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>6Gcw-2NdI</t>
+          <t>bsOG-dq3W</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SYH46751</t>
+          <t>SXZ01554</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>FZhk-HKIH</t>
+          <t>6Gcw-2NdI</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TFD08485</t>
+          <t>SYH46751</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>hAF3-B9JO</t>
+          <t>FZhk-HKIH</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>TGM55607</t>
+          <t>TFD08485</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Igwh-WILA</t>
+          <t>hAF3-B9JO</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TKW11810</t>
+          <t>TGM55607</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>vFGc-jhYf</t>
+          <t>Igwh-WILA</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>TME86867</t>
+          <t>TKW11810</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>JwBH-mo7f</t>
+          <t>vFGc-jhYf</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TMJ36970</t>
+          <t>TME86867</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Qvgo-x1sD</t>
+          <t>JwBH-mo7f</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TRC98148</t>
+          <t>TMJ36970</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>uRxn-Sjq5</t>
+          <t>Qvgo-x1sD</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>TTS04230</t>
+          <t>TRC98148</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>4SBz-xNnw</t>
+          <t>uRxn-Sjq5</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>TXC42578</t>
+          <t>TTS04230</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>zvUn-gzY8</t>
+          <t>4SBz-xNnw</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>UIB17642</t>
+          <t>TXC42578</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>wzZF-madJ</t>
+          <t>zvUn-gzY8</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>UOI75021</t>
+          <t>UIB17642</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>aIoM-VM43</t>
+          <t>wzZF-madJ</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>UUR79971</t>
+          <t>UOI75021</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>lejx-UhZ1</t>
+          <t>aIoM-VM43</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>VDD06679</t>
+          <t>UUR79971</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>sjK5-AWK5</t>
+          <t>lejx-UhZ1</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>VEC51795</t>
+          <t>VDD06679</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>SlPo-kPqt</t>
+          <t>sjK5-AWK5</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>VEQ81429</t>
+          <t>VEC51795</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>yvy4-or5H</t>
+          <t>SlPo-kPqt</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>VHB06952</t>
+          <t>VEQ81429</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>bmhN-dsHP</t>
+          <t>yvy4-or5H</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>VPE32737</t>
+          <t>VHB06952</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>vQOy-57ph</t>
+          <t>bmhN-dsHP</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>VSG31611</t>
+          <t>VPE32737</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>EwTE-lUo4</t>
+          <t>vQOy-57ph</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>VYM86842</t>
+          <t>VSG31611</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Nn9g-AMoK</t>
+          <t>EwTE-lUo4</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>WEO81262</t>
+          <t>VYM86842</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>GmBo-nMD5</t>
+          <t>Nn9g-AMoK</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>WHV65431</t>
+          <t>WEO81262</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>30Si-VkHN</t>
+          <t>GmBo-nMD5</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>WJH36041</t>
+          <t>WHV65431</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>eGUF-CWJ1</t>
+          <t>30Si-VkHN</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>WNA57398</t>
+          <t>WJH36041</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>qBh6-EDT4</t>
+          <t>eGUF-CWJ1</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>WQS25133</t>
+          <t>WNA57398</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>LgRf-Ba54</t>
+          <t>qBh6-EDT4</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>WUA13603</t>
+          <t>WQS25133</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>d5VF-nmUB</t>
+          <t>LgRf-Ba54</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>WUH93925</t>
+          <t>WUA13603</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>TIbx-je2h</t>
+          <t>d5VF-nmUB</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>WVY21466</t>
+          <t>WUH93925</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>PT5x-Xu6X</t>
+          <t>TIbx-je2h</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>WWS24235</t>
+          <t>WVY21466</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>tQ07-j4qO</t>
+          <t>PT5x-Xu6X</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>XED10282</t>
+          <t>WWS24235</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>EJ2M-8tVX</t>
+          <t>tQ07-j4qO</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>XKS75480</t>
+          <t>XED10282</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>ovyX-mZDn</t>
+          <t>EJ2M-8tVX</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>XOA75961</t>
+          <t>XKS75480</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>6SRv-QBFh</t>
+          <t>ovyX-mZDn</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>XOS17378</t>
+          <t>XOA75961</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>foE4-rxKE</t>
+          <t>6SRv-QBFh</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>XRM79618</t>
+          <t>XOS17378</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>MUHM-5AJW</t>
+          <t>foE4-rxKE</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>XSL75240</t>
+          <t>XRM79618</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>1mZJ-bVT4</t>
+          <t>MUHM-5AJW</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>XYT33259</t>
+          <t>XSL75240</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>hp2K-RU6O</t>
+          <t>1mZJ-bVT4</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>XYZ70850</t>
+          <t>XYT33259</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>8tHQ-BkOR</t>
+          <t>hp2K-RU6O</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>XZC74148</t>
+          <t>XYZ70850</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>XQaV-JEI3</t>
+          <t>8tHQ-BkOR</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>YBX87679</t>
+          <t>XZC74148</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>pM0a-f3V8</t>
+          <t>XQaV-JEI3</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>YCN31679</t>
+          <t>YBX87679</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>YKMG-TNE6</t>
+          <t>pM0a-f3V8</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>YEK78642</t>
+          <t>YCN31679</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>yI6d-w0yS</t>
+          <t>YKMG-TNE6</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>YFU10307</t>
+          <t>YEK78642</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>FL4p-3Rjt</t>
+          <t>yI6d-w0yS</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>YHZ51082</t>
+          <t>YFU10307</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>QvSI-g3Yr</t>
+          <t>FL4p-3Rjt</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>YOT12953</t>
+          <t>YHZ51082</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>YQ0C-N8r1</t>
+          <t>QvSI-g3Yr</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ZAM21080</t>
+          <t>YOT12953</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>3mma-r1ed</t>
+          <t>YQ0C-N8r1</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ZFB81591</t>
+          <t>ZAM21080</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>W54B-oXXj</t>
+          <t>3mma-r1ed</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ZHU54125</t>
+          <t>ZFB81591</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Gevi-m3bB</t>
+          <t>W54B-oXXj</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ZLP77106</t>
+          <t>ZHU54125</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>cjIb-jF16</t>
+          <t>Gevi-m3bB</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ZNA23106</t>
+          <t>ZLP77106</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>gmHL-cC4S</t>
+          <t>cjIb-jF16</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ZPU29378</t>
+          <t>ZNA23106</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>UjE1-N11L</t>
+          <t>gmHL-cC4S</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ZSU27095</t>
+          <t>ZPU29378</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>ebWb-W9qX</t>
+          <t>UjE1-N11L</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
+          <t>ZSU27095</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>ebWb-W9qX</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
           <t>ZVK04224</t>
         </is>
       </c>
-      <c r="B252" t="inlineStr">
+      <c r="B253" t="inlineStr">
         <is>
           <t>YesC-PAja</t>
         </is>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B253"/>
+  <dimension ref="A1:B250"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,3019 +448,2983 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>mON3-AQ1Y</t>
+          <t>bxSo-UGF3</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ACP59950</t>
+          <t>ADC47471</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8VHa-g1cr</t>
+          <t>Rf6P-W0Vs</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ADC47471</t>
+          <t>AJF14211</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>om9p-74TO</t>
+          <t>qepa-7GM5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AJF14211</t>
+          <t>AMX72670</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>x9dq-sQ1I</t>
+          <t>VE17-S5mN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AMX72670</t>
+          <t>ANW71835</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>xYWr-5qBv</t>
+          <t>T6qZ-pol9</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ANW71835</t>
+          <t>ARC48959</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>CyW8-uIEP</t>
+          <t>gR8w-G0g7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARC48959</t>
+          <t>ARL55178</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>bv8f-IiFI</t>
+          <t>naH1-fw89</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ARL55178</t>
+          <t>AVJ39759</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C7iA-kl1r</t>
+          <t>Zsis-BKEF</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AVJ39759</t>
+          <t>AXM21790</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HKEr-T1iH</t>
+          <t>4PoI-Vhyi</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AXM21790</t>
+          <t>AZJ82844</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Q4gH-zBcs</t>
+          <t>8BRg-JDRu</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AZJ82844</t>
+          <t>BBA65823</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SLv8-tCuX</t>
+          <t>LWwq-R9AM</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BBA65823</t>
+          <t>BFI60670</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>ZIky-5Da0</t>
+          <t>gNuD-rFqw</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BFI60670</t>
+          <t>BGG58729</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rRnx-JJ0S</t>
+          <t>Ca0p-4xO6</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BGG58729</t>
+          <t>BJH88419</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EHkt-ocPW</t>
+          <t>mDNz-zwwS</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BJH88419</t>
+          <t>BJW79616</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>gl2b-jVjg</t>
+          <t>P3gt-J1ch</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BJW79616</t>
+          <t>BOI99795</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>8e8H-Lk2S</t>
+          <t>IsdE-xEFT</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BOI99795</t>
+          <t>BOZ64205</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yjZL-5bAd</t>
+          <t>LteP-qnTh</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BOZ64205</t>
+          <t>BQV35355</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>tNQE-Expo</t>
+          <t>l7Aw-nutO</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BQV35355</t>
+          <t>BUR49898</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>aqxb-pMS2</t>
+          <t>S3Gi-97MP</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BUR49898</t>
+          <t>CBP36635</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>RECa-FDFw</t>
+          <t>VpOf-O0hm</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CBP36635</t>
+          <t>CDG44201</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>rKKN-EBeu</t>
+          <t>qMTL-rdh2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CDG44201</t>
+          <t>CEG78579</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PY9K-soC4</t>
+          <t>4LGX-vNaj</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CEG78579</t>
+          <t>CEV66266</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>r1OC-jMuj</t>
+          <t>KjLc-sLYS</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CEV66266</t>
+          <t>CEX73283</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>kbbC-eE8y</t>
+          <t>vExN-MAUQ</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CEX73283</t>
+          <t>CGK70284</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Z0je-jzg0</t>
+          <t>pLOQ-8YyB</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CGK70284</t>
+          <t>CGY86131</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>gHjo-yge0</t>
+          <t>RerC-xvG2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CGY86131</t>
+          <t>CHZ14322</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wKKz-0bho</t>
+          <t>thoc-OXtd</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CHZ14322</t>
+          <t>CMY62163</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>aujr-jNu8</t>
+          <t>91MX-mi5f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CMY62163</t>
+          <t>CNJ73848</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>YrxY-9Otl</t>
+          <t>DXQ8-fN02</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CNJ73848</t>
+          <t>CNQ05106</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>vJB4-tLhK</t>
+          <t>x2gx-XOBN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CNQ05106</t>
+          <t>CQL05471</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>9Q5I-rRoq</t>
+          <t>Pfe4-n3x6</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CQL05471</t>
+          <t>CQV21480</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>p1Xw-X3A5</t>
+          <t>7RVg-uiUs</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CQV21480</t>
+          <t>CST44061</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3xXf-BNKG</t>
+          <t>Lf4g-F81f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CST44061</t>
+          <t>CWI21231</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>D9UH-Nxzp</t>
+          <t>Rt9r-iImE</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CWI21231</t>
+          <t>CWI74996</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AuNd-QsRp</t>
+          <t>QTMU-maOn</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CWI74996</t>
+          <t>CXY21844</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nG6H-AmkC</t>
+          <t>adRu-dpQ9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CXY21844</t>
+          <t>CYN09662</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ogMP-07nZ</t>
+          <t>3OXS-bEPf</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CYN09662</t>
+          <t>DCC25940</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>wC1N-HAyl</t>
+          <t>zQJ5-XFP4</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>DCC25940</t>
+          <t>DEI55654</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>J5vJ-Nrpp</t>
+          <t>PhxL-qOUy</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DEI55654</t>
+          <t>DGL58063</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>9p9N-jJUC</t>
+          <t>w9Fx-L8TO</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DGL58063</t>
+          <t>DHH79187</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>YG4P-1YE8</t>
+          <t>jUyr-vsdk</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DHH79187</t>
+          <t>DJK20638</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SgvZ-J2r1</t>
+          <t>vMNC-Po6I</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DJK20638</t>
+          <t>DLF24523</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>pLgL-IWuc</t>
+          <t>oRBq-mrcB</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DLF24523</t>
+          <t>DLP45053</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2AqD-UkQo</t>
+          <t>HjaU-3nbO</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DLP45053</t>
+          <t>DQD33133</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>F0dj-YEFu</t>
+          <t>riJ2-xRdh</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DQD33133</t>
+          <t>DTZ69845</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>n988-zYCB</t>
+          <t>krYw-MMoh</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DTZ69845</t>
+          <t>DUA61401</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>5VO5-5NKL</t>
+          <t>ptjP-SXaM</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DUA61401</t>
+          <t>DVJ66295</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6CiY-WDHs</t>
+          <t>OmCT-lsNT</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DVJ66295</t>
+          <t>DXM69578</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ByTE-NZtV</t>
+          <t>4lB4-G7LV</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DXM69578</t>
+          <t>DZI77349</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>I1a7-3yFs</t>
+          <t>pCCa-O87P</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DZI77349</t>
+          <t>EBT22822</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>mSEc-oQ6a</t>
+          <t>o8Z2-vzJI</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>EBT22822</t>
+          <t>ECG95521</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RNge-C2Ff</t>
+          <t>lefk-6sYF</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ECG95521</t>
+          <t>EWP70521</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Dlvz-1r0a</t>
+          <t>aPDD-0GxE</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EWP70521</t>
+          <t>EYO38305</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>eZm3-26ln</t>
+          <t>r1bz-me8D</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EYO38305</t>
+          <t>FJV52310</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AB9v-cfae</t>
+          <t>IG0p-lbpf</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>FJV52310</t>
+          <t>FLQ72134</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>cZKy-Lb86</t>
+          <t>etbo-KQp5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FLQ72134</t>
+          <t>FNU34959</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>UOnU-gbtK</t>
+          <t>T89s-82uG</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FNU34959</t>
+          <t>FOE41721</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>hyjg-fDeb</t>
+          <t>sp5G-ZyDX</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FOE41721</t>
+          <t>FOJ78948</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>sdqQ-S333</t>
+          <t>h0V1-zM5x</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FOJ78948</t>
+          <t>FQP62630</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>pX79-vnJk</t>
+          <t>EOcq-zl4Y</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FQP62630</t>
+          <t>FUSURIN1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KK1H-zWii</t>
+          <t>49J4-xeuF</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FUSURIN1</t>
+          <t>FVJ14662</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>edAB-bCJW</t>
+          <t>hUTq-bVXX</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FVJ14662</t>
+          <t>FWZ82980</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AytK-WVkP</t>
+          <t>PuVn-7W3v</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FWZ82980</t>
+          <t>FXB60927</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ZNgM-6hLg</t>
+          <t>64Yf-acru</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FXB60927</t>
+          <t>GBS06994</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>qUvM-ac7x</t>
+          <t>8qCz-7J7t</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FXU60367</t>
+          <t>GCV61524</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>t8eQ-yBwP</t>
+          <t>W3ug-nx8E</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GBS06994</t>
+          <t>GEL08954</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>l5Zs-pWPI</t>
+          <t>D1vh-RxbF</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GCV61524</t>
+          <t>GEP48591</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AMeK-AofI</t>
+          <t>s2rv-7G9p</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GEL08954</t>
+          <t>GFN61654</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BjUh-N72s</t>
+          <t>Mlkh-8KB5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GEP48591</t>
+          <t>GIE22684</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>K4OC-yj5v</t>
+          <t>dZGX-zFRy</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GFN61654</t>
+          <t>GKE90115</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1z9m-eHFe</t>
+          <t>yIOB-LXfx</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GIE22684</t>
+          <t>GLG55164</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0Uo7-ImDA</t>
+          <t>bLWT-SJDW</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GKE90115</t>
+          <t>GQG06884</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kdbo-vk5F</t>
+          <t>3dhA-xnwd</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GLG55164</t>
+          <t>GSY94523</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>gPqO-OIci</t>
+          <t>V9gY-f6zC</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GQG06884</t>
+          <t>GVD45273</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>7Oq4-Ln1M</t>
+          <t>39e1-0rcE</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GSY94523</t>
+          <t>GVM53776</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nzvq-ijhb</t>
+          <t>e8Nt-82gu</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GVD45273</t>
+          <t>HBP33017</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>I2aB-HYao</t>
+          <t>PSsm-Brzd</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GVM53776</t>
+          <t>HFX34792</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>dvhB-IjPZ</t>
+          <t>qYEF-rfjw</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HBP33017</t>
+          <t>HMD58733</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>oP3A-KQ7z</t>
+          <t>oweI-0t8c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HFX34792</t>
+          <t>HNS34640</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ENe8-6kV0</t>
+          <t>4obg-0OuC</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HMD58733</t>
+          <t>HPT02640</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>5Nar-y0y9</t>
+          <t>Bi6N-PzDC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HNS34640</t>
+          <t>HQH08532</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>GPhR-2jr5</t>
+          <t>o6is-1191</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HPT02640</t>
+          <t>HRY29891</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Nmwl-Asv3</t>
+          <t>jbbF-zL16</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HQH08532</t>
+          <t>HTN73978</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>lBWi-EO7O</t>
+          <t>5cRG-VNBc</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HRY29891</t>
+          <t>HWP25524</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>pDN4-TeSt</t>
+          <t>ycBe-8pCQ</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HTN73978</t>
+          <t>IAE88291</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>sAuq-nZjw</t>
+          <t>qc78-ELbS</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HWP25524</t>
+          <t>IFQ76747</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>z6cR-BwE0</t>
+          <t>i200-mqdY</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IAE88291</t>
+          <t>IGN23276</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5us0-f3Oq</t>
+          <t>gkjU-rwvW</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IFQ76747</t>
+          <t>IGX57659</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>a2an-iNrK</t>
+          <t>Nw4Q-GkBT</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>IGN23276</t>
+          <t>ILO34901</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>t7Kp-j7Fj</t>
+          <t>jta5-Krd6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>IGX57659</t>
+          <t>IMW07942</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>trz6-GXbR</t>
+          <t>lH2H-GSm9</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ILO34901</t>
+          <t>IQI33918</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>lE8m-9u92</t>
+          <t>bt1K-5lNN</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IMW07942</t>
+          <t>IUU53315</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>eKob-MCPc</t>
+          <t>QUq0-A1fu</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IQI33918</t>
+          <t>IWX83001</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1GtT-k2k9</t>
+          <t>GtSr-XZg4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>IUU53315</t>
+          <t>JJI69427</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>n5hY-Jy20</t>
+          <t>1r4l-H85j</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>IWX83001</t>
+          <t>JMV12916</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>izdi-G8Vg</t>
+          <t>W2O1-6Pv7</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>JJI69427</t>
+          <t>JNQ15800</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>rJHT-mTAb</t>
+          <t>5o43-Tben</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>JMV12916</t>
+          <t>JSH83558</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>FqFe-VggO</t>
+          <t>2JDC-bkoS</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>JNQ15800</t>
+          <t>JSO81414</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>lHc7-xJ6q</t>
+          <t>mMnl-kkap</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>JSH83558</t>
+          <t>JTN17189</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>u6ek-m3yv</t>
+          <t>P151-SXgA</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>JSO81414</t>
+          <t>JTQ20003</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>uwLe-kKDZ</t>
+          <t>PkRY-L5YR</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>JTN17189</t>
+          <t>KCH80368</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>dWi9-LU09</t>
+          <t>cSRP-AKIW</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>JTQ20003</t>
+          <t>KCS62207</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>7Vpo-iUPU</t>
+          <t>coZn-GpKT</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>KCH80368</t>
+          <t>KNB79119</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>CrVw-8nPN</t>
+          <t>qalI-Ogqx</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>KCS62207</t>
+          <t>KPJ23941</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>QW3e-VDl7</t>
+          <t>onsL-YvAW</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>KNB79119</t>
+          <t>KTK81122</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>l3kt-Tf5g</t>
+          <t>oURh-uxmc</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>KPJ23941</t>
+          <t>KVA96952</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>fAWk-5Pwb</t>
+          <t>LrlZ-bnAX</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>KTK81122</t>
+          <t>KVU62139</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Ngr0-eI9i</t>
+          <t>l218-fWQZ</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KVA96952</t>
+          <t>KWN66857</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>kALb-E0V9</t>
+          <t>m2s3-qJdI</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>KVU62139</t>
+          <t>KZL99357</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>pCdv-BzY1</t>
+          <t>6HVD-aNgk</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>KWN66857</t>
+          <t>KZU53477</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>6Xtm-BzEK</t>
+          <t>nNIC-Ra9Z</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>KZL99357</t>
+          <t>LCT57577</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>wvAR-C2lf</t>
+          <t>mivN-ZbOM</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>KZU53477</t>
+          <t>LFA56301</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>d2BU-gYhP</t>
+          <t>smr5-jKiH</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>LCT57577</t>
+          <t>LHQ57930</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>cGqI-BtrQ</t>
+          <t>aLnG-9pOV</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>LFA56301</t>
+          <t>LJE73544</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0e5n-MQ3H</t>
+          <t>el0r-LtCQ</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>LHQ57930</t>
+          <t>LKG10504</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>tjJI-HmPN</t>
+          <t>PYn6-x0rf</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>LJE73544</t>
+          <t>LLI56060</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>17bG-B3xc</t>
+          <t>1Q4a-dKA1</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>LKG10504</t>
+          <t>LPM87075</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>iRRt-CBPu</t>
+          <t>gV8g-noo0</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>LLI56060</t>
+          <t>MAI64055</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>JH3b-ons3</t>
+          <t>pap9-YwDT</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>LPM87075</t>
+          <t>MDE12029</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>JaeJ-ND7R</t>
+          <t>JkS2-qa9L</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MAI64055</t>
+          <t>MEG11153</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>mVRw-YgG2</t>
+          <t>q0DY-FYqK</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MDE12029</t>
+          <t>MIJ60289</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ynDK-e2ua</t>
+          <t>GvIt-ivk8</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MEG11153</t>
+          <t>MND74401</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Bu9x-qNCX</t>
+          <t>D3YV-juVv</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MIJ60289</t>
+          <t>MNW15780</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>kmZ9-fhQv</t>
+          <t>bFJF-y0DG</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MND74401</t>
+          <t>MRQ02763</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>dmhu-OpXg</t>
+          <t>BoNd-AyeS</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MNW15780</t>
+          <t>MUX13896</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>o7d3-2OJ7</t>
+          <t>bOSl-uKkz</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MRQ02763</t>
+          <t>MXC93247</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>gmiE-t4jf</t>
+          <t>hogF-GGVY</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MUX13896</t>
+          <t>MXM72788</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>7Eww-PYBW</t>
+          <t>B7NQ-DQZx</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MXC93247</t>
+          <t>MYD82527</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>f9BM-5DP9</t>
+          <t>MHO7-q8sk</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MXM72788</t>
+          <t>MYX47244</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>vbq4-X5l5</t>
+          <t>7b74-eUb5</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MYD82527</t>
+          <t>NAQ63112</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>D30g-lcGf</t>
+          <t>9wSX-uDbS</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MYX47244</t>
+          <t>NCL61296</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>HgHI-Hsho</t>
+          <t>OUcE-HO2b</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>NAQ63112</t>
+          <t>NCM04473</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>xbT8-sG1L</t>
+          <t>IjKi-HKpI</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>NCL61296</t>
+          <t>NDJ67099</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Cjhu-KcJA</t>
+          <t>4y91-WnfQ</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NCM04473</t>
+          <t>NEE79704</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>LDHI-zed7</t>
+          <t>L7at-hHB8</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NDJ67099</t>
+          <t>NIQ43372</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>XFT3-ilqF</t>
+          <t>Sfsh-1lGo</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NEE79704</t>
+          <t>NLP67632</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Smyq-QWMJ</t>
+          <t>ajKF-nPoj</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NIQ43372</t>
+          <t>NPD00961</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>neXx-dRaj</t>
+          <t>YlWs-c2kz</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NLP67632</t>
+          <t>NUI19784</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>HjR2-BdGh</t>
+          <t>tgfp-Thls</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NPD00961</t>
+          <t>NWX06153</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Yybk-aBjF</t>
+          <t>hBb3-iWRI</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>NUI19784</t>
+          <t>NYF03161</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ITbO-dd00</t>
+          <t>lPdC-O8jt</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>NWX06153</t>
+          <t>NZW46214</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>VJPV-uBK8</t>
+          <t>xqSp-NqDY</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>NYF03161</t>
+          <t>OAM83746</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>GoXO-nL1k</t>
+          <t>wzY2-SqY6</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NZW46214</t>
+          <t>OBI75581</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>YlZi-GMsM</t>
+          <t>bQsI-NaPx</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>OAM83746</t>
+          <t>OBL79766</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SAJE-RkFT</t>
+          <t>HV77-hR0B</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>OBI75581</t>
+          <t>ODU01918</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>4dvS-NlT3</t>
+          <t>Qvdh-JK96</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>OBL79766</t>
+          <t>OEJ86175</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>QFVY-YJcC</t>
+          <t>YISs-SjKI</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>ODU01918</t>
+          <t>OKY47911</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SSM9-Tfr3</t>
+          <t>hOv8-O2Ru</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>OEJ86175</t>
+          <t>ORR85927</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>K9Tu-hlpt</t>
+          <t>s35V-PlnA</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>OKY47911</t>
+          <t>ORT63362</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>L25G-2xoa</t>
+          <t>qiUt-dFPP</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>ORR85927</t>
+          <t>OSB52441</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>zXmM-xtNL</t>
+          <t>nN15-gKHN</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ORT63362</t>
+          <t>OWO93746</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>4XD7-4u2t</t>
+          <t>O5h4-hOsr</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>OSB52441</t>
+          <t>OWR55957</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Us0n-zyyA</t>
+          <t>bRuL-YHqh</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>OWO93746</t>
+          <t>OXE34055</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>6vWc-hdY2</t>
+          <t>3eT7-OzZQ</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>OWR55957</t>
+          <t>OXH82758</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>OK4J-SfxV</t>
+          <t>Bo4R-DvFV</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>OXE34055</t>
+          <t>OXK70326</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>a710-qa6o</t>
+          <t>d4TI-tE1k</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>OXH82758</t>
+          <t>OYK39161</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>IwxQ-4IkV</t>
+          <t>wmvx-ZfAg</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>OXK70326</t>
+          <t>OYZ43696</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>fWI5-Qfd1</t>
+          <t>M5Ve-mLcY</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>OYK39161</t>
+          <t>PDL18808</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CzDq-YySJ</t>
+          <t>CCBf-prNC</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>OYZ43696</t>
+          <t>PDY46515</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>sefE-Jifo</t>
+          <t>zBrN-cC9Y</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PDL18808</t>
+          <t>PHT01595</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>u6Vi-oEl9</t>
+          <t>cmI8-xMWd</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PDY46515</t>
+          <t>PJT16152</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>pV47-zTie</t>
+          <t>qDfb-BJw9</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PHT01595</t>
+          <t>PLL97657</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>nbR2-qvHR</t>
+          <t>Oetq-yiCM</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PJT16152</t>
+          <t>PSM82237</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Haup-RKIA</t>
+          <t>H6ke-jqcc</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PLL97657</t>
+          <t>PVU41752</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>No86-xkiT</t>
+          <t>e0yo-rSn0</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PSM82237</t>
+          <t>PWD33511</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>B4di-jimU</t>
+          <t>NCCU-9XE1</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PVU41752</t>
+          <t>QFN79396</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>dIIu-XuuJ</t>
+          <t>WvGj-XfsZ</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>PWD33511</t>
+          <t>QHB18956</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>JtDJ-OlZR</t>
+          <t>jdGp-ja0L</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>QFN79396</t>
+          <t>QKM89908</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>jhRk-SKjL</t>
+          <t>23kz-RH88</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>QHB18956</t>
+          <t>QRB56514</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>R1Bs-uyGa</t>
+          <t>pF9R-YnM4</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>QKM89908</t>
+          <t>QUE22078</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>lfiW-JLp7</t>
+          <t>9pu8-iucZ</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>QRB56514</t>
+          <t>QVI53832</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>z57C-9RNi</t>
+          <t>XAs5-uNNU</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>QUE22078</t>
+          <t>QYS77373</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>JXdA-VMYJ</t>
+          <t>cPzo-Lk2o</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>QVI53832</t>
+          <t>QYU41690</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>6Cr5-uC3D</t>
+          <t>hjQh-6p3W</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>QYS77373</t>
+          <t>RBA20127</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>hZq5-rNYI</t>
+          <t>2co7-WGVp</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>QYU41690</t>
+          <t>RER39252</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>NLUm-GDBe</t>
+          <t>4fVt-ylDx</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>RAL78524</t>
+          <t>RFD76685</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>wB16-EsPJ</t>
+          <t>1gzs-wWkv</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>RBA20127</t>
+          <t>RLQ73857</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>xEhb-Iimc</t>
+          <t>453V-syuV</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>RER39252</t>
+          <t>RMV88503</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>8jsb-b1IH</t>
+          <t>cuQ8-gPhy</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>RFD76685</t>
+          <t>RNL06004</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>SakO-Zwqk</t>
+          <t>3RBS-OI35</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>RLQ73857</t>
+          <t>RQV81451</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>bopR-ESO6</t>
+          <t>usmT-jlz6</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RMV88503</t>
+          <t>RSN71799</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>lgwu-icSe</t>
+          <t>y8QA-b2wR</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>RNL06004</t>
+          <t>RSV50349</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>NciA-i34W</t>
+          <t>638C-fJyT</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RQV81451</t>
+          <t>RVG62147</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>MIFY-gNMF</t>
+          <t>sL6G-uPrN</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RSN71799</t>
+          <t>SAF98648</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>cJN3-PnZy</t>
+          <t>rlke-9f4S</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>RSV50349</t>
+          <t>SDE98641</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>pOT6-y4n1</t>
+          <t>WNK4-adA8</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>RVG62147</t>
+          <t>SEV98034</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>6QSU-37kS</t>
+          <t>aFy4-e1o5</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SAF98648</t>
+          <t>SGE51092</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>9ihz-kjsD</t>
+          <t>61a8-Ig2b</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SDE98641</t>
+          <t>SGY00276</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ZJmG-OAfd</t>
+          <t>ayh9-N4Wv</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SEV98034</t>
+          <t>SLP43775</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>M3oL-N6xE</t>
+          <t>F974-Uhu1</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SGE51092</t>
+          <t>SMF79012</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>xW7L-gDDC</t>
+          <t>qpdI-JxzI</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SGY00276</t>
+          <t>SNZ44527</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>oOMz-9Ohq</t>
+          <t>29rT-6PNL</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SLP43775</t>
+          <t>SPL79883</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>1PhI-8WBd</t>
+          <t>092t-FjYw</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SMF79012</t>
+          <t>SPZ85652</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>aqV0-4nxI</t>
+          <t>FTij-KVnH</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SNZ44527</t>
+          <t>SQX65443</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>g963-RzUp</t>
+          <t>Ug5T-COxt</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SPL79883</t>
+          <t>SSU10232</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>CPpj-pdtY</t>
+          <t>i2no-CoA9</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SPZ85652</t>
+          <t>SWB32390</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>FXZK-A3Ji</t>
+          <t>rTzy-1eRw</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SQX65443</t>
+          <t>SXZ01554</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>yjQn-84fW</t>
+          <t>iCkb-C988</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SSU10232</t>
+          <t>SYH46751</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>4WgA-jw6b</t>
+          <t>XblJ-ahdv</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SWB32390</t>
+          <t>TFD08485</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>bsOG-dq3W</t>
+          <t>0Ax4-v7AV</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SXZ01554</t>
+          <t>TGM55607</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>6Gcw-2NdI</t>
+          <t>FYff-PrXf</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SYH46751</t>
+          <t>TKW11810</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>FZhk-HKIH</t>
+          <t>dQOk-TjLK</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>TFD08485</t>
+          <t>TME86867</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>hAF3-B9JO</t>
+          <t>C63G-fasb</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TGM55607</t>
+          <t>TMJ36970</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Igwh-WILA</t>
+          <t>lXSD-z7Nb</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>TKW11810</t>
+          <t>TRC98148</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>vFGc-jhYf</t>
+          <t>TOkm-Qkqp</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TME86867</t>
+          <t>TTS04230</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>JwBH-mo7f</t>
+          <t>61Gm-Lt4i</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TMJ36970</t>
+          <t>TXC42578</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Qvgo-x1sD</t>
+          <t>AUCi-1mfa</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>TRC98148</t>
+          <t>UIB17642</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>uRxn-Sjq5</t>
+          <t>ozJ8-a8A7</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>TTS04230</t>
+          <t>UOI75021</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>4SBz-xNnw</t>
+          <t>Ldut-XcOT</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>TXC42578</t>
+          <t>UUR79971</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>zvUn-gzY8</t>
+          <t>pk9S-Ukxs</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>UIB17642</t>
+          <t>VDD06679</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>wzZF-madJ</t>
+          <t>71Tl-YxmP</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>UOI75021</t>
+          <t>VEC51795</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>aIoM-VM43</t>
+          <t>6NtQ-0qm1</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>UUR79971</t>
+          <t>VEQ81429</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>lejx-UhZ1</t>
+          <t>ATzj-IHuL</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>VDD06679</t>
+          <t>VHB06952</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>sjK5-AWK5</t>
+          <t>4wyv-TXJM</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>VEC51795</t>
+          <t>VPE32737</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>SlPo-kPqt</t>
+          <t>xWPx-slVn</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>VEQ81429</t>
+          <t>VSG31611</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>yvy4-or5H</t>
+          <t>ZvHL-C3nO</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>VHB06952</t>
+          <t>VYM86842</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>bmhN-dsHP</t>
+          <t>8Ovh-YRPy</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>VPE32737</t>
+          <t>WEO81262</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>vQOy-57ph</t>
+          <t>6JpS-DUkn</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>VSG31611</t>
+          <t>WHV65431</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>EwTE-lUo4</t>
+          <t>hjwN-D9kb</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>VYM86842</t>
+          <t>WJH36041</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Nn9g-AMoK</t>
+          <t>bvIB-oAOr</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>WEO81262</t>
+          <t>WNA57398</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>GmBo-nMD5</t>
+          <t>TcLf-4Yv7</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>WHV65431</t>
+          <t>WQS25133</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>30Si-VkHN</t>
+          <t>eooF-Sgx3</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>WJH36041</t>
+          <t>WUA13603</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>eGUF-CWJ1</t>
+          <t>g4Ym-EEdJ</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>WNA57398</t>
+          <t>WUH93925</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>qBh6-EDT4</t>
+          <t>GUYn-8R0Q</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>WQS25133</t>
+          <t>WVY21466</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>LgRf-Ba54</t>
+          <t>Yjxx-DEsN</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>WUA13603</t>
+          <t>WWS24235</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>d5VF-nmUB</t>
+          <t>0NGc-wIXp</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>WUH93925</t>
+          <t>XED10282</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>TIbx-je2h</t>
+          <t>iAss-E8hr</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>WVY21466</t>
+          <t>XKS75480</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>PT5x-Xu6X</t>
+          <t>prTJ-p3bI</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>WWS24235</t>
+          <t>XOA75961</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>tQ07-j4qO</t>
+          <t>ABTq-S54T</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>XED10282</t>
+          <t>XOS17378</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>EJ2M-8tVX</t>
+          <t>guHN-GDeC</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>XKS75480</t>
+          <t>XRM79618</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>ovyX-mZDn</t>
+          <t>8uPg-Z9ce</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>XOA75961</t>
+          <t>XSL75240</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>6SRv-QBFh</t>
+          <t>lV2U-HiYX</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>XOS17378</t>
+          <t>XYT33259</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>foE4-rxKE</t>
+          <t>w4mr-2e9B</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>XRM79618</t>
+          <t>XYZ70850</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>MUHM-5AJW</t>
+          <t>jKFM-IJ5A</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>XSL75240</t>
+          <t>XZC74148</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>1mZJ-bVT4</t>
+          <t>y5m2-dceM</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>XYT33259</t>
+          <t>YBX87679</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>hp2K-RU6O</t>
+          <t>amLT-jMca</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>XYZ70850</t>
+          <t>YCN31679</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>8tHQ-BkOR</t>
+          <t>Eyoz-Q4CV</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>XZC74148</t>
+          <t>YEK78642</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>XQaV-JEI3</t>
+          <t>CUxV-CpWo</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>YBX87679</t>
+          <t>YFU10307</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>pM0a-f3V8</t>
+          <t>moaw-e9Xm</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>YCN31679</t>
+          <t>YHZ51082</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>YKMG-TNE6</t>
+          <t>CZg5-JLOp</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>YEK78642</t>
+          <t>YOT12953</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>yI6d-w0yS</t>
+          <t>hdDT-9U5p</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>YFU10307</t>
+          <t>ZAM21080</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>FL4p-3Rjt</t>
+          <t>shqV-Hlf1</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>YHZ51082</t>
+          <t>ZFB81591</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>QvSI-g3Yr</t>
+          <t>4Kat-v1VF</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>YOT12953</t>
+          <t>ZHU54125</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>YQ0C-N8r1</t>
+          <t>vfE5-mL0i</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ZAM21080</t>
+          <t>ZLP77106</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>3mma-r1ed</t>
+          <t>e1DI-VkR9</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ZFB81591</t>
+          <t>ZNA23106</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>W54B-oXXj</t>
+          <t>T4oS-CplO</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ZHU54125</t>
+          <t>ZPU29378</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Gevi-m3bB</t>
+          <t>1E7I-t2hz</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ZLP77106</t>
+          <t>ZSU27095</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>cjIb-jF16</t>
+          <t>Oucv-JrkS</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ZNA23106</t>
+          <t>ZVK04224</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>gmHL-cC4S</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" t="inlineStr">
-        <is>
-          <t>ZPU29378</t>
-        </is>
-      </c>
-      <c r="B251" t="inlineStr">
-        <is>
-          <t>UjE1-N11L</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>ZSU27095</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>ebWb-W9qX</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr">
-        <is>
-          <t>ZVK04224</t>
-        </is>
-      </c>
-      <c r="B253" t="inlineStr">
-        <is>
-          <t>YesC-PAja</t>
+          <t>vpY9-Vy3e</t>
         </is>
       </c>
     </row>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bxSo-UGF3</t>
+          <t>sUGD-qxd0</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rf6P-W0Vs</t>
+          <t>AwMb-hrXE</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>qepa-7GM5</t>
+          <t>PiDO-FUUF</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VE17-S5mN</t>
+          <t>PqxK-LYnE</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T6qZ-pol9</t>
+          <t>VqKU-XRN3</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gR8w-G0g7</t>
+          <t>3Ixg-RHnA</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>naH1-fw89</t>
+          <t>x6pL-u4qp</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Zsis-BKEF</t>
+          <t>1OUS-lbls</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4PoI-Vhyi</t>
+          <t>Cdi8-kzsa</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>8BRg-JDRu</t>
+          <t>yXup-vGvV</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LWwq-R9AM</t>
+          <t>k1pp-pmDs</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gNuD-rFqw</t>
+          <t>LIsl-a450</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ca0p-4xO6</t>
+          <t>3HUs-6uRI</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mDNz-zwwS</t>
+          <t>eX6A-jInl</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>P3gt-J1ch</t>
+          <t>jm7c-Mrj9</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IsdE-xEFT</t>
+          <t>nTOW-ypdx</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LteP-qnTh</t>
+          <t>nTWx-AE8U</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>l7Aw-nutO</t>
+          <t>ZAip-1bVF</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S3Gi-97MP</t>
+          <t>BdDp-PDH5</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>VpOf-O0hm</t>
+          <t>1jPp-SWRL</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>qMTL-rdh2</t>
+          <t>377K-uCfB</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4LGX-vNaj</t>
+          <t>Yf13-8wzH</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>KjLc-sLYS</t>
+          <t>2p1h-Qqmp</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>vExN-MAUQ</t>
+          <t>f12X-9Awk</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>pLOQ-8YyB</t>
+          <t>Worv-AnsG</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RerC-xvG2</t>
+          <t>SzpA-NBr8</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>thoc-OXtd</t>
+          <t>R0xZ-ALwV</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>91MX-mi5f</t>
+          <t>EPQr-3UFt</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DXQ8-fN02</t>
+          <t>X1K5-kqfa</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>x2gx-XOBN</t>
+          <t>RAv2-JkuV</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pfe4-n3x6</t>
+          <t>bJgc-dvv4</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>7RVg-uiUs</t>
+          <t>eYju-ydxM</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lf4g-F81f</t>
+          <t>4lLI-cE1H</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Rt9r-iImE</t>
+          <t>POBO-LsnP</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>QTMU-maOn</t>
+          <t>VgEw-W7ko</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>adRu-dpQ9</t>
+          <t>nzyD-5khJ</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>3OXS-bEPf</t>
+          <t>P38L-R7zC</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>zQJ5-XFP4</t>
+          <t>9oHp-7BJf</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PhxL-qOUy</t>
+          <t>Huft-pcU3</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>w9Fx-L8TO</t>
+          <t>dcF7-qGXN</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>jUyr-vsdk</t>
+          <t>QclU-nbmd</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>vMNC-Po6I</t>
+          <t>usB0-Z6KI</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>oRBq-mrcB</t>
+          <t>0oPE-DuAG</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HjaU-3nbO</t>
+          <t>OcAk-Yctd</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>riJ2-xRdh</t>
+          <t>OZSC-Vz2P</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>krYw-MMoh</t>
+          <t>jLzu-jaYg</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ptjP-SXaM</t>
+          <t>r271-vX40</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OmCT-lsNT</t>
+          <t>q2v6-rdBe</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>4lB4-G7LV</t>
+          <t>aHai-inNu</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>pCCa-O87P</t>
+          <t>y6PB-uVbz</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>o8Z2-vzJI</t>
+          <t>rc56-2UoL</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>lefk-6sYF</t>
+          <t>S8b9-oSCs</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>aPDD-0GxE</t>
+          <t>LTYO-CBBk</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>r1bz-me8D</t>
+          <t>xXIF-BCru</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IG0p-lbpf</t>
+          <t>AyaH-XJcS</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>etbo-KQp5</t>
+          <t>iCOx-UdOu</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>T89s-82uG</t>
+          <t>IaM0-sxYM</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>sp5G-ZyDX</t>
+          <t>e9aF-3ML3</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>h0V1-zM5x</t>
+          <t>xJMF-7OOV</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EOcq-zl4Y</t>
+          <t>kbJS-uyCk</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>49J4-xeuF</t>
+          <t>fGIW-d6dz</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>hUTq-bVXX</t>
+          <t>wBMJ-bQnu</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PuVn-7W3v</t>
+          <t>8Tm8-RDQv</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>64Yf-acru</t>
+          <t>k9RZ-VTl9</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>8qCz-7J7t</t>
+          <t>2BRp-nX6T</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>W3ug-nx8E</t>
+          <t>Gvw1-cnMQ</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>D1vh-RxbF</t>
+          <t>brYf-jqi8</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>s2rv-7G9p</t>
+          <t>I3hV-8zxC</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mlkh-8KB5</t>
+          <t>izia-LDcB</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>dZGX-zFRy</t>
+          <t>VQod-25K2</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>yIOB-LXfx</t>
+          <t>XVrl-78Dr</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>bLWT-SJDW</t>
+          <t>6mqf-T52l</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3dhA-xnwd</t>
+          <t>nanm-lUVg</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>V9gY-f6zC</t>
+          <t>NeYi-uIUw</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>39e1-0rcE</t>
+          <t>0Ox9-EVGc</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>e8Nt-82gu</t>
+          <t>CJSH-tx53</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>PSsm-Brzd</t>
+          <t>liUz-0mOZ</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>qYEF-rfjw</t>
+          <t>FdzS-Lexz</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>oweI-0t8c</t>
+          <t>SRnb-WhVY</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>4obg-0OuC</t>
+          <t>LuBc-WK3z</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Bi6N-PzDC</t>
+          <t>IiAn-mzn0</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>o6is-1191</t>
+          <t>ghWr-smqu</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>jbbF-zL16</t>
+          <t>0Dnx-EgFo</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5cRG-VNBc</t>
+          <t>xMKu-sbyq</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ycBe-8pCQ</t>
+          <t>h3Wl-NhI4</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>qc78-ELbS</t>
+          <t>sami-vpIJ</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>i200-mqdY</t>
+          <t>l0TN-fO4N</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>gkjU-rwvW</t>
+          <t>FWc8-BZJr</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nw4Q-GkBT</t>
+          <t>Ontw-kXV5</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>jta5-Krd6</t>
+          <t>m9kQ-ZBZ1</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>lH2H-GSm9</t>
+          <t>p0Sg-BZZP</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>bt1K-5lNN</t>
+          <t>S7zm-WlxV</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>QUq0-A1fu</t>
+          <t>5yMI-d7BI</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GtSr-XZg4</t>
+          <t>K4Us-EoDe</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1r4l-H85j</t>
+          <t>odiE-txkl</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>W2O1-6Pv7</t>
+          <t>0171-Yygq</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5o43-Tben</t>
+          <t>d5j9-ZSqZ</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2JDC-bkoS</t>
+          <t>SbPZ-PFat</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>mMnl-kkap</t>
+          <t>jXy1-Um5W</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>P151-SXgA</t>
+          <t>MgmQ-lE78</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PkRY-L5YR</t>
+          <t>La9Z-wzUV</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>cSRP-AKIW</t>
+          <t>Ykdi-2rT9</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>coZn-GpKT</t>
+          <t>aJMG-twg4</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>qalI-Ogqx</t>
+          <t>uqBs-PwUf</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>onsL-YvAW</t>
+          <t>KDP1-9mkj</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>oURh-uxmc</t>
+          <t>oZqe-AnWO</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>LrlZ-bnAX</t>
+          <t>h3C5-93KE</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>l218-fWQZ</t>
+          <t>gpeC-Z3yC</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>m2s3-qJdI</t>
+          <t>R75a-oeWU</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>6HVD-aNgk</t>
+          <t>C9qT-wNbF</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>nNIC-Ra9Z</t>
+          <t>Co8R-ydpV</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>mivN-ZbOM</t>
+          <t>BHyO-TQ9B</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>smr5-jKiH</t>
+          <t>DoE6-BKzQ</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>aLnG-9pOV</t>
+          <t>hxxv-OOEi</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>el0r-LtCQ</t>
+          <t>xhZq-Pnpb</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PYn6-x0rf</t>
+          <t>BbrP-e0Yq</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1Q4a-dKA1</t>
+          <t>Zx7K-cQtZ</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>gV8g-noo0</t>
+          <t>Uw4a-Cc9r</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>pap9-YwDT</t>
+          <t>Y54T-emnt</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>JkS2-qa9L</t>
+          <t>VLlH-MuIf</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>q0DY-FYqK</t>
+          <t>MFNC-ykLl</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>GvIt-ivk8</t>
+          <t>B21F-T60x</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>D3YV-juVv</t>
+          <t>V990-iDoX</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>bFJF-y0DG</t>
+          <t>mvez-Ueiz</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>BoNd-AyeS</t>
+          <t>lvzr-TYOM</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>bOSl-uKkz</t>
+          <t>QeC4-eQkF</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>hogF-GGVY</t>
+          <t>2Sop-Usd3</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>B7NQ-DQZx</t>
+          <t>BhQS-2wKl</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>MHO7-q8sk</t>
+          <t>WdHp-17VS</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7b74-eUb5</t>
+          <t>FI2t-b7OZ</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>9wSX-uDbS</t>
+          <t>CUzR-hizS</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>OUcE-HO2b</t>
+          <t>I4SH-bkeZ</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>IjKi-HKpI</t>
+          <t>ngSC-BnNq</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>4y91-WnfQ</t>
+          <t>0IN2-Go6T</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>L7at-hHB8</t>
+          <t>Vc4y-KiMl</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Sfsh-1lGo</t>
+          <t>6JzO-6Mrg</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ajKF-nPoj</t>
+          <t>GpT0-5kWT</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>YlWs-c2kz</t>
+          <t>pG5B-SjvL</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>tgfp-Thls</t>
+          <t>gGwm-vIZc</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>hBb3-iWRI</t>
+          <t>QnzG-oKMW</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>lPdC-O8jt</t>
+          <t>AE1H-yOUM</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>xqSp-NqDY</t>
+          <t>Rxf4-KA0i</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>wzY2-SqY6</t>
+          <t>Pjmr-unOS</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>bQsI-NaPx</t>
+          <t>zsrf-7i5t</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>HV77-hR0B</t>
+          <t>2I70-YkGV</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Qvdh-JK96</t>
+          <t>lPD6-L2aZ</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>YISs-SjKI</t>
+          <t>ZW8a-zMrR</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>hOv8-O2Ru</t>
+          <t>zLLa-K7u1</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>s35V-PlnA</t>
+          <t>TUtw-CEJU</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>qiUt-dFPP</t>
+          <t>6sOz-a5Zl</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>nN15-gKHN</t>
+          <t>gtC2-6KtG</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>O5h4-hOsr</t>
+          <t>6Gy5-9B9R</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>bRuL-YHqh</t>
+          <t>G4zS-0p2j</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>3eT7-OzZQ</t>
+          <t>MoZT-pJWx</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Bo4R-DvFV</t>
+          <t>n6WK-zEIL</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>d4TI-tE1k</t>
+          <t>FSQv-woWh</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>wmvx-ZfAg</t>
+          <t>wIgk-aMBz</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>M5Ve-mLcY</t>
+          <t>znyq-zc7X</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>CCBf-prNC</t>
+          <t>61jS-Q4b4</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>zBrN-cC9Y</t>
+          <t>euxr-Mlvx</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>cmI8-xMWd</t>
+          <t>YMXN-8M5C</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>qDfb-BJw9</t>
+          <t>yxNi-AX6R</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Oetq-yiCM</t>
+          <t>DWCl-xCUq</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>H6ke-jqcc</t>
+          <t>cv5l-lM6M</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>e0yo-rSn0</t>
+          <t>HZun-bNvz</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>NCCU-9XE1</t>
+          <t>oBAh-zN3c</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>WvGj-XfsZ</t>
+          <t>U1pN-mRV4</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>jdGp-ja0L</t>
+          <t>7QpV-CCcd</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>23kz-RH88</t>
+          <t>o1MO-TL3T</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>pF9R-YnM4</t>
+          <t>UadB-Ndqc</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>9pu8-iucZ</t>
+          <t>9ibp-cQjv</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>XAs5-uNNU</t>
+          <t>0Sfp-eG3e</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>cPzo-Lk2o</t>
+          <t>F5BG-iHdw</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>hjQh-6p3W</t>
+          <t>zWpK-ikwj</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>2co7-WGVp</t>
+          <t>qA00-rzzP</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>4fVt-ylDx</t>
+          <t>3iXN-DMTs</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>1gzs-wWkv</t>
+          <t>yYic-hVxe</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>453V-syuV</t>
+          <t>9Uvb-mJxP</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>cuQ8-gPhy</t>
+          <t>jEi2-BhGU</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>3RBS-OI35</t>
+          <t>mr5o-Szmt</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>usmT-jlz6</t>
+          <t>CXa0-ABmn</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>y8QA-b2wR</t>
+          <t>o7YR-ILfx</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>638C-fJyT</t>
+          <t>KlOv-a0Dv</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>sL6G-uPrN</t>
+          <t>09Oi-xPfe</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>rlke-9f4S</t>
+          <t>OzRF-UHCa</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>WNK4-adA8</t>
+          <t>CeBU-ZiLy</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>aFy4-e1o5</t>
+          <t>l77N-cVwg</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>61a8-Ig2b</t>
+          <t>qnXo-ivO7</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ayh9-N4Wv</t>
+          <t>Ibuc-qfqC</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>F974-Uhu1</t>
+          <t>Z20v-ZuJ1</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>qpdI-JxzI</t>
+          <t>ctLT-OcxG</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>29rT-6PNL</t>
+          <t>Bo39-47jJ</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>092t-FjYw</t>
+          <t>HW7g-DK2v</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>FTij-KVnH</t>
+          <t>Qa2U-YmLv</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Ug5T-COxt</t>
+          <t>3utM-55uE</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>i2no-CoA9</t>
+          <t>ezAx-AtZX</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>rTzy-1eRw</t>
+          <t>lM1J-VQvt</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>iCkb-C988</t>
+          <t>Mxld-mZDD</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>XblJ-ahdv</t>
+          <t>fHWd-C2D1</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>0Ax4-v7AV</t>
+          <t>hOdz-ih6t</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>FYff-PrXf</t>
+          <t>yDB9-Tm1J</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>dQOk-TjLK</t>
+          <t>cYma-NUQH</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>C63G-fasb</t>
+          <t>JRyP-BEXU</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>lXSD-z7Nb</t>
+          <t>KZfP-Terb</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>TOkm-Qkqp</t>
+          <t>xUpR-uX0Q</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>61Gm-Lt4i</t>
+          <t>8ViE-8gHZ</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>AUCi-1mfa</t>
+          <t>EJOs-9D4N</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ozJ8-a8A7</t>
+          <t>kZps-2Ygr</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Ldut-XcOT</t>
+          <t>KvsC-hn0G</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>pk9S-Ukxs</t>
+          <t>DAvx-QMPq</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>71Tl-YxmP</t>
+          <t>5sMy-mFO1</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>6NtQ-0qm1</t>
+          <t>9RFr-YwQS</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>ATzj-IHuL</t>
+          <t>d1F9-hh5q</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>4wyv-TXJM</t>
+          <t>bFEy-DGHA</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>xWPx-slVn</t>
+          <t>fRr6-PEd2</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ZvHL-C3nO</t>
+          <t>3rt9-0kM1</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>8Ovh-YRPy</t>
+          <t>DDvO-KtJb</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>6JpS-DUkn</t>
+          <t>z7rf-jrgq</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>hjwN-D9kb</t>
+          <t>hSNU-diX7</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>bvIB-oAOr</t>
+          <t>VPD4-1kYt</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>TcLf-4Yv7</t>
+          <t>nklE-f6ma</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>eooF-Sgx3</t>
+          <t>riWC-q8LU</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>g4Ym-EEdJ</t>
+          <t>5XcF-u49r</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>GUYn-8R0Q</t>
+          <t>MTDT-1R4l</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Yjxx-DEsN</t>
+          <t>aO87-Ul52</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>0NGc-wIXp</t>
+          <t>jyxh-CsG9</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>iAss-E8hr</t>
+          <t>X3JG-lcJA</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>prTJ-p3bI</t>
+          <t>Z6oW-d92k</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>ABTq-S54T</t>
+          <t>ozRp-4aVK</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>guHN-GDeC</t>
+          <t>aa9C-kv6L</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>8uPg-Z9ce</t>
+          <t>utn9-xKXX</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>lV2U-HiYX</t>
+          <t>eDe4-2sgK</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>w4mr-2e9B</t>
+          <t>qRRj-6d4n</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>jKFM-IJ5A</t>
+          <t>z6EK-qMrN</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>y5m2-dceM</t>
+          <t>0hsG-a5x6</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>amLT-jMca</t>
+          <t>6v16-v7Dz</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Eyoz-Q4CV</t>
+          <t>raLt-Gj2v</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>CUxV-CpWo</t>
+          <t>takM-BnFq</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>moaw-e9Xm</t>
+          <t>nhhd-eAhy</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>CZg5-JLOp</t>
+          <t>zS2u-2SkN</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>hdDT-9U5p</t>
+          <t>zjm5-PlZF</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>shqV-Hlf1</t>
+          <t>BbZJ-PLuX</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>4Kat-v1VF</t>
+          <t>iAXV-gBpc</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>vfE5-mL0i</t>
+          <t>aich-uVDY</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>e1DI-VkR9</t>
+          <t>TWWP-668u</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>T4oS-CplO</t>
+          <t>RyU9-cpIy</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>1E7I-t2hz</t>
+          <t>uEK7-EYTX</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Oucv-JrkS</t>
+          <t>OjyR-2v66</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>vpY9-Vy3e</t>
+          <t>IFJ4-T74U</t>
         </is>
       </c>
     </row>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>sUGD-qxd0</t>
+          <t>WZel-24ZF</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AwMb-hrXE</t>
+          <t>w2cS-JRqb</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PiDO-FUUF</t>
+          <t>TL3G-f7Kg</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>PqxK-LYnE</t>
+          <t>xDSj-Pgsn</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VqKU-XRN3</t>
+          <t>2SyC-KCZf</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3Ixg-RHnA</t>
+          <t>MCQQ-NlGm</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>x6pL-u4qp</t>
+          <t>jYKn-n7ZL</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1OUS-lbls</t>
+          <t>uLnG-GD0H</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cdi8-kzsa</t>
+          <t>1qPZ-sO4Q</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>yXup-vGvV</t>
+          <t>bp5k-j7HF</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>k1pp-pmDs</t>
+          <t>FuwI-ajz8</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>LIsl-a450</t>
+          <t>aLjV-kIcE</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3HUs-6uRI</t>
+          <t>rG5J-YtRz</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>eX6A-jInl</t>
+          <t>QbE6-p1i5</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jm7c-Mrj9</t>
+          <t>FKMk-uRUt</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nTOW-ypdx</t>
+          <t>TDj7-ADql</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nTWx-AE8U</t>
+          <t>BvZj-idxF</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ZAip-1bVF</t>
+          <t>Fsa8-DBqS</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BdDp-PDH5</t>
+          <t>mCsC-LTQJ</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1jPp-SWRL</t>
+          <t>Rlgz-fuI4</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>377K-uCfB</t>
+          <t>iD7e-EZgZ</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Yf13-8wzH</t>
+          <t>5YzG-wLh1</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2p1h-Qqmp</t>
+          <t>HuET-KQkA</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>f12X-9Awk</t>
+          <t>cFSk-DlmA</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Worv-AnsG</t>
+          <t>7vvp-1Vap</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SzpA-NBr8</t>
+          <t>SNZq-ezkW</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R0xZ-ALwV</t>
+          <t>RMTO-BhM9</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>EPQr-3UFt</t>
+          <t>fkiA-3shs</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>X1K5-kqfa</t>
+          <t>IUCr-HQbq</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RAv2-JkuV</t>
+          <t>b6R8-oEIE</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>bJgc-dvv4</t>
+          <t>0Zn5-Bl5s</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>eYju-ydxM</t>
+          <t>On50-O6fR</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4lLI-cE1H</t>
+          <t>TFB4-QfMm</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>POBO-LsnP</t>
+          <t>qvnN-SEFX</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>VgEw-W7ko</t>
+          <t>0fta-HJLV</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>nzyD-5khJ</t>
+          <t>RfG3-obxl</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>P38L-R7zC</t>
+          <t>guqH-gNCD</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>9oHp-7BJf</t>
+          <t>JWWv-jRHl</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Huft-pcU3</t>
+          <t>rWW6-ETJV</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>dcF7-qGXN</t>
+          <t>cwpp-qYJN</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>QclU-nbmd</t>
+          <t>OBBc-vBxH</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>usB0-Z6KI</t>
+          <t>k6Pm-fobu</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0oPE-DuAG</t>
+          <t>R4gq-jsHW</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>OcAk-Yctd</t>
+          <t>HIaX-4srA</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OZSC-Vz2P</t>
+          <t>MRWJ-o5KZ</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>jLzu-jaYg</t>
+          <t>nLSP-kp8G</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>r271-vX40</t>
+          <t>e7AT-kAC2</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>q2v6-rdBe</t>
+          <t>cPzG-TZCH</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>aHai-inNu</t>
+          <t>7DoJ-kOKH</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>y6PB-uVbz</t>
+          <t>dW79-bVtk</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>rc56-2UoL</t>
+          <t>zRQt-St5p</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>S8b9-oSCs</t>
+          <t>qRFe-7IVN</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LTYO-CBBk</t>
+          <t>GP4P-ciYF</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>xXIF-BCru</t>
+          <t>BmyS-uc4t</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AyaH-XJcS</t>
+          <t>0he9-5ynU</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>iCOx-UdOu</t>
+          <t>EWIl-SuB7</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>IaM0-sxYM</t>
+          <t>uFMX-Wna1</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>e9aF-3ML3</t>
+          <t>uJbB-vkO1</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>xJMF-7OOV</t>
+          <t>cTiz-rfa0</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>kbJS-uyCk</t>
+          <t>58AN-jV82</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>fGIW-d6dz</t>
+          <t>SxEn-wSQn</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>wBMJ-bQnu</t>
+          <t>kI7H-hZps</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>8Tm8-RDQv</t>
+          <t>G5Yj-M1Lv</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>k9RZ-VTl9</t>
+          <t>DNEB-ubHK</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2BRp-nX6T</t>
+          <t>rUg4-8tUa</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Gvw1-cnMQ</t>
+          <t>CkCG-qlBj</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>brYf-jqi8</t>
+          <t>r4Mq-niP8</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>I3hV-8zxC</t>
+          <t>9O1c-5UAY</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>izia-LDcB</t>
+          <t>es8j-F4Xy</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VQod-25K2</t>
+          <t>NyIJ-eOyf</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>XVrl-78Dr</t>
+          <t>SKBv-8zEH</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>6mqf-T52l</t>
+          <t>q24w-TjAB</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>nanm-lUVg</t>
+          <t>QhOM-xeSa</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>NeYi-uIUw</t>
+          <t>dm7X-UZKe</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0Ox9-EVGc</t>
+          <t>zKK5-oUEJ</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CJSH-tx53</t>
+          <t>aRrh-hPwQ</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>liUz-0mOZ</t>
+          <t>Pdpc-4FWE</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FdzS-Lexz</t>
+          <t>HQYK-wk91</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SRnb-WhVY</t>
+          <t>ztV6-LJdf</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LuBc-WK3z</t>
+          <t>74kl-zy13</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>IiAn-mzn0</t>
+          <t>jbTp-XKP6</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>ghWr-smqu</t>
+          <t>q3YA-9Qvc</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0Dnx-EgFo</t>
+          <t>Qnpk-zyIo</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>xMKu-sbyq</t>
+          <t>OqOW-aCwp</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>h3Wl-NhI4</t>
+          <t>0TKL-PIiy</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>sami-vpIJ</t>
+          <t>62zo-Q5lP</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>l0TN-fO4N</t>
+          <t>Ite2-rGtR</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FWc8-BZJr</t>
+          <t>zVdL-mz6V</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Ontw-kXV5</t>
+          <t>fNLx-IHyk</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>m9kQ-ZBZ1</t>
+          <t>EEEd-IgaM</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>p0Sg-BZZP</t>
+          <t>HJVS-7Uk2</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>S7zm-WlxV</t>
+          <t>746N-HoW4</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5yMI-d7BI</t>
+          <t>vxdn-JFhh</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>K4Us-EoDe</t>
+          <t>BxLI-jTkU</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>odiE-txkl</t>
+          <t>4NVQ-EZKC</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0171-Yygq</t>
+          <t>s9gL-QVOx</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>d5j9-ZSqZ</t>
+          <t>Hx4p-ZuKj</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SbPZ-PFat</t>
+          <t>cRn5-EbL2</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>jXy1-Um5W</t>
+          <t>NnQE-TIWJ</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MgmQ-lE78</t>
+          <t>MKlk-GuO8</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>La9Z-wzUV</t>
+          <t>0F5J-C8Oq</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ykdi-2rT9</t>
+          <t>4Wmq-kVMO</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>aJMG-twg4</t>
+          <t>HuRD-SVoH</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>uqBs-PwUf</t>
+          <t>vNTR-iUwB</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>KDP1-9mkj</t>
+          <t>I5YI-aZMl</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>oZqe-AnWO</t>
+          <t>bOsw-Iavj</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>h3C5-93KE</t>
+          <t>Hw6h-CGVo</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>gpeC-Z3yC</t>
+          <t>nRPq-oWXq</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>R75a-oeWU</t>
+          <t>s7Cr-mbIO</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>C9qT-wNbF</t>
+          <t>3PWY-RTRN</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Co8R-ydpV</t>
+          <t>Lost-faBB</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>BHyO-TQ9B</t>
+          <t>pVGj-8Roa</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>DoE6-BKzQ</t>
+          <t>QIEp-lDCN</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>hxxv-OOEi</t>
+          <t>pXRf-PLfq</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>xhZq-Pnpb</t>
+          <t>qmw6-RI1l</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>BbrP-e0Yq</t>
+          <t>Stlh-1mVa</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Zx7K-cQtZ</t>
+          <t>0JUW-F1zr</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Uw4a-Cc9r</t>
+          <t>tedY-0Tm4</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Y54T-emnt</t>
+          <t>LH4l-XM17</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>VLlH-MuIf</t>
+          <t>eMwQ-ybkq</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>MFNC-ykLl</t>
+          <t>CjVs-wJhK</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>B21F-T60x</t>
+          <t>Y5gq-Np6u</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>V990-iDoX</t>
+          <t>KhPN-dQlS</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>mvez-Ueiz</t>
+          <t>Oqnj-Eo2E</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>lvzr-TYOM</t>
+          <t>0kuU-kfda</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>QeC4-eQkF</t>
+          <t>SwS9-AQOy</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>2Sop-Usd3</t>
+          <t>Se9H-6WtS</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BhQS-2wKl</t>
+          <t>D6lQ-1qgH</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>WdHp-17VS</t>
+          <t>DNNg-MPaw</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>FI2t-b7OZ</t>
+          <t>7Hic-DM3t</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>CUzR-hizS</t>
+          <t>X3WY-lWkQ</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>I4SH-bkeZ</t>
+          <t>D2zH-3Eh6</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ngSC-BnNq</t>
+          <t>rXpt-RFUQ</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0IN2-Go6T</t>
+          <t>hSu5-KJEw</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Vc4y-KiMl</t>
+          <t>nNxX-nAcc</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>6JzO-6Mrg</t>
+          <t>bxTd-J5Nc</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>GpT0-5kWT</t>
+          <t>dgH7-2XFH</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>pG5B-SjvL</t>
+          <t>MMGj-5B4q</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>gGwm-vIZc</t>
+          <t>u9lK-zTVJ</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>QnzG-oKMW</t>
+          <t>slhf-UEsb</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>AE1H-yOUM</t>
+          <t>WXeh-tv9l</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Rxf4-KA0i</t>
+          <t>KJTA-zt8G</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Pjmr-unOS</t>
+          <t>dyfk-Vowv</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>zsrf-7i5t</t>
+          <t>3bLP-f8sP</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2I70-YkGV</t>
+          <t>CLTu-rNQM</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>lPD6-L2aZ</t>
+          <t>cQFI-gW8p</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ZW8a-zMrR</t>
+          <t>3h41-1BDy</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>zLLa-K7u1</t>
+          <t>nzmc-lB6s</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>TUtw-CEJU</t>
+          <t>Ussx-xe1k</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>6sOz-a5Zl</t>
+          <t>ocUh-HoRv</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>gtC2-6KtG</t>
+          <t>DN0I-sWvZ</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>6Gy5-9B9R</t>
+          <t>LiDL-ufU4</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>G4zS-0p2j</t>
+          <t>A8dU-wqRi</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>MoZT-pJWx</t>
+          <t>lhKq-rEHt</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>n6WK-zEIL</t>
+          <t>vi9p-6EsI</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>FSQv-woWh</t>
+          <t>q30P-ILWJ</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>wIgk-aMBz</t>
+          <t>RRVO-K0hU</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>znyq-zc7X</t>
+          <t>22Sx-SLPG</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>61jS-Q4b4</t>
+          <t>q4fU-yEbT</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>euxr-Mlvx</t>
+          <t>qJ8w-MRjG</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>YMXN-8M5C</t>
+          <t>blDn-c0Yk</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>yxNi-AX6R</t>
+          <t>Vz4A-mtdB</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>DWCl-xCUq</t>
+          <t>7sG2-2lit</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>cv5l-lM6M</t>
+          <t>T3db-dkDZ</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>HZun-bNvz</t>
+          <t>RZoQ-NgmP</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>oBAh-zN3c</t>
+          <t>ihsA-vM4n</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>U1pN-mRV4</t>
+          <t>zPc7-zD7z</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>7QpV-CCcd</t>
+          <t>WqFi-dDcV</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>o1MO-TL3T</t>
+          <t>t6eJ-onxp</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>UadB-Ndqc</t>
+          <t>EKNA-RhjZ</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>9ibp-cQjv</t>
+          <t>cnPF-EJal</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>0Sfp-eG3e</t>
+          <t>YdpF-AgWW</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>F5BG-iHdw</t>
+          <t>4NqL-swva</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>zWpK-ikwj</t>
+          <t>2Qw9-uiGH</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>qA00-rzzP</t>
+          <t>k0PV-kGg5</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>3iXN-DMTs</t>
+          <t>fTzk-P9W0</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>yYic-hVxe</t>
+          <t>U2Hl-cAtA</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>9Uvb-mJxP</t>
+          <t>tnGt-MahF</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>jEi2-BhGU</t>
+          <t>rI1x-25pS</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>mr5o-Szmt</t>
+          <t>armr-rKBl</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>CXa0-ABmn</t>
+          <t>Yg7Q-mBda</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>o7YR-ILfx</t>
+          <t>qdbI-lN4T</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>KlOv-a0Dv</t>
+          <t>aybp-KeH5</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>09Oi-xPfe</t>
+          <t>hdOB-bZqg</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>OzRF-UHCa</t>
+          <t>t1wK-8FYL</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>CeBU-ZiLy</t>
+          <t>Ip1U-pkPo</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>l77N-cVwg</t>
+          <t>t9nq-8CNT</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>qnXo-ivO7</t>
+          <t>S5DV-55jG</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Ibuc-qfqC</t>
+          <t>dgnZ-AHKA</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Z20v-ZuJ1</t>
+          <t>phpe-wbti</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>ctLT-OcxG</t>
+          <t>i40Y-C0v6</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Bo39-47jJ</t>
+          <t>JLt1-KNN8</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>HW7g-DK2v</t>
+          <t>Tlmi-i1EH</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Qa2U-YmLv</t>
+          <t>9WXL-YOga</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>3utM-55uE</t>
+          <t>hy2t-V4p3</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ezAx-AtZX</t>
+          <t>e6Q6-RTlK</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>lM1J-VQvt</t>
+          <t>r91p-9rgv</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Mxld-mZDD</t>
+          <t>x3WB-imxE</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>fHWd-C2D1</t>
+          <t>ilLg-xVFo</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>hOdz-ih6t</t>
+          <t>nuRp-Tspd</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>yDB9-Tm1J</t>
+          <t>AYnx-ZyDl</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>cYma-NUQH</t>
+          <t>1L4s-ntqZ</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>JRyP-BEXU</t>
+          <t>4HPa-OjUT</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>KZfP-Terb</t>
+          <t>bCtI-k8TV</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>xUpR-uX0Q</t>
+          <t>hBoE-eVFc</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>8ViE-8gHZ</t>
+          <t>AVfs-TcsW</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>EJOs-9D4N</t>
+          <t>6ehN-iRcy</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>kZps-2Ygr</t>
+          <t>ySbB-p9iS</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>KvsC-hn0G</t>
+          <t>ynf6-7HwC</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>DAvx-QMPq</t>
+          <t>exlP-cIgv</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>5sMy-mFO1</t>
+          <t>f85c-Ywlm</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>9RFr-YwQS</t>
+          <t>sy5J-WcQR</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>d1F9-hh5q</t>
+          <t>vAbE-2BER</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>bFEy-DGHA</t>
+          <t>7APB-BwPV</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>fRr6-PEd2</t>
+          <t>Pb0m-THZN</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>3rt9-0kM1</t>
+          <t>KIsV-NrMS</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>DDvO-KtJb</t>
+          <t>ptXQ-J0AN</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>z7rf-jrgq</t>
+          <t>siFx-58nj</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>hSNU-diX7</t>
+          <t>fJ1l-C5X7</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>VPD4-1kYt</t>
+          <t>vZxH-BvI5</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>nklE-f6ma</t>
+          <t>5AkD-8KnH</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>riWC-q8LU</t>
+          <t>ezLv-iTSL</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>5XcF-u49r</t>
+          <t>XFHM-tVYZ</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>MTDT-1R4l</t>
+          <t>rmL3-PtrC</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>aO87-Ul52</t>
+          <t>4RaP-7LTS</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>jyxh-CsG9</t>
+          <t>p86A-fE5e</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>X3JG-lcJA</t>
+          <t>eCSL-WsVn</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Z6oW-d92k</t>
+          <t>t19C-XZql</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>ozRp-4aVK</t>
+          <t>0HVJ-joGg</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>aa9C-kv6L</t>
+          <t>aBHx-vajQ</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>utn9-xKXX</t>
+          <t>LuIM-182i</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>eDe4-2sgK</t>
+          <t>edMy-G8od</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>qRRj-6d4n</t>
+          <t>S7u3-mI4a</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>z6EK-qMrN</t>
+          <t>kW7f-t5Oo</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>0hsG-a5x6</t>
+          <t>tGaK-Nttk</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>6v16-v7Dz</t>
+          <t>XI5K-ouf1</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>raLt-Gj2v</t>
+          <t>8RYH-JbUl</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>takM-BnFq</t>
+          <t>SdOE-n4Qj</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>nhhd-eAhy</t>
+          <t>Bb3H-4L13</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>zS2u-2SkN</t>
+          <t>hl04-gpfd</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>zjm5-PlZF</t>
+          <t>XK3E-SCSS</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>BbZJ-PLuX</t>
+          <t>9VpM-VrmX</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>iAXV-gBpc</t>
+          <t>tID3-9I5Z</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>aich-uVDY</t>
+          <t>eDMH-ccdw</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>TWWP-668u</t>
+          <t>eDlA-xbzB</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>RyU9-cpIy</t>
+          <t>0bHd-KnZJ</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>uEK7-EYTX</t>
+          <t>2tM1-lA5u</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>OjyR-2v66</t>
+          <t>Ammt-wQv9</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>IFJ4-T74U</t>
+          <t>LacF-jBkj</t>
         </is>
       </c>
     </row>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B250"/>
+  <dimension ref="A1:B249"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WZel-24ZF</t>
+          <t>4Vs0-MW8g</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>w2cS-JRqb</t>
+          <t>Y6Tg-zV3B</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>TL3G-f7Kg</t>
+          <t>J8il-ibpL</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>xDSj-Pgsn</t>
+          <t>f8Qi-AvSh</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2SyC-KCZf</t>
+          <t>1uUb-l51S</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MCQQ-NlGm</t>
+          <t>hWmA-f4Gu</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>jYKn-n7ZL</t>
+          <t>Fnsy-SqSp</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>uLnG-GD0H</t>
+          <t>pN3y-ztOG</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1qPZ-sO4Q</t>
+          <t>FAYx-QZoD</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>bp5k-j7HF</t>
+          <t>9m3u-z4vf</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>FuwI-ajz8</t>
+          <t>L7Hn-XFfB</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>aLjV-kIcE</t>
+          <t>aGGn-Mtmp</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rG5J-YtRz</t>
+          <t>wvzt-fmHY</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>QbE6-p1i5</t>
+          <t>Q7xh-W7oK</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FKMk-uRUt</t>
+          <t>lGuf-t0BH</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>TDj7-ADql</t>
+          <t>EXut-EfVh</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BvZj-idxF</t>
+          <t>LrtT-AaAW</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fsa8-DBqS</t>
+          <t>iLeg-BwhE</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>mCsC-LTQJ</t>
+          <t>4YqA-ge8W</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Rlgz-fuI4</t>
+          <t>FMMt-vZta</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>iD7e-EZgZ</t>
+          <t>WZa1-sKRz</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5YzG-wLh1</t>
+          <t>CFPr-vwEH</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>HuET-KQkA</t>
+          <t>2JwI-5gyc</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>cFSk-DlmA</t>
+          <t>KEDs-eU5A</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>7vvp-1Vap</t>
+          <t>i8EM-Wpso</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SNZq-ezkW</t>
+          <t>AUUy-ubyU</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RMTO-BhM9</t>
+          <t>gvTg-ntIR</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>fkiA-3shs</t>
+          <t>kb7k-Kz2R</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IUCr-HQbq</t>
+          <t>3FT1-F2Wr</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>b6R8-oEIE</t>
+          <t>WC7u-Vwsa</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0Zn5-Bl5s</t>
+          <t>Ow29-f2CN</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>On50-O6fR</t>
+          <t>Haak-V0wc</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TFB4-QfMm</t>
+          <t>iPVC-XRob</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>qvnN-SEFX</t>
+          <t>6ot3-OB8h</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0fta-HJLV</t>
+          <t>v6AP-PvqQ</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RfG3-obxl</t>
+          <t>0wpN-5hXA</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>guqH-gNCD</t>
+          <t>WLH6-QyZ7</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JWWv-jRHl</t>
+          <t>hbpQ-J84g</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>rWW6-ETJV</t>
+          <t>JOXg-zs1s</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>cwpp-qYJN</t>
+          <t>v7Mp-H1lL</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>OBBc-vBxH</t>
+          <t>Rhow-ZZjw</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>k6Pm-fobu</t>
+          <t>Sjz6-L78y</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>R4gq-jsHW</t>
+          <t>58o3-CFNw</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HIaX-4srA</t>
+          <t>kBYK-HY9d</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MRWJ-o5KZ</t>
+          <t>yaLG-XOWV</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>nLSP-kp8G</t>
+          <t>8hr3-AmWY</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>e7AT-kAC2</t>
+          <t>JkgH-KcWR</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>cPzG-TZCH</t>
+          <t>UjPK-t5DQ</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7DoJ-kOKH</t>
+          <t>YUor-OCfM</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>dW79-bVtk</t>
+          <t>eLh3-dcag</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>zRQt-St5p</t>
+          <t>Pijb-bvuD</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>qRFe-7IVN</t>
+          <t>OAua-bzLf</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>GP4P-ciYF</t>
+          <t>2bXu-9UOi</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BmyS-uc4t</t>
+          <t>axBf-GGfU</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0he9-5ynU</t>
+          <t>ZUUi-RmsK</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EWIl-SuB7</t>
+          <t>nLk9-BcX4</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>uFMX-Wna1</t>
+          <t>5gFR-PwkM</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>uJbB-vkO1</t>
+          <t>BJYH-r6AM</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>cTiz-rfa0</t>
+          <t>4MXf-NqTg</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>58AN-jV82</t>
+          <t>wMFc-UFb8</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SxEn-wSQn</t>
+          <t>yFYy-gnnz</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>kI7H-hZps</t>
+          <t>wwNH-Bx03</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>G5Yj-M1Lv</t>
+          <t>6sW6-VT5F</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DNEB-ubHK</t>
+          <t>VA0A-e3Cw</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>rUg4-8tUa</t>
+          <t>Whc9-ZfOJ</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CkCG-qlBj</t>
+          <t>PasO-ZBBm</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>r4Mq-niP8</t>
+          <t>Jl2s-xTLa</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>9O1c-5UAY</t>
+          <t>7L5d-MZco</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>es8j-F4Xy</t>
+          <t>ypzr-sMDa</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NyIJ-eOyf</t>
+          <t>HjnP-bMf7</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SKBv-8zEH</t>
+          <t>ykpq-Yw5f</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>q24w-TjAB</t>
+          <t>gSrO-QmDW</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>QhOM-xeSa</t>
+          <t>B5B4-GpgC</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>dm7X-UZKe</t>
+          <t>bNeL-OSoB</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>zKK5-oUEJ</t>
+          <t>wLhH-4So4</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>aRrh-hPwQ</t>
+          <t>IRHq-HUhY</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pdpc-4FWE</t>
+          <t>0pod-B10f</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HQYK-wk91</t>
+          <t>q6kj-rLfc</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ztV6-LJdf</t>
+          <t>pm89-7L5F</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>74kl-zy13</t>
+          <t>aezm-9vGg</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>jbTp-XKP6</t>
+          <t>Nt8e-zu5a</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>q3YA-9Qvc</t>
+          <t>s5M7-vasb</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Qnpk-zyIo</t>
+          <t>O5SL-sxau</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>OqOW-aCwp</t>
+          <t>YNFl-z4re</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0TKL-PIiy</t>
+          <t>MWJT-lOBc</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>62zo-Q5lP</t>
+          <t>Ipju-ApeR</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ite2-rGtR</t>
+          <t>pSSX-tfOr</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>zVdL-mz6V</t>
+          <t>Jd2Z-KqAj</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>fNLx-IHyk</t>
+          <t>WEiI-nmuy</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EEEd-IgaM</t>
+          <t>h8KJ-4i3h</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>HJVS-7Uk2</t>
+          <t>ruIF-uH6Q</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>746N-HoW4</t>
+          <t>p4l1-6pfS</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>vxdn-JFhh</t>
+          <t>JubV-pIKE</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>BxLI-jTkU</t>
+          <t>6vKX-1fAy</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>4NVQ-EZKC</t>
+          <t>gP3K-RQS5</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>s9gL-QVOx</t>
+          <t>Ob7L-CCDt</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Hx4p-ZuKj</t>
+          <t>jaW3-Wc1a</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>cRn5-EbL2</t>
+          <t>lw7D-sy07</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>NnQE-TIWJ</t>
+          <t>1fPi-xqiW</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MKlk-GuO8</t>
+          <t>qxca-m8ET</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0F5J-C8Oq</t>
+          <t>VmiB-qkgq</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>4Wmq-kVMO</t>
+          <t>D7vq-RLk9</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>HuRD-SVoH</t>
+          <t>qfrp-jWIs</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>vNTR-iUwB</t>
+          <t>6Yok-I6Uy</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>I5YI-aZMl</t>
+          <t>ediU-PcZZ</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>bOsw-Iavj</t>
+          <t>GkE5-5tLJ</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Hw6h-CGVo</t>
+          <t>gLYJ-B13G</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>nRPq-oWXq</t>
+          <t>1uaj-eSqt</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>s7Cr-mbIO</t>
+          <t>gic5-Gr0T</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>3PWY-RTRN</t>
+          <t>LGN2-R1ur</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Lost-faBB</t>
+          <t>KjsV-xAiO</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>pVGj-8Roa</t>
+          <t>dSt4-4m8N</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>QIEp-lDCN</t>
+          <t>p4in-wX1q</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>pXRf-PLfq</t>
+          <t>W5oY-6vCp</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>qmw6-RI1l</t>
+          <t>mmWl-5eu2</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Stlh-1mVa</t>
+          <t>4p9S-5RYF</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0JUW-F1zr</t>
+          <t>h5JS-UXNQ</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>tedY-0Tm4</t>
+          <t>aiBU-zSdN</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>LH4l-XM17</t>
+          <t>ftNe-bYAg</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>eMwQ-ybkq</t>
+          <t>HwRR-eU2G</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>CjVs-wJhK</t>
+          <t>H3Fm-tGbj</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Y5gq-Np6u</t>
+          <t>Sql8-gH10</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>KhPN-dQlS</t>
+          <t>TNzH-fCNg</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Oqnj-Eo2E</t>
+          <t>9GBB-2F8Z</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0kuU-kfda</t>
+          <t>VdZf-9nQb</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>SwS9-AQOy</t>
+          <t>qMEW-W0V8</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Se9H-6WtS</t>
+          <t>dVHE-H6ja</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>D6lQ-1qgH</t>
+          <t>yvwZ-P5Y9</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>DNNg-MPaw</t>
+          <t>pdes-hA4I</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>7Hic-DM3t</t>
+          <t>0sDE-y1xM</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>X3WY-lWkQ</t>
+          <t>jL14-qmf5</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>D2zH-3Eh6</t>
+          <t>kLuG-gkcx</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>rXpt-RFUQ</t>
+          <t>TifG-ds4R</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>hSu5-KJEw</t>
+          <t>InoH-H6YG</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>nNxX-nAcc</t>
+          <t>G3uA-cUXz</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>bxTd-J5Nc</t>
+          <t>CL7X-vfUv</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>dgH7-2XFH</t>
+          <t>6SLZ-uYRA</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>MMGj-5B4q</t>
+          <t>mKPv-a8yd</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>u9lK-zTVJ</t>
+          <t>OWVy-ndHp</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>slhf-UEsb</t>
+          <t>rWoY-igKS</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>WXeh-tv9l</t>
+          <t>wAJa-tesj</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>KJTA-zt8G</t>
+          <t>NVA5-lKLj</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>dyfk-Vowv</t>
+          <t>t31i-qwEP</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>3bLP-f8sP</t>
+          <t>ItRz-HK1N</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>CLTu-rNQM</t>
+          <t>TzMb-GFR6</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>cQFI-gW8p</t>
+          <t>McdL-VMRL</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>3h41-1BDy</t>
+          <t>A7PC-tXBr</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>nzmc-lB6s</t>
+          <t>8Ax0-HSZN</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Ussx-xe1k</t>
+          <t>6fQM-iUy8</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>ocUh-HoRv</t>
+          <t>CRYh-fEJL</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>DN0I-sWvZ</t>
+          <t>b28r-c3fd</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>LiDL-ufU4</t>
+          <t>mVQm-I1Zt</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>A8dU-wqRi</t>
+          <t>N8O6-6i5V</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>lhKq-rEHt</t>
+          <t>XiXo-dxsa</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>vi9p-6EsI</t>
+          <t>QhPH-KehJ</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>q30P-ILWJ</t>
+          <t>q0W2-rpjc</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>RRVO-K0hU</t>
+          <t>GjCH-Pzuv</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>22Sx-SLPG</t>
+          <t>JCET-cxBi</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>q4fU-yEbT</t>
+          <t>VcME-tV56</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>qJ8w-MRjG</t>
+          <t>v1ET-cl2Y</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>blDn-c0Yk</t>
+          <t>YnrU-4pMt</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Vz4A-mtdB</t>
+          <t>bgOH-fT8h</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>7sG2-2lit</t>
+          <t>XAZ5-8AA6</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>T3db-dkDZ</t>
+          <t>tNdN-FY5c</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>RZoQ-NgmP</t>
+          <t>1Sdh-Gk9v</t>
         </is>
       </c>
     </row>
@@ -2428,1003 +2428,991 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>ihsA-vM4n</t>
+          <t>2GrK-oIFC</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>QFN79396</t>
+          <t>QHB18956</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>zPc7-zD7z</t>
+          <t>xBAR-H4mM</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>QHB18956</t>
+          <t>QKM89908</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>WqFi-dDcV</t>
+          <t>UlwA-qypB</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>QKM89908</t>
+          <t>QRB56514</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>t6eJ-onxp</t>
+          <t>2yz2-kS30</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>QRB56514</t>
+          <t>QUE22078</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>EKNA-RhjZ</t>
+          <t>Jw8v-neBr</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>QUE22078</t>
+          <t>QVI53832</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>cnPF-EJal</t>
+          <t>fuuV-0rON</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>QVI53832</t>
+          <t>QYS77373</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>YdpF-AgWW</t>
+          <t>PagX-5S0O</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>QYS77373</t>
+          <t>QYU41690</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>4NqL-swva</t>
+          <t>3KNF-Q0bk</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>QYU41690</t>
+          <t>RBA20127</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>2Qw9-uiGH</t>
+          <t>osVq-fgZU</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>RBA20127</t>
+          <t>RER39252</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>k0PV-kGg5</t>
+          <t>BvMj-N9IT</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>RER39252</t>
+          <t>RFD76685</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>fTzk-P9W0</t>
+          <t>Fnvz-gfX3</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>RFD76685</t>
+          <t>RLQ73857</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>U2Hl-cAtA</t>
+          <t>2DdR-7K2e</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>RLQ73857</t>
+          <t>RMV88503</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>tnGt-MahF</t>
+          <t>lOMy-nxHM</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>RMV88503</t>
+          <t>RNL06004</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>rI1x-25pS</t>
+          <t>I9kT-DwN6</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>RNL06004</t>
+          <t>RQV81451</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>armr-rKBl</t>
+          <t>zE2x-ykvO</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>RQV81451</t>
+          <t>RSN71799</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Yg7Q-mBda</t>
+          <t>9Rw3-p7CC</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RSN71799</t>
+          <t>RSV50349</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>qdbI-lN4T</t>
+          <t>56hT-Uwjj</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>RSV50349</t>
+          <t>RVG62147</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>aybp-KeH5</t>
+          <t>k1kl-1E5f</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RVG62147</t>
+          <t>SAF98648</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>hdOB-bZqg</t>
+          <t>i7dp-sU0E</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SAF98648</t>
+          <t>SDE98641</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>t1wK-8FYL</t>
+          <t>7zcz-Gwju</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>SDE98641</t>
+          <t>SEV98034</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Ip1U-pkPo</t>
+          <t>EKE3-c0wv</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>SEV98034</t>
+          <t>SGE51092</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>t9nq-8CNT</t>
+          <t>SV7q-C61L</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>SGE51092</t>
+          <t>SGY00276</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>S5DV-55jG</t>
+          <t>gu4P-t3LQ</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>SGY00276</t>
+          <t>SLP43775</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>dgnZ-AHKA</t>
+          <t>7gq9-9swT</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>SLP43775</t>
+          <t>SMF79012</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>phpe-wbti</t>
+          <t>mQY7-RSxu</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SMF79012</t>
+          <t>SNZ44527</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>i40Y-C0v6</t>
+          <t>WTEn-aPsu</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SNZ44527</t>
+          <t>SPL79883</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>JLt1-KNN8</t>
+          <t>GqsR-9fc9</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SPL79883</t>
+          <t>SPZ85652</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Tlmi-i1EH</t>
+          <t>Teel-i7VE</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SPZ85652</t>
+          <t>SQX65443</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>9WXL-YOga</t>
+          <t>Vksx-hvgQ</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SQX65443</t>
+          <t>SSU10232</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>hy2t-V4p3</t>
+          <t>URo5-xRti</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SSU10232</t>
+          <t>SWB32390</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>e6Q6-RTlK</t>
+          <t>9ONH-W4IM</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SWB32390</t>
+          <t>SXZ01554</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>r91p-9rgv</t>
+          <t>jL7R-QEpY</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SXZ01554</t>
+          <t>SYH46751</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>x3WB-imxE</t>
+          <t>qZYc-myNK</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SYH46751</t>
+          <t>TFD08485</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>ilLg-xVFo</t>
+          <t>I1Lt-t5Dt</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>TFD08485</t>
+          <t>TGM55607</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>nuRp-Tspd</t>
+          <t>cNkY-uwcH</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>TGM55607</t>
+          <t>TKW11810</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>AYnx-ZyDl</t>
+          <t>4QK9-TBnC</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>TKW11810</t>
+          <t>TME86867</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>1L4s-ntqZ</t>
+          <t>4CqV-DnUY</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>TME86867</t>
+          <t>TMJ36970</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>4HPa-OjUT</t>
+          <t>N4Se-Mjqf</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TMJ36970</t>
+          <t>TRC98148</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>bCtI-k8TV</t>
+          <t>K0Zj-b13J</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>TRC98148</t>
+          <t>TTS04230</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>hBoE-eVFc</t>
+          <t>qYDa-xd2m</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TTS04230</t>
+          <t>TXC42578</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>AVfs-TcsW</t>
+          <t>q5tk-GEZC</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TXC42578</t>
+          <t>UIB17642</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>6ehN-iRcy</t>
+          <t>k7cs-Q0Oa</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>UIB17642</t>
+          <t>UOI75021</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>ySbB-p9iS</t>
+          <t>WVAl-jZer</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>UOI75021</t>
+          <t>UUR79971</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>ynf6-7HwC</t>
+          <t>fNLs-8zL7</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>UUR79971</t>
+          <t>VDD06679</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>exlP-cIgv</t>
+          <t>nD61-NDNR</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>VDD06679</t>
+          <t>VEC51795</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>f85c-Ywlm</t>
+          <t>is5G-nBno</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>VEC51795</t>
+          <t>VEQ81429</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>sy5J-WcQR</t>
+          <t>M3I3-HvPY</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>VEQ81429</t>
+          <t>VHB06952</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>vAbE-2BER</t>
+          <t>cJ8p-fupV</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>VHB06952</t>
+          <t>VPE32737</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>7APB-BwPV</t>
+          <t>jO1z-7ZcG</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>VPE32737</t>
+          <t>VSG31611</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Pb0m-THZN</t>
+          <t>6QQY-P9vf</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>VSG31611</t>
+          <t>VYM86842</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>KIsV-NrMS</t>
+          <t>hiLV-iJgt</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>VYM86842</t>
+          <t>WEO81262</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>ptXQ-J0AN</t>
+          <t>EG2F-k5tT</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>WEO81262</t>
+          <t>WHV65431</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>siFx-58nj</t>
+          <t>goLc-8fjj</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>WHV65431</t>
+          <t>WJH36041</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>fJ1l-C5X7</t>
+          <t>WRjp-YyEY</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>WJH36041</t>
+          <t>WNA57398</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>vZxH-BvI5</t>
+          <t>g54L-gT81</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>WNA57398</t>
+          <t>WQS25133</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>5AkD-8KnH</t>
+          <t>0MjX-zWYb</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>WQS25133</t>
+          <t>WUA13603</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>ezLv-iTSL</t>
+          <t>0SN7-dbZL</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>WUA13603</t>
+          <t>WUH93925</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>XFHM-tVYZ</t>
+          <t>iQ9a-s9mS</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>WUH93925</t>
+          <t>WVY21466</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>rmL3-PtrC</t>
+          <t>69jF-O3uN</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>WVY21466</t>
+          <t>WWS24235</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>4RaP-7LTS</t>
+          <t>Kqxj-qGJK</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>WWS24235</t>
+          <t>XED10282</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>p86A-fE5e</t>
+          <t>yp1f-CEkJ</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>XED10282</t>
+          <t>XKS75480</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>eCSL-WsVn</t>
+          <t>4ZEF-pIA7</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>XKS75480</t>
+          <t>XOA75961</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>t19C-XZql</t>
+          <t>44VC-DjLo</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>XOA75961</t>
+          <t>XOS17378</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>0HVJ-joGg</t>
+          <t>4WzI-S9ig</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>XOS17378</t>
+          <t>XRM79618</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>aBHx-vajQ</t>
+          <t>Wo2L-gXKK</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>XRM79618</t>
+          <t>XSL75240</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>LuIM-182i</t>
+          <t>JJmZ-jxHU</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>XSL75240</t>
+          <t>XYT33259</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>edMy-G8od</t>
+          <t>zlPX-rTCH</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>XYT33259</t>
+          <t>XYZ70850</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>S7u3-mI4a</t>
+          <t>TgDG-ODgx</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>XYZ70850</t>
+          <t>XZC74148</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>kW7f-t5Oo</t>
+          <t>7XuE-IgAx</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>XZC74148</t>
+          <t>YBX87679</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>tGaK-Nttk</t>
+          <t>XCRE-OPNs</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>YBX87679</t>
+          <t>YCN31679</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>XI5K-ouf1</t>
+          <t>ZadT-JIN2</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>YCN31679</t>
+          <t>YEK78642</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>8RYH-JbUl</t>
+          <t>wtHN-d7Q3</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>YEK78642</t>
+          <t>YFU10307</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>SdOE-n4Qj</t>
+          <t>iMGr-5SYW</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>YFU10307</t>
+          <t>YHZ51082</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Bb3H-4L13</t>
+          <t>vLOX-Iavh</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>YHZ51082</t>
+          <t>YOT12953</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>hl04-gpfd</t>
+          <t>jnuC-9Yed</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>YOT12953</t>
+          <t>ZAM21080</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>XK3E-SCSS</t>
+          <t>5q2w-TLAy</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>ZAM21080</t>
+          <t>ZFB81591</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>9VpM-VrmX</t>
+          <t>HRQR-1IMI</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>ZFB81591</t>
+          <t>ZHU54125</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>tID3-9I5Z</t>
+          <t>aQ3J-ZmLK</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>ZHU54125</t>
+          <t>ZLP77106</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>eDMH-ccdw</t>
+          <t>IEJc-jF09</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>ZLP77106</t>
+          <t>ZNA23106</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>eDlA-xbzB</t>
+          <t>icfO-yrQu</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>ZNA23106</t>
+          <t>ZPU29378</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>0bHd-KnZJ</t>
+          <t>Cdcx-YiMr</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>ZPU29378</t>
+          <t>ZSU27095</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>2tM1-lA5u</t>
+          <t>DbrT-7siT</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>ZSU27095</t>
+          <t>ZVK04224</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Ammt-wQv9</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" t="inlineStr">
-        <is>
-          <t>ZVK04224</t>
-        </is>
-      </c>
-      <c r="B250" t="inlineStr">
-        <is>
-          <t>LacF-jBkj</t>
+          <t>MJae-mXRT</t>
         </is>
       </c>
     </row>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4Vs0-MW8g</t>
+          <t>4zir-bsfb</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Y6Tg-zV3B</t>
+          <t>Oj9J-OwCr</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>J8il-ibpL</t>
+          <t>kokC-k6lT</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>f8Qi-AvSh</t>
+          <t>XT10-My83</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1uUb-l51S</t>
+          <t>MZzc-Ah9l</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hWmA-f4Gu</t>
+          <t>31Gv-WkEc</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Fnsy-SqSp</t>
+          <t>rvk5-lIz3</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>pN3y-ztOG</t>
+          <t>KYnE-2iA1</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>FAYx-QZoD</t>
+          <t>ntHW-JS3J</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>9m3u-z4vf</t>
+          <t>QE0E-A0cS</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>L7Hn-XFfB</t>
+          <t>Yvww-etcw</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>aGGn-Mtmp</t>
+          <t>DuxM-7X46</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>wvzt-fmHY</t>
+          <t>ouQZ-WSaa</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Q7xh-W7oK</t>
+          <t>wG7G-26jW</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>lGuf-t0BH</t>
+          <t>GRXO-j6Td</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EXut-EfVh</t>
+          <t>jfSo-dCrj</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LrtT-AaAW</t>
+          <t>bYiD-Q9v9</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>iLeg-BwhE</t>
+          <t>u5Fs-AQsG</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4YqA-ge8W</t>
+          <t>9RA7-bLxD</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>FMMt-vZta</t>
+          <t>a6M0-zYrC</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>WZa1-sKRz</t>
+          <t>Qkbt-4873</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CFPr-vwEH</t>
+          <t>aVWR-s8nA</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2JwI-5gyc</t>
+          <t>4Jwq-tvP3</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>KEDs-eU5A</t>
+          <t>htcP-nCwJ</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>i8EM-Wpso</t>
+          <t>noFO-vBeB</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>AUUy-ubyU</t>
+          <t>4t2y-dd6C</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>gvTg-ntIR</t>
+          <t>rNyy-S7K9</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>kb7k-Kz2R</t>
+          <t>DRLD-Uoiw</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3FT1-F2Wr</t>
+          <t>kRkw-1keu</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WC7u-Vwsa</t>
+          <t>hfhx-Nnzd</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ow29-f2CN</t>
+          <t>7McA-CQQi</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Haak-V0wc</t>
+          <t>oZgY-qQHz</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>iPVC-XRob</t>
+          <t>HUmr-BZMt</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>6ot3-OB8h</t>
+          <t>QOL9-55ow</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>v6AP-PvqQ</t>
+          <t>uZmy-6bpM</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0wpN-5hXA</t>
+          <t>6bF7-8cdu</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>WLH6-QyZ7</t>
+          <t>xj3L-FH5O</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>hbpQ-J84g</t>
+          <t>Wgxs-4ZDO</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>JOXg-zs1s</t>
+          <t>Hga7-J6Ck</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>v7Mp-H1lL</t>
+          <t>Nb5N-3RsA</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Rhow-ZZjw</t>
+          <t>sGHN-FPPt</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Sjz6-L78y</t>
+          <t>6ZWy-RYd2</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>58o3-CFNw</t>
+          <t>9C3O-KBpG</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>kBYK-HY9d</t>
+          <t>r0yu-Bye4</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>yaLG-XOWV</t>
+          <t>QE5g-8Nki</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>8hr3-AmWY</t>
+          <t>1W4F-30q9</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JkgH-KcWR</t>
+          <t>ZcTS-6ilz</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>UjPK-t5DQ</t>
+          <t>sgSv-1UxN</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>YUor-OCfM</t>
+          <t>ScMJ-Gl9O</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>eLh3-dcag</t>
+          <t>Gvog-jcWJ</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pijb-bvuD</t>
+          <t>AenR-sMMx</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>OAua-bzLf</t>
+          <t>Zl5D-MzKA</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2bXu-9UOi</t>
+          <t>QJms-4GeZ</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>axBf-GGfU</t>
+          <t>5C4J-ox35</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ZUUi-RmsK</t>
+          <t>2VPh-7znv</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nLk9-BcX4</t>
+          <t>MiE8-jkV9</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5gFR-PwkM</t>
+          <t>sHQu-yiny</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BJYH-r6AM</t>
+          <t>xngf-EOnZ</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4MXf-NqTg</t>
+          <t>Q9ex-ymhw</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>wMFc-UFb8</t>
+          <t>KEaN-EppL</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>yFYy-gnnz</t>
+          <t>tWoK-Conp</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>wwNH-Bx03</t>
+          <t>AAI8-pbUZ</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6sW6-VT5F</t>
+          <t>c0JI-woBp</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VA0A-e3Cw</t>
+          <t>A1QG-CZAo</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Whc9-ZfOJ</t>
+          <t>PKvv-UZRr</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PasO-ZBBm</t>
+          <t>zTK7-dos0</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jl2s-xTLa</t>
+          <t>dBLw-jtiF</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>7L5d-MZco</t>
+          <t>eH3f-eKjt</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ypzr-sMDa</t>
+          <t>zxtn-LcKy</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>HjnP-bMf7</t>
+          <t>JpEF-hmDT</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>ykpq-Yw5f</t>
+          <t>rUp7-34MU</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>gSrO-QmDW</t>
+          <t>TYFV-gX8y</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>B5B4-GpgC</t>
+          <t>oMbA-GDUd</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>bNeL-OSoB</t>
+          <t>71CO-Q4qI</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>wLhH-4So4</t>
+          <t>e0nI-hOsj</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IRHq-HUhY</t>
+          <t>biWo-dT4w</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0pod-B10f</t>
+          <t>wTV9-tfN6</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>q6kj-rLfc</t>
+          <t>hh1K-D7Kr</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>pm89-7L5F</t>
+          <t>mKE2-5DAz</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>aezm-9vGg</t>
+          <t>q9Zt-PLiT</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Nt8e-zu5a</t>
+          <t>wKWZ-Zn9l</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>s5M7-vasb</t>
+          <t>bYwn-En7O</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>O5SL-sxau</t>
+          <t>RW81-Is3W</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>YNFl-z4re</t>
+          <t>pnrh-dYOO</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MWJT-lOBc</t>
+          <t>0uCE-rXpQ</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ipju-ApeR</t>
+          <t>Cgr2-ZwLm</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>pSSX-tfOr</t>
+          <t>dDEw-KMgc</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Jd2Z-KqAj</t>
+          <t>K4Zq-CMbu</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WEiI-nmuy</t>
+          <t>xNv1-DV18</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>h8KJ-4i3h</t>
+          <t>4CaN-vvh1</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>ruIF-uH6Q</t>
+          <t>SI2A-wxoA</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>p4l1-6pfS</t>
+          <t>Vun1-1MrD</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>JubV-pIKE</t>
+          <t>nhdd-BJ0E</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>6vKX-1fAy</t>
+          <t>ipi5-fTKW</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>gP3K-RQS5</t>
+          <t>I7hJ-tqHS</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Ob7L-CCDt</t>
+          <t>Bacv-KIJs</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>jaW3-Wc1a</t>
+          <t>aEqK-1mEp</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>lw7D-sy07</t>
+          <t>7BEm-7ssB</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1fPi-xqiW</t>
+          <t>PfvI-AZeC</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>qxca-m8ET</t>
+          <t>x4ot-a3eJ</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>VmiB-qkgq</t>
+          <t>yJxi-Rlsa</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>D7vq-RLk9</t>
+          <t>nOvs-rUBK</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>qfrp-jWIs</t>
+          <t>YhCf-IDS6</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>6Yok-I6Uy</t>
+          <t>V7pV-Zw9v</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>ediU-PcZZ</t>
+          <t>t4dN-nI61</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GkE5-5tLJ</t>
+          <t>2tIu-FAoY</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>gLYJ-B13G</t>
+          <t>qt5R-6Juf</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>1uaj-eSqt</t>
+          <t>BFvL-QTKQ</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>gic5-Gr0T</t>
+          <t>5OpV-wE71</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>LGN2-R1ur</t>
+          <t>oIyj-jA9p</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>KjsV-xAiO</t>
+          <t>mU81-VaQH</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>dSt4-4m8N</t>
+          <t>g7SY-HY4k</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>p4in-wX1q</t>
+          <t>a52m-m89W</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>W5oY-6vCp</t>
+          <t>Vt8M-X2DY</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>mmWl-5eu2</t>
+          <t>kbFM-NsHL</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>4p9S-5RYF</t>
+          <t>Odwl-Dwui</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>h5JS-UXNQ</t>
+          <t>f8C4-aU6z</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>aiBU-zSdN</t>
+          <t>yf5A-sqwY</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ftNe-bYAg</t>
+          <t>VgC1-n5EE</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>HwRR-eU2G</t>
+          <t>54mv-WXUm</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>H3Fm-tGbj</t>
+          <t>KHBo-JabH</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Sql8-gH10</t>
+          <t>ssW8-Esm4</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>TNzH-fCNg</t>
+          <t>AfPB-8sjK</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>9GBB-2F8Z</t>
+          <t>e2NQ-cP4F</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>VdZf-9nQb</t>
+          <t>fkUC-VE9e</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>qMEW-W0V8</t>
+          <t>Gynj-h7yw</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>dVHE-H6ja</t>
+          <t>4C9R-pZdp</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>yvwZ-P5Y9</t>
+          <t>3L89-Bnq9</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>pdes-hA4I</t>
+          <t>eBvP-JT1t</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0sDE-y1xM</t>
+          <t>ZSsL-lrk3</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>jL14-qmf5</t>
+          <t>1Lzr-6MEC</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>kLuG-gkcx</t>
+          <t>X4SY-WgpQ</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>TifG-ds4R</t>
+          <t>he3p-ZTwa</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>InoH-H6YG</t>
+          <t>ffZp-H03c</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>G3uA-cUXz</t>
+          <t>mXyG-FYEb</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>CL7X-vfUv</t>
+          <t>J8uJ-86HH</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>6SLZ-uYRA</t>
+          <t>Lrzg-4Pg1</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>mKPv-a8yd</t>
+          <t>Xtaz-WrTu</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>OWVy-ndHp</t>
+          <t>o1tT-tylO</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>rWoY-igKS</t>
+          <t>TCNd-Nv5n</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>wAJa-tesj</t>
+          <t>9Qgy-UXwv</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>NVA5-lKLj</t>
+          <t>7h6V-oOmb</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>t31i-qwEP</t>
+          <t>rDr0-92FS</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ItRz-HK1N</t>
+          <t>j4pC-B4yX</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>TzMb-GFR6</t>
+          <t>Cggg-rTlJ</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>McdL-VMRL</t>
+          <t>vNlt-8mZx</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>A7PC-tXBr</t>
+          <t>DALm-s3Uv</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>8Ax0-HSZN</t>
+          <t>3f7G-xv1w</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>6fQM-iUy8</t>
+          <t>rj3k-EGab</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>CRYh-fEJL</t>
+          <t>Ew5n-ZEB0</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>b28r-c3fd</t>
+          <t>sspL-Gx7W</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>mVQm-I1Zt</t>
+          <t>prs4-D4PM</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>N8O6-6i5V</t>
+          <t>QsAC-gjQF</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>XiXo-dxsa</t>
+          <t>bALW-mzyt</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>QhPH-KehJ</t>
+          <t>owZ7-Bdkf</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>q0W2-rpjc</t>
+          <t>wjlr-XtKm</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>GjCH-Pzuv</t>
+          <t>UjnH-kmYE</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>JCET-cxBi</t>
+          <t>4RTa-QB12</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>VcME-tV56</t>
+          <t>Jj0o-lJp9</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>v1ET-cl2Y</t>
+          <t>a4FV-LCEd</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>YnrU-4pMt</t>
+          <t>Qe2L-JeqB</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>bgOH-fT8h</t>
+          <t>5jxo-GRBz</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>XAZ5-8AA6</t>
+          <t>MFnq-oHbO</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>tNdN-FY5c</t>
+          <t>lRpe-8gcR</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>1Sdh-Gk9v</t>
+          <t>4SNQ-6q3C</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>2GrK-oIFC</t>
+          <t>flmS-QApI</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>xBAR-H4mM</t>
+          <t>1f7z-grr6</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>UlwA-qypB</t>
+          <t>v88H-ZHEU</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>2yz2-kS30</t>
+          <t>VGch-GQ1e</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Jw8v-neBr</t>
+          <t>cfRU-y1NX</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>fuuV-0rON</t>
+          <t>vlFG-iqiN</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>PagX-5S0O</t>
+          <t>2f3q-SotQ</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>3KNF-Q0bk</t>
+          <t>rnQF-o5s4</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>osVq-fgZU</t>
+          <t>z0ZE-HaJV</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>BvMj-N9IT</t>
+          <t>ESI3-tc2p</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Fnvz-gfX3</t>
+          <t>1pi6-ddh6</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>2DdR-7K2e</t>
+          <t>xKiC-dh3N</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>lOMy-nxHM</t>
+          <t>1yYm-yp0q</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>I9kT-DwN6</t>
+          <t>pzrV-Z4Ez</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>zE2x-ykvO</t>
+          <t>QYMa-7mNW</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>9Rw3-p7CC</t>
+          <t>x1nA-mths</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>56hT-Uwjj</t>
+          <t>qUvu-u8vx</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>k1kl-1E5f</t>
+          <t>jGsJ-eKCD</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>i7dp-sU0E</t>
+          <t>4OGr-5Jch</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>7zcz-Gwju</t>
+          <t>X8HC-haSS</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>EKE3-c0wv</t>
+          <t>xE5P-qU5M</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>SV7q-C61L</t>
+          <t>sCj3-2o6e</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>gu4P-t3LQ</t>
+          <t>ECIX-A09C</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>7gq9-9swT</t>
+          <t>9yct-OKk0</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>mQY7-RSxu</t>
+          <t>vq2L-MKh5</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>WTEn-aPsu</t>
+          <t>AWhL-FrLO</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>GqsR-9fc9</t>
+          <t>HBXY-f0oC</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Teel-i7VE</t>
+          <t>CjZF-iwGY</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Vksx-hvgQ</t>
+          <t>0Eds-1gJX</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>URo5-xRti</t>
+          <t>O5mA-oR4X</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>9ONH-W4IM</t>
+          <t>OejP-pb8g</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>jL7R-QEpY</t>
+          <t>HKMd-Go2r</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>qZYc-myNK</t>
+          <t>PX1E-uiQQ</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>I1Lt-t5Dt</t>
+          <t>xiNg-YECh</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>cNkY-uwcH</t>
+          <t>C7ZB-qHbl</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>4QK9-TBnC</t>
+          <t>soh7-LjpF</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>4CqV-DnUY</t>
+          <t>CDmn-VaqI</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>N4Se-Mjqf</t>
+          <t>OW5j-pGL4</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>K0Zj-b13J</t>
+          <t>U90N-TTGF</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>qYDa-xd2m</t>
+          <t>seWe-PgNp</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>q5tk-GEZC</t>
+          <t>rH36-pPzf</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>k7cs-Q0Oa</t>
+          <t>x4qO-V9lk</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>WVAl-jZer</t>
+          <t>zPyB-xYQS</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>fNLs-8zL7</t>
+          <t>qlPk-Nd6p</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>nD61-NDNR</t>
+          <t>zdUP-Wsyy</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>is5G-nBno</t>
+          <t>xW4j-kb2q</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>M3I3-HvPY</t>
+          <t>qK9t-l201</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>cJ8p-fupV</t>
+          <t>6GJE-ZbGk</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>jO1z-7ZcG</t>
+          <t>gQGU-lzTO</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>6QQY-P9vf</t>
+          <t>MLDO-pn7x</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>hiLV-iJgt</t>
+          <t>Wjcm-a9sm</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>EG2F-k5tT</t>
+          <t>Y8YD-kvZO</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>goLc-8fjj</t>
+          <t>5cAH-fiCE</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>WRjp-YyEY</t>
+          <t>IAet-VDWt</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>g54L-gT81</t>
+          <t>iu8F-LwHc</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>0MjX-zWYb</t>
+          <t>bgq6-xYjx</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>0SN7-dbZL</t>
+          <t>Ng9j-gCYO</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>iQ9a-s9mS</t>
+          <t>BoUe-RX3x</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>69jF-O3uN</t>
+          <t>6EYU-Qlma</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Kqxj-qGJK</t>
+          <t>fEm9-bYuf</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>yp1f-CEkJ</t>
+          <t>viRo-nyqG</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>4ZEF-pIA7</t>
+          <t>7jRG-F09d</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>44VC-DjLo</t>
+          <t>NlxD-B8hW</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>4WzI-S9ig</t>
+          <t>k8xL-ma2t</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Wo2L-gXKK</t>
+          <t>R33u-shkL</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>JJmZ-jxHU</t>
+          <t>CJVe-bHs0</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>zlPX-rTCH</t>
+          <t>PVdj-oHTu</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>TgDG-ODgx</t>
+          <t>HPi3-5wSr</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>7XuE-IgAx</t>
+          <t>ppeB-QzZt</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>XCRE-OPNs</t>
+          <t>wQzI-iWmR</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>ZadT-JIN2</t>
+          <t>qo9H-tYB6</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>wtHN-d7Q3</t>
+          <t>YT2S-CCyZ</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>iMGr-5SYW</t>
+          <t>d6nC-T7M5</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>vLOX-Iavh</t>
+          <t>WFyX-rlHf</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>jnuC-9Yed</t>
+          <t>4vPR-Kynb</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>5q2w-TLAy</t>
+          <t>lFte-XILo</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>HRQR-1IMI</t>
+          <t>ZpnF-OtMk</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>aQ3J-ZmLK</t>
+          <t>a29C-BcIz</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>IEJc-jF09</t>
+          <t>DpKX-cNeM</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>icfO-yrQu</t>
+          <t>VuoD-UBRR</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Cdcx-YiMr</t>
+          <t>Zybt-HSrs</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>DbrT-7siT</t>
+          <t>QPns-KrrT</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>MJae-mXRT</t>
+          <t>E1KP-pZlq</t>
         </is>
       </c>
     </row>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -448,7 +448,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4zir-bsfb</t>
+          <t>vp6P-m8XF</t>
         </is>
       </c>
     </row>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Oj9J-OwCr</t>
+          <t>MfZa-gAiD</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>kokC-k6lT</t>
+          <t>02b1-PgGb</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>XT10-My83</t>
+          <t>omfl-T4bP</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MZzc-Ah9l</t>
+          <t>d0qO-ifY3</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31Gv-WkEc</t>
+          <t>gAvH-uhbO</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>rvk5-lIz3</t>
+          <t>ieJB-AZCd</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KYnE-2iA1</t>
+          <t>r5nk-hQiw</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ntHW-JS3J</t>
+          <t>jnAM-JsAH</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>QE0E-A0cS</t>
+          <t>lmjD-vzjt</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Yvww-etcw</t>
+          <t>qBMp-jFup</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DuxM-7X46</t>
+          <t>Dx5e-e3qI</t>
         </is>
       </c>
     </row>
@@ -592,7 +592,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ouQZ-WSaa</t>
+          <t>Sx2S-ygz3</t>
         </is>
       </c>
     </row>
@@ -604,7 +604,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>wG7G-26jW</t>
+          <t>MqKW-3yeK</t>
         </is>
       </c>
     </row>
@@ -616,7 +616,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GRXO-j6Td</t>
+          <t>PBPI-pY0J</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>jfSo-dCrj</t>
+          <t>IxgT-jQSC</t>
         </is>
       </c>
     </row>
@@ -640,7 +640,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>bYiD-Q9v9</t>
+          <t>83px-gjo9</t>
         </is>
       </c>
     </row>
@@ -652,7 +652,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>u5Fs-AQsG</t>
+          <t>4Dev-CtY8</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>9RA7-bLxD</t>
+          <t>rRoC-i8Df</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>a6M0-zYrC</t>
+          <t>dP18-KyL0</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Qkbt-4873</t>
+          <t>Bify-ERmM</t>
         </is>
       </c>
     </row>
@@ -700,7 +700,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>aVWR-s8nA</t>
+          <t>5xTQ-LNP3</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4Jwq-tvP3</t>
+          <t>avRi-haTc</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>htcP-nCwJ</t>
+          <t>rTSA-5UpI</t>
         </is>
       </c>
     </row>
@@ -736,7 +736,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>noFO-vBeB</t>
+          <t>FCfO-UuUE</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>4t2y-dd6C</t>
+          <t>pQFV-zco4</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>rNyy-S7K9</t>
+          <t>pCS4-sGyp</t>
         </is>
       </c>
     </row>
@@ -772,7 +772,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DRLD-Uoiw</t>
+          <t>vxYo-NVNj</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>kRkw-1keu</t>
+          <t>8o4T-3ypw</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>hfhx-Nnzd</t>
+          <t>MEhu-WENy</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7McA-CQQi</t>
+          <t>Xfk4-vmlc</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>oZgY-qQHz</t>
+          <t>2nNP-xJUI</t>
         </is>
       </c>
     </row>
@@ -832,7 +832,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HUmr-BZMt</t>
+          <t>QZUD-gMsC</t>
         </is>
       </c>
     </row>
@@ -844,7 +844,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>QOL9-55ow</t>
+          <t>ROfS-4xG0</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>uZmy-6bpM</t>
+          <t>Xta8-3RiZ</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>6bF7-8cdu</t>
+          <t>QmFm-L5gz</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>xj3L-FH5O</t>
+          <t>k1l3-irnp</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Wgxs-4ZDO</t>
+          <t>WMHV-PqOw</t>
         </is>
       </c>
     </row>
@@ -904,7 +904,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Hga7-J6Ck</t>
+          <t>xJ6d-nOeH</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nb5N-3RsA</t>
+          <t>iPbP-VbL8</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>sGHN-FPPt</t>
+          <t>wcuj-4fVY</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>6ZWy-RYd2</t>
+          <t>hQbY-uKiH</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9C3O-KBpG</t>
+          <t>fLZS-EPr0</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>r0yu-Bye4</t>
+          <t>Hz0f-0MfM</t>
         </is>
       </c>
     </row>
@@ -976,7 +976,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>QE5g-8Nki</t>
+          <t>OFGS-KFYb</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1W4F-30q9</t>
+          <t>Uaqf-Sh8V</t>
         </is>
       </c>
     </row>
@@ -1000,7 +1000,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>ZcTS-6ilz</t>
+          <t>54qK-Koku</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>sgSv-1UxN</t>
+          <t>rAiO-zeRi</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ScMJ-Gl9O</t>
+          <t>AGIt-wZfE</t>
         </is>
       </c>
     </row>
@@ -1036,7 +1036,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Gvog-jcWJ</t>
+          <t>d0ul-Miun</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>AenR-sMMx</t>
+          <t>78km-8tjf</t>
         </is>
       </c>
     </row>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Zl5D-MzKA</t>
+          <t>E74P-iWHh</t>
         </is>
       </c>
     </row>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>QJms-4GeZ</t>
+          <t>k8tP-7SnM</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5C4J-ox35</t>
+          <t>gVxG-Fb1S</t>
         </is>
       </c>
     </row>
@@ -1096,7 +1096,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2VPh-7znv</t>
+          <t>UxhJ-sUVr</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>MiE8-jkV9</t>
+          <t>NFhq-noJT</t>
         </is>
       </c>
     </row>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>sHQu-yiny</t>
+          <t>9IxV-0AzM</t>
         </is>
       </c>
     </row>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>xngf-EOnZ</t>
+          <t>fEK2-8aDJ</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Q9ex-ymhw</t>
+          <t>4Uje-BKmV</t>
         </is>
       </c>
     </row>
@@ -1156,7 +1156,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>KEaN-EppL</t>
+          <t>GomM-VNYr</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>tWoK-Conp</t>
+          <t>9LaX-8j4j</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AAI8-pbUZ</t>
+          <t>b5j3-8DP8</t>
         </is>
       </c>
     </row>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>c0JI-woBp</t>
+          <t>GFjH-SzP0</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>A1QG-CZAo</t>
+          <t>X2Ww-XpVR</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PKvv-UZRr</t>
+          <t>ChhS-BM13</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>zTK7-dos0</t>
+          <t>1wrJ-lwqV</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1240,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>dBLw-jtiF</t>
+          <t>vTLU-Fe9r</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>eH3f-eKjt</t>
+          <t>OOZo-7mR8</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>zxtn-LcKy</t>
+          <t>bwtJ-yKAx</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JpEF-hmDT</t>
+          <t>kSMR-huTt</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>rUp7-34MU</t>
+          <t>W4DL-RZlP</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>TYFV-gX8y</t>
+          <t>7Yn0-c6Vb</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>oMbA-GDUd</t>
+          <t>h9B2-oJy0</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>71CO-Q4qI</t>
+          <t>dWSo-oSZS</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>e0nI-hOsj</t>
+          <t>Agbv-LTOC</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>biWo-dT4w</t>
+          <t>4prB-67K4</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>wTV9-tfN6</t>
+          <t>QMYX-h0UA</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>hh1K-D7Kr</t>
+          <t>PHEP-92JN</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>mKE2-5DAz</t>
+          <t>SkS8-tEBX</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>q9Zt-PLiT</t>
+          <t>i0DF-RBBN</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>wKWZ-Zn9l</t>
+          <t>FzMN-ExMi</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>bYwn-En7O</t>
+          <t>IDx0-9r4Z</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>RW81-Is3W</t>
+          <t>5jPw-ifAM</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>pnrh-dYOO</t>
+          <t>oMMw-aU25</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0uCE-rXpQ</t>
+          <t>BBeP-NGPX</t>
         </is>
       </c>
     </row>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Cgr2-ZwLm</t>
+          <t>zAYl-WPmn</t>
         </is>
       </c>
     </row>
@@ -1480,7 +1480,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>dDEw-KMgc</t>
+          <t>bkVl-z1tv</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>K4Zq-CMbu</t>
+          <t>NM0P-INXh</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>xNv1-DV18</t>
+          <t>TPtV-yWWl</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>4CaN-vvh1</t>
+          <t>Avku-kb8V</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SI2A-wxoA</t>
+          <t>rIXG-slO0</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Vun1-1MrD</t>
+          <t>DM5Z-bhnb</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1552,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>nhdd-BJ0E</t>
+          <t>KPdD-QEnb</t>
         </is>
       </c>
     </row>
@@ -1564,7 +1564,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ipi5-fTKW</t>
+          <t>XdiO-fzUx</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>I7hJ-tqHS</t>
+          <t>hPw2-fDuz</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Bacv-KIJs</t>
+          <t>9sil-L8T8</t>
         </is>
       </c>
     </row>
@@ -1600,7 +1600,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>aEqK-1mEp</t>
+          <t>FQjj-JF6Y</t>
         </is>
       </c>
     </row>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>7BEm-7ssB</t>
+          <t>WjGt-hIpu</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>PfvI-AZeC</t>
+          <t>dUSP-pQyn</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>x4ot-a3eJ</t>
+          <t>lP7J-WzF7</t>
         </is>
       </c>
     </row>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>yJxi-Rlsa</t>
+          <t>0UJD-ukgD</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>nOvs-rUBK</t>
+          <t>6p9Q-EH3Z</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1672,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>YhCf-IDS6</t>
+          <t>fNBs-XwYu</t>
         </is>
       </c>
     </row>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>V7pV-Zw9v</t>
+          <t>iZrB-rETj</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>t4dN-nI61</t>
+          <t>jVfU-T9Qu</t>
         </is>
       </c>
     </row>
@@ -1708,7 +1708,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2tIu-FAoY</t>
+          <t>uzyn-jYW9</t>
         </is>
       </c>
     </row>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>qt5R-6Juf</t>
+          <t>V32T-KWdH</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>BFvL-QTKQ</t>
+          <t>rtfF-JLk5</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>5OpV-wE71</t>
+          <t>FXJi-SAua</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>oIyj-jA9p</t>
+          <t>1jt9-G1wQ</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1768,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>mU81-VaQH</t>
+          <t>06Ee-U4Aq</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>g7SY-HY4k</t>
+          <t>YrPT-I6Wz</t>
         </is>
       </c>
     </row>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>a52m-m89W</t>
+          <t>3Kwh-VBn0</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Vt8M-X2DY</t>
+          <t>ZqtO-Rljr</t>
         </is>
       </c>
     </row>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>kbFM-NsHL</t>
+          <t>Q1I9-w5pm</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Odwl-Dwui</t>
+          <t>qipn-1dE2</t>
         </is>
       </c>
     </row>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>f8C4-aU6z</t>
+          <t>i2x4-Vpu3</t>
         </is>
       </c>
     </row>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>yf5A-sqwY</t>
+          <t>0VHP-TIRs</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>VgC1-n5EE</t>
+          <t>cnHF-cS0w</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>54mv-WXUm</t>
+          <t>M94x-hsx9</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>KHBo-JabH</t>
+          <t>817h-pdVU</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ssW8-Esm4</t>
+          <t>L0tJ-vaOm</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>AfPB-8sjK</t>
+          <t>dxvO-ybIJ</t>
         </is>
       </c>
     </row>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>e2NQ-cP4F</t>
+          <t>5icC-OYBs</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1936,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>fkUC-VE9e</t>
+          <t>xmEH-foX9</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Gynj-h7yw</t>
+          <t>fBU2-UntU</t>
         </is>
       </c>
     </row>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>4C9R-pZdp</t>
+          <t>wpMD-hhdy</t>
         </is>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>3L89-Bnq9</t>
+          <t>joU4-IQqe</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>eBvP-JT1t</t>
+          <t>3pJf-PdpS</t>
         </is>
       </c>
     </row>
@@ -1996,7 +1996,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>ZSsL-lrk3</t>
+          <t>kNj7-zB6z</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>1Lzr-6MEC</t>
+          <t>xgOE-YjL7</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>X4SY-WgpQ</t>
+          <t>fOD6-Gqt1</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>he3p-ZTwa</t>
+          <t>sqBS-jyy3</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>ffZp-H03c</t>
+          <t>y4Rd-HobI</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2056,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>mXyG-FYEb</t>
+          <t>rWfB-fM4l</t>
         </is>
       </c>
     </row>
@@ -2068,7 +2068,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>J8uJ-86HH</t>
+          <t>8pJ9-Q4JR</t>
         </is>
       </c>
     </row>
@@ -2080,7 +2080,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Lrzg-4Pg1</t>
+          <t>hiR1-dOuf</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Xtaz-WrTu</t>
+          <t>XOhz-kt7G</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2104,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>o1tT-tylO</t>
+          <t>8t9E-OMSS</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2116,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>TCNd-Nv5n</t>
+          <t>Xx82-pPSz</t>
         </is>
       </c>
     </row>
@@ -2128,7 +2128,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>9Qgy-UXwv</t>
+          <t>N7if-XRIt</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>7h6V-oOmb</t>
+          <t>Xr33-pZ48</t>
         </is>
       </c>
     </row>
@@ -2152,7 +2152,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>rDr0-92FS</t>
+          <t>8O5e-zejU</t>
         </is>
       </c>
     </row>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>j4pC-B4yX</t>
+          <t>SU1p-XQfw</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Cggg-rTlJ</t>
+          <t>uXnP-vaUm</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>vNlt-8mZx</t>
+          <t>jWdg-U28N</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>DALm-s3Uv</t>
+          <t>6wnZ-8HUg</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>3f7G-xv1w</t>
+          <t>bMVh-HqIQ</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>rj3k-EGab</t>
+          <t>F1wJ-dY4I</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Ew5n-ZEB0</t>
+          <t>SXbM-INPS</t>
         </is>
       </c>
     </row>
@@ -2248,7 +2248,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>sspL-Gx7W</t>
+          <t>VxpX-PZyD</t>
         </is>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>prs4-D4PM</t>
+          <t>9WES-9Owf</t>
         </is>
       </c>
     </row>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>QsAC-gjQF</t>
+          <t>N1pS-qDqg</t>
         </is>
       </c>
     </row>
@@ -2284,7 +2284,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>bALW-mzyt</t>
+          <t>KHjD-rlEt</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>owZ7-Bdkf</t>
+          <t>Q5CI-pSL9</t>
         </is>
       </c>
     </row>
@@ -2308,7 +2308,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>wjlr-XtKm</t>
+          <t>wvvl-NvTC</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>UjnH-kmYE</t>
+          <t>a3Ev-aFDe</t>
         </is>
       </c>
     </row>
@@ -2332,7 +2332,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>4RTa-QB12</t>
+          <t>uuG4-WV4h</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Jj0o-lJp9</t>
+          <t>sXqf-VFUZ</t>
         </is>
       </c>
     </row>
@@ -2356,7 +2356,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>a4FV-LCEd</t>
+          <t>6GlE-mjul</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Qe2L-JeqB</t>
+          <t>ns9t-bbLp</t>
         </is>
       </c>
     </row>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5jxo-GRBz</t>
+          <t>ZkVh-PjOZ</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MFnq-oHbO</t>
+          <t>7xxz-i1IP</t>
         </is>
       </c>
     </row>
@@ -2404,7 +2404,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>lRpe-8gcR</t>
+          <t>DwZY-o6T2</t>
         </is>
       </c>
     </row>
@@ -2416,7 +2416,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>4SNQ-6q3C</t>
+          <t>Z5em-qjmP</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>flmS-QApI</t>
+          <t>Ng5S-jDsD</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>1f7z-grr6</t>
+          <t>c7Wu-Fguq</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>v88H-ZHEU</t>
+          <t>62NY-gkDz</t>
         </is>
       </c>
     </row>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>VGch-GQ1e</t>
+          <t>vDXh-sWdk</t>
         </is>
       </c>
     </row>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>cfRU-y1NX</t>
+          <t>fmti-PURG</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2488,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>vlFG-iqiN</t>
+          <t>Gwu5-WYSR</t>
         </is>
       </c>
     </row>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>2f3q-SotQ</t>
+          <t>3D7z-AWDM</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>rnQF-o5s4</t>
+          <t>osAx-99VR</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>z0ZE-HaJV</t>
+          <t>066Z-mRKY</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2536,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>ESI3-tc2p</t>
+          <t>GF4K-zqpV</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>1pi6-ddh6</t>
+          <t>iDU8-5ohW</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>xKiC-dh3N</t>
+          <t>vUtv-biRL</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>1yYm-yp0q</t>
+          <t>T4pC-bsmy</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>pzrV-Z4Ez</t>
+          <t>go4x-SaCU</t>
         </is>
       </c>
     </row>
@@ -2596,7 +2596,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>QYMa-7mNW</t>
+          <t>JlZu-5W9K</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>x1nA-mths</t>
+          <t>34We-qFSk</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>qUvu-u8vx</t>
+          <t>2qTb-lr2E</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2632,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>jGsJ-eKCD</t>
+          <t>lA6Y-oNLD</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>4OGr-5Jch</t>
+          <t>cBWo-nSa7</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>X8HC-haSS</t>
+          <t>mvMs-A88X</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>xE5P-qU5M</t>
+          <t>teFU-1g5m</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>sCj3-2o6e</t>
+          <t>MlFe-2l84</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ECIX-A09C</t>
+          <t>SnzL-cc1d</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2704,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>9yct-OKk0</t>
+          <t>TaXI-K9gw</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>vq2L-MKh5</t>
+          <t>LPOy-4zAE</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>AWhL-FrLO</t>
+          <t>gZrK-YEuK</t>
         </is>
       </c>
     </row>
@@ -2740,7 +2740,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>HBXY-f0oC</t>
+          <t>NlDF-9rLk</t>
         </is>
       </c>
     </row>
@@ -2752,7 +2752,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>CjZF-iwGY</t>
+          <t>koyX-ffpR</t>
         </is>
       </c>
     </row>
@@ -2764,7 +2764,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>0Eds-1gJX</t>
+          <t>CN2Y-wyu3</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>O5mA-oR4X</t>
+          <t>b6eL-ouQ1</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>OejP-pb8g</t>
+          <t>cL5O-BRDw</t>
         </is>
       </c>
     </row>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>HKMd-Go2r</t>
+          <t>6JkX-Oj10</t>
         </is>
       </c>
     </row>
@@ -2812,7 +2812,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>PX1E-uiQQ</t>
+          <t>euTL-op0i</t>
         </is>
       </c>
     </row>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>xiNg-YECh</t>
+          <t>lvEz-9bMf</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>C7ZB-qHbl</t>
+          <t>qMVP-Ffg3</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>soh7-LjpF</t>
+          <t>Usu4-z2lj</t>
         </is>
       </c>
     </row>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>CDmn-VaqI</t>
+          <t>qO9C-YMrs</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>OW5j-pGL4</t>
+          <t>KnUW-Tt59</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>U90N-TTGF</t>
+          <t>8mrv-Mqz5</t>
         </is>
       </c>
     </row>
@@ -2896,7 +2896,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>seWe-PgNp</t>
+          <t>fETQ-sIOG</t>
         </is>
       </c>
     </row>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>rH36-pPzf</t>
+          <t>YiL3-7pqZ</t>
         </is>
       </c>
     </row>
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>x4qO-V9lk</t>
+          <t>L9Xe-D6Cc</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2932,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>zPyB-xYQS</t>
+          <t>Ab89-iybI</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>qlPk-Nd6p</t>
+          <t>ZMnC-Qi6x</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>zdUP-Wsyy</t>
+          <t>hPPJ-MAMw</t>
         </is>
       </c>
     </row>
@@ -2968,7 +2968,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>xW4j-kb2q</t>
+          <t>C7Qa-KMMY</t>
         </is>
       </c>
     </row>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>qK9t-l201</t>
+          <t>RbVT-n08k</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>6GJE-ZbGk</t>
+          <t>A5KP-oTzC</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>gQGU-lzTO</t>
+          <t>HGqG-kRMf</t>
         </is>
       </c>
     </row>
@@ -3016,7 +3016,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>MLDO-pn7x</t>
+          <t>Qrce-ppqR</t>
         </is>
       </c>
     </row>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Wjcm-a9sm</t>
+          <t>0u5A-XH5S</t>
         </is>
       </c>
     </row>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Y8YD-kvZO</t>
+          <t>xxJ2-RAa1</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>5cAH-fiCE</t>
+          <t>d7vz-ingf</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>IAet-VDWt</t>
+          <t>Ikru-q5QM</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>iu8F-LwHc</t>
+          <t>RNNH-EgB4</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>bgq6-xYjx</t>
+          <t>XeSG-u0fH</t>
         </is>
       </c>
     </row>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Ng9j-gCYO</t>
+          <t>3fc1-7IuS</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>BoUe-RX3x</t>
+          <t>X0Cd-lZvB</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>6EYU-Qlma</t>
+          <t>axWI-S46h</t>
         </is>
       </c>
     </row>
@@ -3136,7 +3136,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>fEm9-bYuf</t>
+          <t>w9M2-pSFC</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>viRo-nyqG</t>
+          <t>5xWE-37kH</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>7jRG-F09d</t>
+          <t>UIOP-3KdL</t>
         </is>
       </c>
     </row>
@@ -3172,7 +3172,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>NlxD-B8hW</t>
+          <t>duB5-H5C4</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>k8xL-ma2t</t>
+          <t>xn7h-qB2k</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>R33u-shkL</t>
+          <t>VwcS-Ogfi</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>CJVe-bHs0</t>
+          <t>7eFJ-fiQA</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>PVdj-oHTu</t>
+          <t>2yno-9hqf</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>HPi3-5wSr</t>
+          <t>M5OE-naoj</t>
         </is>
       </c>
     </row>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>ppeB-QzZt</t>
+          <t>juw0-IeTh</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>wQzI-iWmR</t>
+          <t>rA0i-YPoU</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>qo9H-tYB6</t>
+          <t>rDQH-Dl4g</t>
         </is>
       </c>
     </row>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>YT2S-CCyZ</t>
+          <t>OM8T-p9MY</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3292,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>d6nC-T7M5</t>
+          <t>TqZT-we5J</t>
         </is>
       </c>
     </row>
@@ -3304,7 +3304,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>WFyX-rlHf</t>
+          <t>vBeI-RHa0</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>4vPR-Kynb</t>
+          <t>Bxvt-ebzu</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>lFte-XILo</t>
+          <t>bPEU-sTWf</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>ZpnF-OtMk</t>
+          <t>HYdN-Nw0x</t>
         </is>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>a29C-BcIz</t>
+          <t>8SQJ-b5Mz</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>DpKX-cNeM</t>
+          <t>ZaIO-nPhW</t>
         </is>
       </c>
     </row>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>VuoD-UBRR</t>
+          <t>oLRq-g96k</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Zybt-HSrs</t>
+          <t>B8in-S4JL</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>QPns-KrrT</t>
+          <t>h17K-4iVx</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>E1KP-pZlq</t>
+          <t>ANkA-qPc5</t>
         </is>
       </c>
     </row>

--- a/IDM_User_Codes.xlsx
+++ b/IDM_User_Codes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B258"/>
+  <dimension ref="A1:B263"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,3058 +467,3118 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AJF14211</t>
+          <t>AIM63883</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>02b1-PgGb</t>
+          <t>yH08-gAff</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AMX72670</t>
+          <t>AJF14211</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>omfl-T4bP</t>
+          <t>02b1-PgGb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ANW71835</t>
+          <t>AMX72670</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>d0qO-ifY3</t>
+          <t>omfl-T4bP</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ARC48959</t>
+          <t>ANW71835</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>gAvH-uhbO</t>
+          <t>d0qO-ifY3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ARL55178</t>
+          <t>ARC48959</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ieJB-AZCd</t>
+          <t>gAvH-uhbO</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AVJ39759</t>
+          <t>ARL55178</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>r5nk-hQiw</t>
+          <t>ieJB-AZCd</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AXM21790</t>
+          <t>AVJ39759</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>jnAM-JsAH</t>
+          <t>r5nk-hQiw</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>AZJ82844</t>
+          <t>AXM21790</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>lmjD-vzjt</t>
+          <t>jnAM-JsAH</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Admin</t>
+          <t>AZJ82844</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A1234</t>
+          <t>lmjD-vzjt</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BBA65823</t>
+          <t>Admin</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>qBMp-jFup</t>
+          <t>A1234</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>BFI60670</t>
+          <t>BBA65823</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dx5e-e3qI</t>
+          <t>qBMp-jFup</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BGG58729</t>
+          <t>BFI60670</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sx2S-ygz3</t>
+          <t>Dx5e-e3qI</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BHD97254</t>
+          <t>BGG58729</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ivHp-A2r6</t>
+          <t>Sx2S-ygz3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BJH88419</t>
+          <t>BHD97254</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>MqKW-3yeK</t>
+          <t>ivHp-A2r6</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BJW79616</t>
+          <t>BJH88419</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>PBPI-pY0J</t>
+          <t>MqKW-3yeK</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BOI99795</t>
+          <t>BJW79616</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>IxgT-jQSC</t>
+          <t>PBPI-pY0J</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BOZ64205</t>
+          <t>BOI99795</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>83px-gjo9</t>
+          <t>IxgT-jQSC</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BQV35355</t>
+          <t>BOZ64205</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4Dev-CtY8</t>
+          <t>83px-gjo9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BUR49898</t>
+          <t>BQV35355</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>rRoC-i8Df</t>
+          <t>4Dev-CtY8</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CBP36635</t>
+          <t>BUR49898</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>dP18-KyL0</t>
+          <t>rRoC-i8Df</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CDG44201</t>
+          <t>CBP36635</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Bify-ERmM</t>
+          <t>dP18-KyL0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CEG78579</t>
+          <t>CDG44201</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5xTQ-LNP3</t>
+          <t>Bify-ERmM</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CEV66266</t>
+          <t>CEG78579</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>avRi-haTc</t>
+          <t>5xTQ-LNP3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>CEX73283</t>
+          <t>CEV66266</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>rTSA-5UpI</t>
+          <t>avRi-haTc</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CGK70284</t>
+          <t>CEX73283</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FCfO-UuUE</t>
+          <t>rTSA-5UpI</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CGY86131</t>
+          <t>CGK70284</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>pQFV-zco4</t>
+          <t>FCfO-UuUE</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CHZ14322</t>
+          <t>CGY86131</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>pCS4-sGyp</t>
+          <t>pQFV-zco4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CMY62163</t>
+          <t>CHZ14322</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>vxYo-NVNj</t>
+          <t>pCS4-sGyp</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CNJ73848</t>
+          <t>CMY62163</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>8o4T-3ypw</t>
+          <t>vxYo-NVNj</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CNQ05106</t>
+          <t>CNJ73848</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MEhu-WENy</t>
+          <t>8o4T-3ypw</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CQL05471</t>
+          <t>CNQ05106</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Xfk4-vmlc</t>
+          <t>MEhu-WENy</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CQV21480</t>
+          <t>CQL05471</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2nNP-xJUI</t>
+          <t>Xfk4-vmlc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CST44061</t>
+          <t>CQV21480</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>QZUD-gMsC</t>
+          <t>2nNP-xJUI</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CWI21231</t>
+          <t>CST44061</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ROfS-4xG0</t>
+          <t>QZUD-gMsC</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CWI74996</t>
+          <t>CWI21231</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Xta8-3RiZ</t>
+          <t>ROfS-4xG0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CXY21844</t>
+          <t>CWI74996</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>QmFm-L5gz</t>
+          <t>Xta8-3RiZ</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CYN09662</t>
+          <t>CXY21844</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>k1l3-irnp</t>
+          <t>QmFm-L5gz</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DCC25940</t>
+          <t>CYN09662</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>WMHV-PqOw</t>
+          <t>k1l3-irnp</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>DEI55654</t>
+          <t>DCC25940</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>xJ6d-nOeH</t>
+          <t>WMHV-PqOw</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>DGL58063</t>
+          <t>DEI55654</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>iPbP-VbL8</t>
+          <t>xJ6d-nOeH</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DHH79187</t>
+          <t>DGL58063</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>wcuj-4fVY</t>
+          <t>iPbP-VbL8</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>DIZ91955</t>
+          <t>DHH79187</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>4RdG-anrm</t>
+          <t>wcuj-4fVY</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>DJK20638</t>
+          <t>DIZ91955</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>hQbY-uKiH</t>
+          <t>4RdG-anrm</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>DLF24523</t>
+          <t>DJK20638</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>fLZS-EPr0</t>
+          <t>hQbY-uKiH</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>DLP45053</t>
+          <t>DLF24523</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Hz0f-0MfM</t>
+          <t>fLZS-EPr0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DQD33133</t>
+          <t>DLP45053</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>OFGS-KFYb</t>
+          <t>Hz0f-0MfM</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DTZ69845</t>
+          <t>DQD33133</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Uaqf-Sh8V</t>
+          <t>OFGS-KFYb</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DUA61401</t>
+          <t>DTZ69845</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>54qK-Koku</t>
+          <t>Uaqf-Sh8V</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DVJ66295</t>
+          <t>DUA61401</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>rAiO-zeRi</t>
+          <t>54qK-Koku</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DXM69578</t>
+          <t>DVJ66295</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>AGIt-wZfE</t>
+          <t>rAiO-zeRi</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DZI77349</t>
+          <t>DXM69578</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>d0ul-Miun</t>
+          <t>AGIt-wZfE</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EBT22822</t>
+          <t>DZI77349</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>78km-8tjf</t>
+          <t>d0ul-Miun</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ECG95521</t>
+          <t>EBT22822</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>E74P-iWHh</t>
+          <t>78km-8tjf</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EPP90817</t>
+          <t>ECG95521</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>W1tu-Fqbz</t>
+          <t>E74P-iWHh</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EWP70521</t>
+          <t>EPP90817</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>k8tP-7SnM</t>
+          <t>W1tu-Fqbz</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EYO38305</t>
+          <t>EWP70521</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>gVxG-Fb1S</t>
+          <t>k8tP-7SnM</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>FJV52310</t>
+          <t>EYO38305</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>UxhJ-sUVr</t>
+          <t>gVxG-Fb1S</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FLQ72134</t>
+          <t>FJV52310</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NFhq-noJT</t>
+          <t>UxhJ-sUVr</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FNU34959</t>
+          <t>FLQ72134</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>9IxV-0AzM</t>
+          <t>NFhq-noJT</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FOE41721</t>
+          <t>FNU34959</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>fEK2-8aDJ</t>
+          <t>9IxV-0AzM</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FOJ78948</t>
+          <t>FOE41721</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4Uje-BKmV</t>
+          <t>fEK2-8aDJ</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FQP62630</t>
+          <t>FOJ78948</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GomM-VNYr</t>
+          <t>4Uje-BKmV</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FUSURIN1</t>
+          <t>FQP62630</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>9LaX-8j4j</t>
+          <t>GomM-VNYr</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>FVJ14662</t>
+          <t>FUSURIN1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>b5j3-8DP8</t>
+          <t>9LaX-8j4j</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>FWZ82980</t>
+          <t>FVJ14662</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GFjH-SzP0</t>
+          <t>b5j3-8DP8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>FXB60927</t>
+          <t>FWZ82980</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>X2Ww-XpVR</t>
+          <t>GFjH-SzP0</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GBS06994</t>
+          <t>FXB60927</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>ChhS-BM13</t>
+          <t>X2Ww-XpVR</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GCV61524</t>
+          <t>GBS06994</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1wrJ-lwqV</t>
+          <t>ChhS-BM13</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GEL08954</t>
+          <t>GCV61524</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>vTLU-Fe9r</t>
+          <t>1wrJ-lwqV</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GEP48591</t>
+          <t>GEL08954</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>OOZo-7mR8</t>
+          <t>vTLU-Fe9r</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GFN61654</t>
+          <t>GEP48591</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>bwtJ-yKAx</t>
+          <t>OOZo-7mR8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GIE22684</t>
+          <t>GFN61654</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>kSMR-huTt</t>
+          <t>bwtJ-yKAx</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GKE90115</t>
+          <t>GIE22684</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>W4DL-RZlP</t>
+          <t>kSMR-huTt</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GLG55164</t>
+          <t>GKE90115</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7Yn0-c6Vb</t>
+          <t>W4DL-RZlP</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GNX35494</t>
+          <t>GLG55164</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>LR4h-0j29</t>
+          <t>7Yn0-c6Vb</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GQG06884</t>
+          <t>GNX35494</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>h9B2-oJy0</t>
+          <t>LR4h-0j29</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GSY94523</t>
+          <t>GQG06884</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>dWSo-oSZS</t>
+          <t>h9B2-oJy0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>GVD45273</t>
+          <t>GSY94523</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Agbv-LTOC</t>
+          <t>dWSo-oSZS</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>GVM53776</t>
+          <t>GVD45273</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>4prB-67K4</t>
+          <t>Agbv-LTOC</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HBP33017</t>
+          <t>GVM53776</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>QMYX-h0UA</t>
+          <t>4prB-67K4</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HFX34792</t>
+          <t>GVP32724</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PHEP-92JN</t>
+          <t>QXqp-7XO7</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HMD58733</t>
+          <t>HBP33017</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SkS8-tEBX</t>
+          <t>QMYX-h0UA</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>HNS34640</t>
+          <t>HFX34792</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>i0DF-RBBN</t>
+          <t>PHEP-92JN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>HPT02640</t>
+          <t>HHH33520</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FzMN-ExMi</t>
+          <t>6ZGL-DomE</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>HQH08532</t>
+          <t>HLX84996</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IDx0-9r4Z</t>
+          <t>UqUi-NQdm</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>HRY29891</t>
+          <t>HMD58733</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>5jPw-ifAM</t>
+          <t>SkS8-tEBX</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>HTN73978</t>
+          <t>HNS34640</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>oMMw-aU25</t>
+          <t>i0DF-RBBN</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>HWP25524</t>
+          <t>HPT02640</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BBeP-NGPX</t>
+          <t>FzMN-ExMi</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>HXG62536</t>
+          <t>HQH08532</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>bMPZ-7q5b</t>
+          <t>IDx0-9r4Z</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>IAE88291</t>
+          <t>HRY29891</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>zAYl-WPmn</t>
+          <t>5jPw-ifAM</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>IFQ76747</t>
+          <t>HTN73978</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>bkVl-z1tv</t>
+          <t>oMMw-aU25</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>IGN23276</t>
+          <t>HWP25524</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>NM0P-INXh</t>
+          <t>BBeP-NGPX</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>IGX57659</t>
+          <t>HXG62536</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TPtV-yWWl</t>
+          <t>bMPZ-7q5b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>ILO34901</t>
+          <t>IAE88291</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Avku-kb8V</t>
+          <t>zAYl-WPmn</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>IMW07942</t>
+          <t>IFQ76747</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>rIXG-slO0</t>
+          <t>bkVl-z1tv</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>IQI33918</t>
+          <t>IGN23276</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DM5Z-bhnb</t>
+          <t>NM0P-INXh</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>IUU53315</t>
+          <t>IGX57659</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>KPdD-QEnb</t>
+          <t>TPtV-yWWl</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>IWX83001</t>
+          <t>ILO34901</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>XdiO-fzUx</t>
+          <t>Avku-kb8V</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>JJI69427</t>
+          <t>IMW07942</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>hPw2-fDuz</t>
+          <t>rIXG-slO0</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>JMV12916</t>
+          <t>IQI33918</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>9sil-L8T8</t>
+          <t>DM5Z-bhnb</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>JNQ15800</t>
+          <t>IUU53315</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>FQjj-JF6Y</t>
+          <t>KPdD-QEnb</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>JSH83558</t>
+          <t>IWX83001</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>WjGt-hIpu</t>
+          <t>XdiO-fzUx</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>JSO81414</t>
+          <t>JJI69427</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>dUSP-pQyn</t>
+          <t>hPw2-fDuz</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>JTN17189</t>
+          <t>JMV12916</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>lP7J-WzF7</t>
+          <t>9sil-L8T8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>JTQ20003</t>
+          <t>JNQ15800</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0UJD-ukgD</t>
+          <t>FQjj-JF6Y</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>KCH80368</t>
+          <t>JSH83558</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>6p9Q-EH3Z</t>
+          <t>WjGt-hIpu</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>KCS62207</t>
+          <t>JSO81414</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>fNBs-XwYu</t>
+          <t>dUSP-pQyn</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>KNB79119</t>
+          <t>JTN17189</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>iZrB-rETj</t>
+          <t>lP7J-WzF7</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>KPJ23941</t>
+          <t>JTQ20003</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>jVfU-T9Qu</t>
+          <t>0UJD-ukgD</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>KTK81122</t>
+          <t>KCH80368</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>uzyn-jYW9</t>
+          <t>6p9Q-EH3Z</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>KVA96952</t>
+          <t>KCS62207</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>V32T-KWdH</t>
+          <t>fNBs-XwYu</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>KVU62139</t>
+          <t>KNB79119</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>rtfF-JLk5</t>
+          <t>iZrB-rETj</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>KWN66857</t>
+          <t>KPJ23941</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>FXJi-SAua</t>
+          <t>jVfU-T9Qu</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>KZL99357</t>
+          <t>KTK81122</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>1jt9-G1wQ</t>
+          <t>uzyn-jYW9</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>KZU53477</t>
+          <t>KVA96952</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>06Ee-U4Aq</t>
+          <t>V32T-KWdH</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>LCT57577</t>
+          <t>KVU62139</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>YrPT-I6Wz</t>
+          <t>rtfF-JLk5</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>LFA56301</t>
+          <t>KWN66857</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>3Kwh-VBn0</t>
+          <t>FXJi-SAua</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>LHQ57930</t>
+          <t>KZL99357</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ZqtO-Rljr</t>
+          <t>1jt9-G1wQ</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>LJE73544</t>
+          <t>KZU53477</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Q1I9-w5pm</t>
+          <t>06Ee-U4Aq</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>LKG10504</t>
+          <t>LCT57577</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>qipn-1dE2</t>
+          <t>YrPT-I6Wz</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>LLI56060</t>
+          <t>LFA56301</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>i2x4-Vpu3</t>
+          <t>3Kwh-VBn0</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>LPM87075</t>
+          <t>LHQ57930</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0VHP-TIRs</t>
+          <t>ZqtO-Rljr</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MAI64055</t>
+          <t>LJE73544</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>cnHF-cS0w</t>
+          <t>Q1I9-w5pm</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MDE12029</t>
+          <t>LKG10504</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>M94x-hsx9</t>
+          <t>qipn-1dE2</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MEG11153</t>
+          <t>LLI56060</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>817h-pdVU</t>
+          <t>i2x4-Vpu3</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MIJ60289</t>
+          <t>LPM87075</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>L0tJ-vaOm</t>
+          <t>0VHP-TIRs</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MND74401</t>
+          <t>MAI64055</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>dxvO-ybIJ</t>
+          <t>cnHF-cS0w</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MNW15780</t>
+          <t>MDE12029</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5icC-OYBs</t>
+          <t>M94x-hsx9</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MRQ02763</t>
+          <t>MEG11153</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>xmEH-foX9</t>
+          <t>817h-pdVU</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MUX13896</t>
+          <t>MIJ60289</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>fBU2-UntU</t>
+          <t>L0tJ-vaOm</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MXC93247</t>
+          <t>MND74401</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>wpMD-hhdy</t>
+          <t>dxvO-ybIJ</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MXM72788</t>
+          <t>MNW15780</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>joU4-IQqe</t>
+          <t>5icC-OYBs</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MYD82527</t>
+          <t>MRQ02763</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>3pJf-PdpS</t>
+          <t>xmEH-foX9</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>MYX47244</t>
+          <t>MUX13896</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>kNj7-zB6z</t>
+          <t>fBU2-UntU</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NAQ63112</t>
+          <t>MXC93247</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>xgOE-YjL7</t>
+          <t>wpMD-hhdy</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NCL61296</t>
+          <t>MXM72788</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>fOD6-Gqt1</t>
+          <t>joU4-IQqe</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NCM04473</t>
+          <t>MYD82527</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>sqBS-jyy3</t>
+          <t>3pJf-PdpS</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NDJ67099</t>
+          <t>MYX47244</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>y4Rd-HobI</t>
+          <t>kNj7-zB6z</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>NEE79704</t>
+          <t>NAQ63112</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>rWfB-fM4l</t>
+          <t>xgOE-YjL7</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>NIQ43372</t>
+          <t>NCL61296</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>8pJ9-Q4JR</t>
+          <t>fOD6-Gqt1</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>NLP67632</t>
+          <t>NCM04473</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>hiR1-dOuf</t>
+          <t>sqBS-jyy3</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NPD00961</t>
+          <t>NDJ67099</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>XOhz-kt7G</t>
+          <t>y4Rd-HobI</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NUI19784</t>
+          <t>NEE79704</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>8t9E-OMSS</t>
+          <t>rWfB-fM4l</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>NWX06153</t>
+          <t>NIQ43372</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Xx82-pPSz</t>
+          <t>8pJ9-Q4JR</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>NYF03161</t>
+          <t>NLP67632</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>N7if-XRIt</t>
+          <t>hiR1-dOuf</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>NZW46214</t>
+          <t>NPD00961</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Xr33-pZ48</t>
+          <t>XOhz-kt7G</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>OAM83746</t>
+          <t>NUI19784</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>8O5e-zejU</t>
+          <t>8t9E-OMSS</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>OBI75581</t>
+          <t>NWX06153</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SU1p-XQfw</t>
+          <t>Xx82-pPSz</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>OBL79766</t>
+          <t>NYF03161</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>uXnP-vaUm</t>
+          <t>N7if-XRIt</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>ODU01918</t>
+          <t>NZW46214</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>jWdg-U28N</t>
+          <t>Xr33-pZ48</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>OEJ86175</t>
+          <t>OAM83746</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>6wnZ-8HUg</t>
+          <t>8O5e-zejU</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>OKY47911</t>
+          <t>OBI75581</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>bMVh-HqIQ</t>
+          <t>SU1p-XQfw</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>ORR85927</t>
+          <t>OBL79766</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>F1wJ-dY4I</t>
+          <t>uXnP-vaUm</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>ORT63362</t>
+          <t>ODU01918</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>SXbM-INPS</t>
+          <t>jWdg-U28N</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>OSB52441</t>
+          <t>OEJ86175</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>VxpX-PZyD</t>
+          <t>6wnZ-8HUg</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>OWO93746</t>
+          <t>OKY47911</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>9WES-9Owf</t>
+          <t>bMVh-HqIQ</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>OWR55957</t>
+          <t>ORR85927</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>N1pS-qDqg</t>
+          <t>F1wJ-dY4I</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>OXE34055</t>
+          <t>ORT63362</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>KHjD-rlEt</t>
+          <t>SXbM-INPS</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>OXH82758</t>
+          <t>OSB52441</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Q5CI-pSL9</t>
+          <t>VxpX-PZyD</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>OXK70326</t>
+          <t>OWO93746</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>wvvl-NvTC</t>
+          <t>9WES-9Owf</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>OYK39161</t>
+          <t>OWR55957</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>a3Ev-aFDe</t>
+          <t>N1pS-qDqg</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>OYZ43696</t>
+          <t>OXE34055</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>uuG4-WV4h</t>
+          <t>KHjD-rlEt</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PDL18808</t>
+          <t>OXH82758</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>sXqf-VFUZ</t>
+          <t>Q5CI-pSL9</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PDY46515</t>
+          <t>OXK70326</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>6GlE-mjul</t>
+          <t>wvvl-NvTC</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PHT01595</t>
+          <t>OYK39161</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>ns9t-bbLp</t>
+          <t>a3Ev-aFDe</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>PJT16152</t>
+          <t>OYZ43696</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>ZkVh-PjOZ</t>
+          <t>uuG4-WV4h</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PLL97657</t>
+          <t>PDL18808</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>7xxz-i1IP</t>
+          <t>sXqf-VFUZ</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PSM82237</t>
+          <t>PDY46515</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>DwZY-o6T2</t>
+          <t>6GlE-mjul</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PVU41752</t>
+          <t>PHT01595</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Z5em-qjmP</t>
+          <t>ns9t-bbLp</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PWD33511</t>
+          <t>PJT16152</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Ng5S-jDsD</t>
+          <t>ZkVh-PjOZ</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>QHB18956</t>
+          <t>PLL97657</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>c7Wu-Fguq</t>
+          <t>7xxz-i1IP</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>QJS17402</t>
+          <t>PSM82237</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>WFg9-AnQU</t>
+          <t>DwZY-o6T2</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>QKM89908</t>
+          <t>PVU41752</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>62NY-gkDz</t>
+          <t>Z5em-qjmP</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>QRB56514</t>
+          <t>PWD33511</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>vDXh-sWdk</t>
+          <t>Ng5S-jDsD</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>QUE22078</t>
+          <t>QHB18956</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>fmti-PURG</t>
+          <t>c7Wu-Fguq</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>QVI53832</t>
+          <t>QJS17402</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Gwu5-WYSR</t>
+          <t>WFg9-AnQU</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>QYS77373</t>
+          <t>QKM89908</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>3D7z-AWDM</t>
+          <t>62NY-gkDz</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>QYU41690</t>
+          <t>QRB56514</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>osAx-99VR</t>
+          <t>vDXh-sWdk</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>RBA20127</t>
+          <t>QUE22078</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>066Z-mRKY</t>
+          <t>fmti-PURG</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>RER39252</t>
+          <t>QVI53832</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>GF4K-zqpV</t>
+          <t>Gwu5-WYSR</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>RFD76685</t>
+          <t>QYS77373</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>iDU8-5ohW</t>
+          <t>3D7z-AWDM</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>RLQ73857</t>
+          <t>QYU41690</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>vUtv-biRL</t>
+          <t>osAx-99VR</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>RMV88503</t>
+          <t>RBA20127</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>T4pC-bsmy</t>
+          <t>066Z-mRKY</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>RNL06004</t>
+          <t>RER39252</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>go4x-SaCU</t>
+          <t>GF4K-zqpV</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>RQV81451</t>
+          <t>RFD76685</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>JlZu-5W9K</t>
+          <t>iDU8-5ohW</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>RSN71799</t>
+          <t>RLQ73857</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>34We-qFSk</t>
+          <t>vUtv-biRL</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>RSV50349</t>
+          <t>RMV88503</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>2qTb-lr2E</t>
+          <t>T4pC-bsmy</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>RVG62147</t>
+          <t>RNL06004</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>lA6Y-oNLD</t>
+          <t>go4x-SaCU</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>SAF98648</t>
+          <t>RQV81451</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>cBWo-nSa7</t>
+          <t>JlZu-5W9K</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SDE98641</t>
+          <t>RSN71799</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>mvMs-A88X</t>
+          <t>34We-qFSk</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>SEV98034</t>
+          <t>RSV50349</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>teFU-1g5m</t>
+          <t>2qTb-lr2E</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>SGE51092</t>
+          <t>RVG62147</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>MlFe-2l84</t>
+          <t>lA6Y-oNLD</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>SGY00276</t>
+          <t>SAF98648</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>SnzL-cc1d</t>
+          <t>cBWo-nSa7</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>SLP43775</t>
+          <t>SDE98641</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>TaXI-K9gw</t>
+          <t>mvMs-A88X</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>SMF79012</t>
+          <t>SEV98034</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>LPOy-4zAE</t>
+          <t>teFU-1g5m</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>SNZ44527</t>
+          <t>SGE51092</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>gZrK-YEuK</t>
+          <t>MlFe-2l84</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>SPL79883</t>
+          <t>SGY00276</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>NlDF-9rLk</t>
+          <t>SnzL-cc1d</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>SPZ85652</t>
+          <t>SLP43775</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>koyX-ffpR</t>
+          <t>TaXI-K9gw</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>SQX65443</t>
+          <t>SMF79012</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>CN2Y-wyu3</t>
+          <t>LPOy-4zAE</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>SSU10232</t>
+          <t>SNZ44527</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>b6eL-ouQ1</t>
+          <t>gZrK-YEuK</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>SWB32390</t>
+          <t>SPL79883</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>cL5O-BRDw</t>
+          <t>NlDF-9rLk</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>SXZ01554</t>
+          <t>SPZ85652</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>6JkX-Oj10</t>
+          <t>koyX-ffpR</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>SYH46751</t>
+          <t>SQX65443</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>euTL-op0i</t>
+          <t>CN2Y-wyu3</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>TFD08485</t>
+          <t>SSU10232</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>lvEz-9bMf</t>
+          <t>b6eL-ouQ1</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>TGM55607</t>
+          <t>SWB32390</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>qMVP-Ffg3</t>
+          <t>cL5O-BRDw</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>TKW11810</t>
+          <t>SXZ01554</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Usu4-z2lj</t>
+          <t>6JkX-Oj10</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>TME86867</t>
+          <t>SYH46751</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>qO9C-YMrs</t>
+          <t>euTL-op0i</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>TMJ36970</t>
+          <t>TFD08485</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>KnUW-Tt59</t>
+          <t>lvEz-9bMf</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>TRC98148</t>
+          <t>TGM55607</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>8mrv-Mqz5</t>
+          <t>qMVP-Ffg3</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>TTS04230</t>
+          <t>TKW11810</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>fETQ-sIOG</t>
+          <t>Usu4-z2lj</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TXC42578</t>
+          <t>TME86867</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>YiL3-7pqZ</t>
+          <t>qO9C-YMrs</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>UIB17642</t>
+          <t>TMJ36970</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>L9Xe-D6Cc</t>
+          <t>KnUW-Tt59</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>UOI75021</t>
+          <t>TRC98148</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Ab89-iybI</t>
+          <t>8mrv-Mqz5</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>UUR79971</t>
+          <t>TTS04230</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>ZMnC-Qi6x</t>
+          <t>fETQ-sIOG</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>VDD06679</t>
+          <t>TXC42578</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>hPPJ-MAMw</t>
+          <t>YiL3-7pqZ</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>VEC51795</t>
+          <t>UIB17642</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>C7Qa-KMMY</t>
+          <t>L9Xe-D6Cc</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>VEQ81429</t>
+          <t>UOI75021</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>RbVT-n08k</t>
+          <t>Ab89-iybI</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>VHB06952</t>
+          <t>UUR79971</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>A5KP-oTzC</t>
+          <t>ZMnC-Qi6x</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>VPE32737</t>
+          <t>VDD06679</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>HGqG-kRMf</t>
+          <t>hPPJ-MAMw</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>VSG31611</t>
+          <t>VEC51795</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Qrce-ppqR</t>
+          <t>C7Qa-KMMY</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>VYM86842</t>
+          <t>VEQ81429</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>0u5A-XH5S</t>
+          <t>RbVT-n08k</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>WEO81262</t>
+          <t>VHB06952</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>xxJ2-RAa1</t>
+          <t>A5KP-oTzC</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>WHV65431</t>
+          <t>VPE32737</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>d7vz-ingf</t>
+          <t>HGqG-kRMf</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>WJH36041</t>
+          <t>VSG31611</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Ikru-q5QM</t>
+          <t>Qrce-ppqR</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>WNA57398</t>
+          <t>VYM86842</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>RNNH-EgB4</t>
+          <t>0u5A-XH5S</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>WQS25133</t>
+          <t>WEO81262</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>XeSG-u0fH</t>
+          <t>xxJ2-RAa1</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>WUA13603</t>
+          <t>WHV65431</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>3fc1-7IuS</t>
+          <t>d7vz-ingf</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>WUH93925</t>
+          <t>WJH36041</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>X0Cd-lZvB</t>
+          <t>Ikru-q5QM</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>WVY21466</t>
+          <t>WNA57398</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>axWI-S46h</t>
+          <t>RNNH-EgB4</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>WWS24235</t>
+          <t>WPN55871</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>w9M2-pSFC</t>
+          <t>JiCz-AY5O</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>XED10282</t>
+          <t>WQS25133</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>5xWE-37kH</t>
+          <t>XeSG-u0fH</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>XKS75480</t>
+          <t>WUA13603</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>UIOP-3KdL</t>
+          <t>3fc1-7IuS</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>XOA75961</t>
+          <t>WUH93925</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>duB5-H5C4</t>
+          <t>X0Cd-lZvB</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>XOS17378</t>
+          <t>WVY21466</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>xn7h-qB2k</t>
+          <t>axWI-S46h</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>XRM79618</t>
+          <t>WWS24235</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>VwcS-Ogfi</t>
+          <t>w9M2-pSFC</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>XSL75240</t>
+          <t>XED10282</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>7eFJ-fiQA</t>
+          <t>5xWE-37kH</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>XYT33259</t>
+          <t>XKS75480</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>2yno-9hqf</t>
+          <t>UIOP-3KdL</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>XYZ70850</t>
+          <t>XOA75961</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>M5OE-naoj</t>
+          <t>duB5-H5C4</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>XZC74148</t>
+          <t>XOS17378</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>juw0-IeTh</t>
+          <t>xn7h-qB2k</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>XZY48875</t>
+          <t>XRM79618</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>lSZ9-XRCu</t>
+          <t>VwcS-Ogfi</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>YBX87679</t>
+          <t>XSL75240</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>rA0i-YPoU</t>
+          <t>7eFJ-fiQA</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>YCN31679</t>
+          <t>XYT33259</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>rDQH-Dl4g</t>
+          <t>2yno-9hqf</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>YEK78642</t>
+          <t>XYZ70850</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>OM8T-p9MY</t>
+          <t>M5OE-naoj</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>YFU10307</t>
+          <t>XZC74148</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>TqZT-we5J</t>
+          <t>juw0-IeTh</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>YHZ51082</t>
+          <t>XZY48875</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>vBeI-RHa0</t>
+          <t>lSZ9-XRCu</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>YOT12953</t>
+          <t>YBX87679</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Bxvt-ebzu</t>
+          <t>rA0i-YPoU</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>ZAM21080</t>
+          <t>YCN31679</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>bPEU-sTWf</t>
+          <t>rDQH-Dl4g</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>ZFB81591</t>
+          <t>YEK78642</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>HYdN-Nw0x</t>
+          <t>OM8T-p9MY</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>ZHU54125</t>
+          <t>YFU10307</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>8SQJ-b5Mz</t>
+          <t>TqZT-we5J</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>ZLP77106</t>
+          <t>YHZ51082</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>ZaIO-nPhW</t>
+          <t>vBeI-RHa0</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ZNA23106</t>
+          <t>YOT12953</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>oLRq-g96k</t>
+          <t>Bxvt-ebzu</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ZPU29378</t>
+          <t>ZAM21080</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>B8in-S4JL</t>
+          <t>bPEU-sTWf</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>ZSU27095</t>
+          <t>ZFB81591</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>h17K-4iVx</t>
+          <t>HYdN-Nw0x</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>ZVK04224</t>
+          <t>ZHU54125</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>ANkA-qPc5</t>
+          <t>8SQJ-b5Mz</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
+          <t>ZLP77106</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>ZaIO-nPhW</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>ZNA23106</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>oLRq-g96k</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>ZPU29378</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>B8in-S4JL</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>ZSU27095</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>h17K-4iVx</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>ZVK04224</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>ANkA-qPc5</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
           <t>ZXQ93619</t>
         </is>
       </c>
-      <c r="B258" t="inlineStr">
+      <c r="B263" t="inlineStr">
         <is>
           <t>A5LF-s4Q7</t>
         </is>
